--- a/출산준비물_통합데이터.xlsx
+++ b/출산준비물_통합데이터.xlsx
@@ -5,18 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://m100001874-my.sharepoint.com/personal/kong090821_cbsn-e_cbe_go_kr/Documents/2026학년도/인공지능/출산준비물어플/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\kongkong\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{320B26DF-CA25-4D3C-9A72-2B49BA6EE5DB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BBBE05E-9B08-4B26-BAAF-254A162E7872}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14415" activeTab="3" xr2:uid="{3135985E-FF11-40B9-B2CB-3B6A437FA0AD}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14415" activeTab="5" xr2:uid="{788198A8-8058-4D1A-8238-52DDCB41F95D}"/>
   </bookViews>
   <sheets>
     <sheet name="출산가방 체크리스트" sheetId="1" r:id="rId1"/>
     <sheet name="육아용품 체크리스트" sheetId="2" r:id="rId2"/>
     <sheet name="시기별할일" sheetId="3" r:id="rId3"/>
     <sheet name="출산혜택정리" sheetId="4" r:id="rId4"/>
+    <sheet name="🎯 맞춤_추천_설정" sheetId="5" r:id="rId5"/>
+    <sheet name="📊 사용자_활동_통계" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="792">
   <si>
     <t>ID</t>
   </si>
@@ -2296,6 +2298,114 @@
   </si>
   <si>
     <t>출생 후 3개월 이내</t>
+  </si>
+  <si>
+    <t>구분</t>
+  </si>
+  <si>
+    <t>추천 품목 ID 목록 (쉼표 구분)</t>
+  </si>
+  <si>
+    <t>설명 및 포함 품목 안내</t>
+  </si>
+  <si>
+    <t>제왕절개</t>
+  </si>
+  <si>
+    <t>m_cloth_7, m_hyg_7, m_hyg_1, m_cloth_5, g_life_1</t>
+  </si>
+  <si>
+    <t>산후복대, 흉터시트, 맘스안심팬티, 압박스타킹, 꺾인빨대 텀블러</t>
+  </si>
+  <si>
+    <t>자연분만</t>
+  </si>
+  <si>
+    <t>m_hyg_8, m_hyg_3, m_hyg_2</t>
+  </si>
+  <si>
+    <t>회음부방석, 마이비데, 오버나이트 생리대 세트</t>
+  </si>
+  <si>
+    <t>조리원이용</t>
+  </si>
+  <si>
+    <t>m_feed_1, m_feed_2, m_feed_4, m_feed_6, m_feed_7, m_cloth_6, b_care_3, b_care_4</t>
+  </si>
+  <si>
+    <t>수유패드, 저장팩, 유두크림, 유축깔때기, 손목보호대, 아기로션/영양제</t>
+  </si>
+  <si>
+    <t>자택조리</t>
+  </si>
+  <si>
+    <t>m_feed_1, m_feed_4, b_care_3</t>
+  </si>
+  <si>
+    <t>기본 수유패드, 유두보호크림, 아기로션</t>
+  </si>
+  <si>
+    <t>공통산모</t>
+  </si>
+  <si>
+    <t>m_cloth_1, m_cloth_2, m_cloth_3, m_cloth_4, m_cloth_8, m_sk_1, m_sk_2, m_sk_3</t>
+  </si>
+  <si>
+    <t>수유브라, 산모팬티, 무압박양말, 슬리퍼, 세면/화장품 세트</t>
+  </si>
+  <si>
+    <t>공통신생아</t>
+  </si>
+  <si>
+    <t>b_cloth_1, b_cloth_2, b_cloth_3, b_care_1, b_safe_1</t>
+  </si>
+  <si>
+    <t>배냇저고리, 속싸개, 겉싸개, 손수건, 카시트</t>
+  </si>
+  <si>
+    <t>공통보호자</t>
+  </si>
+  <si>
+    <t>g_doc_1, g_doc_2, g_life_4</t>
+  </si>
+  <si>
+    <t>산모수첩/신분증, 결제수단, 충전기/멀티탭</t>
+  </si>
+  <si>
+    <t>기록일시</t>
+  </si>
+  <si>
+    <t>사용자구분</t>
+  </si>
+  <si>
+    <t>이벤트</t>
+  </si>
+  <si>
+    <t>분만법</t>
+  </si>
+  <si>
+    <t>조리원여부</t>
+  </si>
+  <si>
+    <t>아기성별</t>
+  </si>
+  <si>
+    <t>지역</t>
+  </si>
+  <si>
+    <t>출산예정일</t>
+  </si>
+  <si>
+    <t>담은_출산가방수</t>
+  </si>
+  <si>
+    <t>담은_출산가방_품목ID</t>
+  </si>
+  <si>
+    <t>담은_육아용품수</t>
+  </si>
+  <si>
+    <t>담은_육아용품_품목ID</t>
   </si>
 </sst>
 </file>
@@ -2675,7 +2785,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C271EB9-E2ED-46C0-81E1-6BEC1697A853}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02C8DBF0-3492-48AF-92E6-1D1FFA7C9414}">
   <dimension ref="A1:K64"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -4655,7 +4765,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB2A766-F96F-472D-82E3-17788B73A90A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2770643F-111E-4A5D-8616-80859450F545}">
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -5357,7 +5467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE8A5D57-CB77-4B23-B381-6398AE762867}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16BB3175-6AFC-40CB-A530-D2B9F1E5D321}">
   <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -6072,7 +6182,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{286B01FB-B70B-4F8B-8CD0-985A8836AC47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667B3C2E-D9BA-4B3F-8DF3-50FFC17C28E3}">
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -6456,314 +6566,168 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x0101006B1953B06C073B43B6E722FE317AF72E" ma:contentTypeVersion="18" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="6fb64ccad2d49c8e48cfee9b7c295033">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="65819029-d4b2-4b56-9509-8aef2e9ff0ee" xmlns:ns4="9628d5c8-ac27-48c6-8474-b2056ac766a7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec8d6d6d26866640027cd316e7f688bc" ns3:_="" ns4:_="">
-    <xsd:import namespace="65819029-d4b2-4b56-9509-8aef2e9ff0ee"/>
-    <xsd:import namespace="9628d5c8-ac27-48c6-8474-b2056ac766a7"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns4:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns4:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns4:SharingHintHash" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="65819029-d4b2-4b56-9509-8aef2e9ff0ee" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSystemTags" ma:index="23" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="24" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="25" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9628d5c8-ac27-48c6-8474-b2056ac766a7" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="공유 대상" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="세부 정보 공유" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="SharingHintHash" ma:index="21" nillable="true" ma:displayName="힌트 해시 공유" ma:hidden="true" ma:internalName="SharingHintHash" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="콘텐츠 형식"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="제목"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41CBCFD5-C905-4678-B6A1-827A44CDC5C1}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="77.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="27.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>759</v>
+      </c>
+      <c r="B2" t="s">
+        <v>760</v>
+      </c>
+      <c r="C2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>762</v>
+      </c>
+      <c r="B3" t="s">
+        <v>763</v>
+      </c>
+      <c r="C3" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>765</v>
+      </c>
+      <c r="B4" t="s">
+        <v>766</v>
+      </c>
+      <c r="C4" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>768</v>
+      </c>
+      <c r="B5" t="s">
+        <v>769</v>
+      </c>
+      <c r="C5" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>771</v>
+      </c>
+      <c r="B6" t="s">
+        <v>772</v>
+      </c>
+      <c r="C6" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>774</v>
+      </c>
+      <c r="B7" t="s">
+        <v>775</v>
+      </c>
+      <c r="C7" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>777</v>
+      </c>
+      <c r="B8" t="s">
+        <v>778</v>
+      </c>
+      <c r="C8" t="s">
+        <v>779</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B74EF06B-97A3-49A2-8679-CB5C01347A69}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="65819029-d4b2-4b56-9509-8aef2e9ff0ee"/>
-    <ds:schemaRef ds:uri="9628d5c8-ac27-48c6-8474-b2056ac766a7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE159EF8-9C06-44FF-8B0E-D0B43B272602}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9A140A4-5755-4764-A556-4BC4E1ADF74C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="9628d5c8-ac27-48c6-8474-b2056ac766a7"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="65819029-d4b2-4b56-9509-8aef2e9ff0ee"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1380B039-30BB-435A-94A7-17EB2A0D6656}">
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="27.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>791</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/출산준비물_통합데이터.xlsx
+++ b/출산준비물_통합데이터.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\kongkong\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\진규어플\출산준비물어플\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BBBE05E-9B08-4B26-BAAF-254A162E7872}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4675FD0-6914-440D-B3ED-4B13F6513AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14415" activeTab="5" xr2:uid="{788198A8-8058-4D1A-8238-52DDCB41F95D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{02399CA1-EAED-454A-8052-CF66F4BDA800}"/>
   </bookViews>
   <sheets>
     <sheet name="출산가방 체크리스트" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,18 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2785,7 +2797,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02C8DBF0-3492-48AF-92E6-1D1FFA7C9414}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFB3206B-F8A7-496B-9718-D983D49B3A71}">
   <dimension ref="A1:K64"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -4760,12 +4772,12 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2770643F-111E-4A5D-8616-80859450F545}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{399BC4B1-00D0-41C6-B792-3DBE4B49DD9B}">
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -5467,7 +5479,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16BB3175-6AFC-40CB-A530-D2B9F1E5D321}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79330AF7-82AD-483A-A056-402503BD0997}">
   <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -6182,7 +6194,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667B3C2E-D9BA-4B3F-8DF3-50FFC17C28E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A0545E3-D5BC-4E8A-BF28-4B0E5B5E1939}">
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -6567,7 +6579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41CBCFD5-C905-4678-B6A1-827A44CDC5C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21E1C48-0AFE-4280-8099-C17C721D1BC6}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -6671,7 +6683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1380B039-30BB-435A-94A7-17EB2A0D6656}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CA8445D-D70A-40AA-AA35-BA1340A1CAA9}">
   <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>

--- a/출산준비물_통합데이터.xlsx
+++ b/출산준비물_통합데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\진규어플\출산준비물어플\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4675FD0-6914-440D-B3ED-4B13F6513AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B571C13F-E898-485E-A8DE-F4757ABB75A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{02399CA1-EAED-454A-8052-CF66F4BDA800}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{6BD4DBDD-FDA2-49C9-9FA2-7748851977C3}"/>
   </bookViews>
   <sheets>
     <sheet name="출산가방 체크리스트" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="806">
   <si>
     <t>ID</t>
   </si>
@@ -2315,10 +2315,52 @@
     <t>구분</t>
   </si>
   <si>
-    <t>추천 품목 ID 목록 (쉼표 구분)</t>
-  </si>
-  <si>
-    <t>설명 및 포함 품목 안내</t>
+    <t>추천품목ID1</t>
+  </si>
+  <si>
+    <t>품목명1</t>
+  </si>
+  <si>
+    <t>추천품목ID2</t>
+  </si>
+  <si>
+    <t>품목명2</t>
+  </si>
+  <si>
+    <t>추천품목ID3</t>
+  </si>
+  <si>
+    <t>품목명3</t>
+  </si>
+  <si>
+    <t>추천품목ID4</t>
+  </si>
+  <si>
+    <t>품목명4</t>
+  </si>
+  <si>
+    <t>추천품목ID5</t>
+  </si>
+  <si>
+    <t>품목명5</t>
+  </si>
+  <si>
+    <t>추천품목ID6</t>
+  </si>
+  <si>
+    <t>품목명6</t>
+  </si>
+  <si>
+    <t>추천품목ID7</t>
+  </si>
+  <si>
+    <t>품목명7</t>
+  </si>
+  <si>
+    <t>추천품목ID8</t>
+  </si>
+  <si>
+    <t>품목명8</t>
   </si>
   <si>
     <t>제왕절개</t>
@@ -2797,7 +2839,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFB3206B-F8A7-496B-9718-D983D49B3A71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21FF587-FEC6-413E-929C-9470D5D53914}">
   <dimension ref="A1:K64"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -4777,7 +4819,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{399BC4B1-00D0-41C6-B792-3DBE4B49DD9B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39EA8986-82CF-4065-B488-659BF03572F5}">
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -5479,7 +5521,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79330AF7-82AD-483A-A056-402503BD0997}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43136E99-29D0-4A68-B90F-6C25D8CE8256}">
   <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -6194,7 +6236,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A0545E3-D5BC-4E8A-BF28-4B0E5B5E1939}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F552A4D2-FB82-4063-862C-E2CD3384FC8D}">
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -6579,16 +6621,30 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21E1C48-0AFE-4280-8099-C17C721D1BC6}">
-  <dimension ref="A1:C8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A5589B3-69BE-4DFD-BEA2-5F5F989622B9}">
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="77.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="65.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27.95" customHeight="1">
+    <row r="1" spans="1:17" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>756</v>
       </c>
@@ -6598,82 +6654,124 @@
       <c r="C1" s="1" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>759</v>
+        <v>773</v>
       </c>
       <c r="B2" t="s">
-        <v>760</v>
+        <v>774</v>
       </c>
       <c r="C2" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>762</v>
+        <v>776</v>
       </c>
       <c r="B3" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="C3" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="B4" t="s">
-        <v>766</v>
+        <v>780</v>
       </c>
       <c r="C4" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="B5" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="C5" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>771</v>
+        <v>785</v>
       </c>
       <c r="B6" t="s">
-        <v>772</v>
+        <v>786</v>
       </c>
       <c r="C6" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
       <c r="B7" t="s">
-        <v>775</v>
+        <v>789</v>
       </c>
       <c r="C7" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>777</v>
+        <v>791</v>
       </c>
       <c r="B8" t="s">
-        <v>778</v>
+        <v>792</v>
       </c>
       <c r="C8" t="s">
-        <v>779</v>
+        <v>793</v>
       </c>
     </row>
   </sheetData>
@@ -6683,7 +6781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CA8445D-D70A-40AA-AA35-BA1340A1CAA9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC931DD-2A80-4CE3-BD8D-6EBD7186602B}">
   <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -6702,40 +6800,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>780</v>
+        <v>794</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>781</v>
+        <v>795</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>782</v>
+        <v>796</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>783</v>
+        <v>797</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>784</v>
+        <v>798</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>785</v>
+        <v>799</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>787</v>
+        <v>801</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>788</v>
+        <v>802</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>789</v>
+        <v>803</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>790</v>
+        <v>804</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>791</v>
+        <v>805</v>
       </c>
     </row>
   </sheetData>

--- a/출산준비물_통합데이터.xlsx
+++ b/출산준비물_통합데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\진규어플\출산준비물어플\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B571C13F-E898-485E-A8DE-F4757ABB75A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EB126D0-4C70-4786-815D-FDE69C05E852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{6BD4DBDD-FDA2-49C9-9FA2-7748851977C3}"/>
+    <workbookView xWindow="5340" yWindow="3030" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="5" xr2:uid="{529BC0EA-11C5-48AB-B786-C56AF9AD1BF9}"/>
   </bookViews>
   <sheets>
     <sheet name="출산가방 체크리스트" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="851">
   <si>
     <t>ID</t>
   </si>
@@ -566,7 +566,7 @@
     <t>개인 위생 &amp; 스킨케어</t>
   </si>
   <si>
-    <t>산모 세면도구 세트 (1세트)</t>
+    <t>산모 세면용품 세트 (1세트)</t>
   </si>
   <si>
     <t>(샴푸·바디워시·칫솔치약 등)</t>
@@ -644,6 +644,27 @@
     <t>콜라브 드라이샴푸 무향 저자극 파우더</t>
   </si>
   <si>
+    <t>m_sk_5</t>
+  </si>
+  <si>
+    <t>엄마용 영양제 (비타민, 철분 등)</t>
+  </si>
+  <si>
+    <t>1세트</t>
+  </si>
+  <si>
+    <t>(산후 회복·철분·비타민D·유산균)</t>
+  </si>
+  <si>
+    <t>솔가 철분 25mg 식물성 캡슐 (90일분)</t>
+  </si>
+  <si>
+    <t>닥터에디션 맘스 프로바이오틱스 유산균</t>
+  </si>
+  <si>
+    <t>종근당건강 락토핏 생유산균 맘스</t>
+  </si>
+  <si>
     <t>b_cloth_1</t>
   </si>
   <si>
@@ -866,6 +887,66 @@
     <t>말랑하니 유아 전동 손톱트리머</t>
   </si>
   <si>
+    <t>b_care_dday</t>
+  </si>
+  <si>
+    <t>디데이달력 (모자동실 성장 촬영용)</t>
+  </si>
+  <si>
+    <t>1개</t>
+  </si>
+  <si>
+    <t>(모자동실 기념사진 및 성장 기록)</t>
+  </si>
+  <si>
+    <t>말랑하니 아기 디데이달력 우드 스탠드형</t>
+  </si>
+  <si>
+    <t>달콤한기억 신생아 성장 디데이 캘린더</t>
+  </si>
+  <si>
+    <t>리틀포레스트 원목 감성 디데이달력</t>
+  </si>
+  <si>
+    <t>b_care_focusbook</t>
+  </si>
+  <si>
+    <t>초점책 (모자동실 흑백/컬러 초점책)</t>
+  </si>
+  <si>
+    <t>1권</t>
+  </si>
+  <si>
+    <t>(신생아 시각 발달 놀이용)</t>
+  </si>
+  <si>
+    <t>애플비 아기 초점책 병풍형 (흑백+컬러)</t>
+  </si>
+  <si>
+    <t>블루래빗 첫 두뇌계발 초점 플래시북</t>
+  </si>
+  <si>
+    <t>튤립사운드북 흑백 초점 병풍 세트</t>
+  </si>
+  <si>
+    <t>b_care_nightlight</t>
+  </si>
+  <si>
+    <t>수유등 (모자동실/조리원 밤 수유용)</t>
+  </si>
+  <si>
+    <t>(조도 조절 가능한 수유 무드등)</t>
+  </si>
+  <si>
+    <t>말랑하니 아기 무드등 LED 터치 수유등</t>
+  </si>
+  <si>
+    <t>바깃(Bagit) 모션인식 센서 터치 수유등</t>
+  </si>
+  <si>
+    <t>아르떼미데 톨로메오 미니 핀차 수유등</t>
+  </si>
+  <si>
     <t>b_safe_1</t>
   </si>
   <si>
@@ -1052,7 +1133,10 @@
     <t>g_dad_2</t>
   </si>
   <si>
-    <t>보호자 세면도구 &amp; 면도기</t>
+    <t>보호자(아빠) 세면용품 &amp; 면도기</t>
+  </si>
+  <si>
+    <t>(칫솔·치약·면도기·세안제)</t>
   </si>
   <si>
     <t>질레트 프로글라이드 플렉스볼 여행용 키트</t>
@@ -1085,10 +1169,10 @@
     <t>g_dad_4</t>
   </si>
   <si>
-    <t>보호자용 침구 / 이불 (필요시)</t>
-  </si>
-  <si>
-    <t>(보호자 침구 미제공 병원 확인)</t>
+    <t>아빠용 침구류 (이불·베개 / 필요시)</t>
+  </si>
+  <si>
+    <t>(병원 제공 여부 확인 필요)</t>
   </si>
   <si>
     <t>자주(JAJU) 접이식 극세사 캠핑 무릎담요</t>
@@ -1106,19 +1190,43 @@
     <t>생활 &amp; 편의 도구</t>
   </si>
   <si>
-    <t>구부러지는 꺾임 빨대 / 텀블러</t>
+    <t>텀블러 (보온/보냉용)</t>
+  </si>
+  <si>
+    <t>(손잡이형/빨대 호환)</t>
+  </si>
+  <si>
+    <t>스탠리 퀜처 H2.0 진공 텀블러</t>
+  </si>
+  <si>
+    <t>스탠리 퀜처 H2.0 플로우헤븐 진공 텀블러 887ml</t>
+  </si>
+  <si>
+    <t>글라스락 셰프토프 보온보냉 스트로우 텀블러</t>
+  </si>
+  <si>
+    <t>다이소 개별포장 주름 자바라 빨대 (100입)</t>
+  </si>
+  <si>
+    <t>g_life_straw</t>
+  </si>
+  <si>
+    <t>주름빨대 (구부러지는 꺾임 빨대)</t>
+  </si>
+  <si>
+    <t>1팩</t>
   </si>
   <si>
     <t>(누워서 수분 섭취 시 필수)</t>
   </si>
   <si>
-    <t>아띠빠스 실리콘 꺾임 빨대 텀블러 세트</t>
-  </si>
-  <si>
-    <t>글라스락 셰프토프 보온보냉 스트로우 텀블러</t>
-  </si>
-  <si>
-    <t>다이소 개별포장 주름 자바라 빨대 (100입)</t>
+    <t>다이소 개별포장 주름 자바라 꺾임빨대 (100입)</t>
+  </si>
+  <si>
+    <t>아띠빠스 실리콘 세척 가능 안심 꺾임 빨대</t>
+  </si>
+  <si>
+    <t>마더케이 일회용 꺾임 위생 빨대 60P</t>
   </si>
   <si>
     <t>g_life_2</t>
@@ -1136,25 +1244,43 @@
     <t>락앤락 메트로 머그 텀블러 600ml</t>
   </si>
   <si>
-    <t>g_life_3</t>
-  </si>
-  <si>
-    <t>스마트폰 충전기 &amp; 멀티탭 (3~5구)</t>
-  </si>
-  <si>
-    <t>(콘센트 거리 먼 경우 대비 2m 이상)</t>
+    <t>g_life_4</t>
+  </si>
+  <si>
+    <t>휴대폰 충전기 (긴 케이블 권장)</t>
+  </si>
+  <si>
+    <t>(침대 콘센트 거리 대비 2m 이상)</t>
   </si>
   <si>
     <t>벨킨 부스트업 초고속 3in1 멀티 충전기</t>
   </si>
   <si>
+    <t>신지모루 60W C타입 3미터 롱 케이블</t>
+  </si>
+  <si>
+    <t>삼성전자 45W 초고속 충전기 키트</t>
+  </si>
+  <si>
+    <t>g_life_multi</t>
+  </si>
+  <si>
+    <t>멀티탭 (3~5구, 긴 줄)</t>
+  </si>
+  <si>
+    <t>(산모 및 보호자 기기 동시 충전)</t>
+  </si>
+  <si>
+    <t>현대일렉트릭 서버탭 안전 멀티탭 4구 (3m)</t>
+  </si>
+  <si>
     <t>샤오미 멀티탭 3구 USB 3포트 (2m)</t>
   </si>
   <si>
-    <t>신지모루 60W C타입 3미터 롱 케이블</t>
-  </si>
-  <si>
-    <t>g_life_4</t>
+    <t>현대일렉트릭 고용량 개별 멀티탭 4구 (3m)</t>
+  </si>
+  <si>
+    <t>신성 개별 스위치 안전 멀티탭 5구</t>
   </si>
   <si>
     <t>휴대폰 거치대 (자바라/스탠드)</t>
@@ -1211,7 +1337,16 @@
     <t>g_life_7</t>
   </si>
   <si>
-    <t>손 소독제 &amp; 알코올 스왑</t>
+    <t>손세정제 (휴대용 손소독제)</t>
+  </si>
+  <si>
+    <t>(신생아 접촉 전 손 소독)</t>
+  </si>
+  <si>
+    <t>아이깨끗해 휴대용 거품형 손세정제</t>
+  </si>
+  <si>
+    <t>아이깨끗해 휴대용 거품형 손세정제 50ml</t>
   </si>
   <si>
     <t>유한양행 알코올 스왑 100매 개별포장</t>
@@ -1220,25 +1355,25 @@
     <t>데톨 오리지널 손소독 젤 200ml</t>
   </si>
   <si>
-    <t>닥터스에이 겔형 에탄올 손소독제</t>
-  </si>
-  <si>
-    <t>g_life_8</t>
-  </si>
-  <si>
-    <t>멀티 비타민 &amp; 철분제 &amp; 유산균</t>
-  </si>
-  <si>
-    <t>(산후 회복 및 수유 영양 보충)</t>
-  </si>
-  <si>
-    <t>솔가 철분 25mg 식물성 캡슐 (90일분)</t>
-  </si>
-  <si>
-    <t>닥터에디션 맘스 프로바이오틱스 유산균</t>
-  </si>
-  <si>
-    <t>종근당건강 락토핏 생유산균 베베/맘스</t>
+    <t>g_life_mask</t>
+  </si>
+  <si>
+    <t>일회용마스크 (KF94/비말 차단, 1팩)</t>
+  </si>
+  <si>
+    <t>(병원·조리원 방역 및 면회용)</t>
+  </si>
+  <si>
+    <t>아에르 KF94 피크 비말차단 마스크</t>
+  </si>
+  <si>
+    <t>아에르 KF94 피크 라이트 마스크 50매</t>
+  </si>
+  <si>
+    <t>크리넥스 데일리 비말차단 입체형 마스크 50매</t>
+  </si>
+  <si>
+    <t>웰킵스 뉴스마트 황사방역마스크 KF94 30매</t>
   </si>
   <si>
     <t>g_life_9</t>
@@ -2839,20 +2974,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21FF587-FEC6-413E-929C-9470D5D53914}">
-  <dimension ref="A1:K64"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF1F800-C143-404B-BD22-AF7A7E2C8C39}">
+  <dimension ref="A1:K70"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="42.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="45.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="43.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="43.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3802,16 +3937,22 @@
         <v>200</v>
       </c>
       <c r="B32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" t="s">
+        <v>173</v>
+      </c>
+      <c r="D32" t="s">
         <v>201</v>
       </c>
-      <c r="C32" t="s">
+      <c r="E32" t="s">
         <v>202</v>
       </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s">
         <v>203</v>
-      </c>
-      <c r="F32" t="s">
-        <v>64</v>
       </c>
       <c r="H32" t="s">
         <v>204</v>
@@ -3831,193 +3972,190 @@
         <v>207</v>
       </c>
       <c r="B33" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C33" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D33" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F33" t="s">
         <v>64</v>
       </c>
       <c r="H33" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I33" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J33" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K33" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B34" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C34" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D34" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F34" t="s">
         <v>64</v>
       </c>
-      <c r="G34" t="s">
-        <v>215</v>
-      </c>
       <c r="H34" t="s">
         <v>216</v>
       </c>
       <c r="I34" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J34" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K34" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B35" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C35" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D35" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F35" t="s">
         <v>64</v>
       </c>
       <c r="G35" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J35" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B36" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C36" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D36" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F36" t="s">
         <v>64</v>
       </c>
+      <c r="G36" t="s">
+        <v>228</v>
+      </c>
       <c r="H36" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I36" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J36" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K36" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B37" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C37" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D37" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F37" t="s">
         <v>64</v>
       </c>
       <c r="H37" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I37" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J37" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K37" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B38" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C38" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="D38" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" t="s">
-        <v>238</v>
+        <v>64</v>
       </c>
       <c r="H38" t="s">
         <v>239</v>
       </c>
       <c r="I38" t="s">
+        <v>239</v>
+      </c>
+      <c r="J38" t="s">
         <v>240</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
         <v>241</v>
-      </c>
-      <c r="K38" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
+        <v>242</v>
+      </c>
+      <c r="B39" t="s">
+        <v>208</v>
+      </c>
+      <c r="C39" t="s">
         <v>243</v>
-      </c>
-      <c r="B39" t="s">
-        <v>201</v>
-      </c>
-      <c r="C39" t="s">
-        <v>236</v>
       </c>
       <c r="D39" t="s">
         <v>244</v>
@@ -4046,10 +4184,10 @@
         <v>250</v>
       </c>
       <c r="B40" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C40" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D40" t="s">
         <v>251</v>
@@ -4057,69 +4195,69 @@
       <c r="F40" t="s">
         <v>15</v>
       </c>
+      <c r="G40" t="s">
+        <v>252</v>
+      </c>
       <c r="H40" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I40" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J40" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K40" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B41" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C41" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D41" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F41" t="s">
         <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I41" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K41" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B42" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C42" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D42" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F42" t="s">
-        <v>167</v>
-      </c>
-      <c r="G42" t="s">
-        <v>263</v>
+        <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I42" t="s">
         <v>265</v>
@@ -4136,10 +4274,10 @@
         <v>268</v>
       </c>
       <c r="B43" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C43" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D43" t="s">
         <v>269</v>
@@ -4147,150 +4285,162 @@
       <c r="F43" t="s">
         <v>167</v>
       </c>
+      <c r="G43" t="s">
+        <v>270</v>
+      </c>
       <c r="H43" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I43" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J43" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K43" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B44" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C44" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="D44" t="s">
         <v>276</v>
       </c>
       <c r="F44" t="s">
-        <v>64</v>
-      </c>
-      <c r="G44" t="s">
+        <v>167</v>
+      </c>
+      <c r="H44" t="s">
         <v>277</v>
       </c>
-      <c r="H44" t="s">
+      <c r="I44" t="s">
         <v>278</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>279</v>
       </c>
-      <c r="J44" t="s">
+      <c r="K44" t="s">
         <v>280</v>
-      </c>
-      <c r="K44" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
+        <v>281</v>
+      </c>
+      <c r="B45" t="s">
+        <v>208</v>
+      </c>
+      <c r="C45" t="s">
+        <v>243</v>
+      </c>
+      <c r="D45" t="s">
         <v>282</v>
       </c>
-      <c r="B45" t="s">
-        <v>201</v>
-      </c>
-      <c r="C45" t="s">
-        <v>275</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>283</v>
       </c>
       <c r="F45" t="s">
-        <v>64</v>
+        <v>167</v>
+      </c>
+      <c r="G45" t="s">
+        <v>284</v>
       </c>
       <c r="H45" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I45" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J45" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K45" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B46" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C46" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="D46" t="s">
-        <v>288</v>
+        <v>289</v>
+      </c>
+      <c r="E46" t="s">
+        <v>290</v>
       </c>
       <c r="F46" t="s">
         <v>167</v>
       </c>
       <c r="G46" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H46" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I46" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J46" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K46" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B47" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C47" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="D47" t="s">
-        <v>294</v>
+        <v>296</v>
+      </c>
+      <c r="E47" t="s">
+        <v>283</v>
       </c>
       <c r="F47" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H47" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I47" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J47" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K47" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B48" t="s">
-        <v>301</v>
+        <v>208</v>
       </c>
       <c r="C48" t="s">
         <v>302</v>
@@ -4299,7 +4449,7 @@
         <v>303</v>
       </c>
       <c r="F48" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="G48" t="s">
         <v>304</v>
@@ -4322,7 +4472,7 @@
         <v>309</v>
       </c>
       <c r="B49" t="s">
-        <v>301</v>
+        <v>208</v>
       </c>
       <c r="C49" t="s">
         <v>302</v>
@@ -4331,94 +4481,91 @@
         <v>310</v>
       </c>
       <c r="F49" t="s">
-        <v>15</v>
-      </c>
-      <c r="G49" t="s">
+        <v>64</v>
+      </c>
+      <c r="H49" t="s">
         <v>311</v>
       </c>
-      <c r="H49" t="s">
+      <c r="I49" t="s">
+        <v>311</v>
+      </c>
+      <c r="J49" t="s">
         <v>312</v>
       </c>
-      <c r="I49" t="s">
-        <v>312</v>
-      </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>313</v>
-      </c>
-      <c r="K49" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B50" t="s">
-        <v>301</v>
+        <v>208</v>
       </c>
       <c r="C50" t="s">
         <v>302</v>
       </c>
       <c r="D50" t="s">
+        <v>315</v>
+      </c>
+      <c r="F50" t="s">
+        <v>167</v>
+      </c>
+      <c r="G50" t="s">
         <v>316</v>
       </c>
-      <c r="F50" t="s">
-        <v>15</v>
-      </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>317</v>
       </c>
-      <c r="H50" t="s">
+      <c r="I50" t="s">
+        <v>317</v>
+      </c>
+      <c r="J50" t="s">
         <v>318</v>
       </c>
-      <c r="I50" t="s">
+      <c r="K50" t="s">
         <v>319</v>
-      </c>
-      <c r="J50" t="s">
-        <v>320</v>
-      </c>
-      <c r="K50" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B51" t="s">
-        <v>301</v>
+        <v>208</v>
       </c>
       <c r="C51" t="s">
         <v>302</v>
       </c>
       <c r="D51" t="s">
+        <v>321</v>
+      </c>
+      <c r="F51" t="s">
+        <v>64</v>
+      </c>
+      <c r="G51" t="s">
+        <v>322</v>
+      </c>
+      <c r="H51" t="s">
         <v>323</v>
       </c>
-      <c r="F51" t="s">
-        <v>167</v>
-      </c>
-      <c r="G51" t="s">
+      <c r="I51" t="s">
         <v>324</v>
       </c>
-      <c r="H51" t="s">
+      <c r="J51" t="s">
         <v>325</v>
       </c>
-      <c r="I51" t="s">
-        <v>325</v>
-      </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>326</v>
-      </c>
-      <c r="K51" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
+        <v>327</v>
+      </c>
+      <c r="B52" t="s">
         <v>328</v>
-      </c>
-      <c r="B52" t="s">
-        <v>301</v>
       </c>
       <c r="C52" t="s">
         <v>329</v>
@@ -4429,386 +4576,593 @@
       <c r="F52" t="s">
         <v>15</v>
       </c>
+      <c r="G52" t="s">
+        <v>331</v>
+      </c>
       <c r="H52" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I52" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J52" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K52" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B53" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C53" t="s">
         <v>329</v>
       </c>
       <c r="D53" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F53" t="s">
         <v>15</v>
       </c>
+      <c r="G53" t="s">
+        <v>338</v>
+      </c>
       <c r="H53" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I53" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J53" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K53" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B54" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C54" t="s">
         <v>329</v>
       </c>
       <c r="D54" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F54" t="s">
         <v>15</v>
       </c>
+      <c r="G54" t="s">
+        <v>344</v>
+      </c>
       <c r="H54" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="I54" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="J54" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K54" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B55" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C55" t="s">
         <v>329</v>
       </c>
       <c r="D55" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F55" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="G55" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="H55" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="I55" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J55" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="K55" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B56" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C56" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D56" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F56" t="s">
         <v>15</v>
       </c>
-      <c r="G56" t="s">
-        <v>355</v>
-      </c>
       <c r="H56" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I56" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J56" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="K56" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B57" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C57" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D57" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F57" t="s">
         <v>15</v>
       </c>
+      <c r="G57" t="s">
+        <v>364</v>
+      </c>
       <c r="H57" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="I57" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="J57" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="K57" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B58" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C58" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D58" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F58" t="s">
         <v>15</v>
       </c>
-      <c r="G58" t="s">
-        <v>366</v>
-      </c>
       <c r="H58" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="I58" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="J58" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="K58" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B59" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C59" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D59" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F59" t="s">
-        <v>15</v>
+        <v>194</v>
       </c>
       <c r="G59" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="H59" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="I59" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="J59" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K59" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B60" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C60" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="D60" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F60" t="s">
         <v>15</v>
       </c>
+      <c r="G60" t="s">
+        <v>383</v>
+      </c>
       <c r="H60" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="I60" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="J60" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="K60" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B61" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C61" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="D61" t="s">
-        <v>383</v>
+        <v>389</v>
+      </c>
+      <c r="E61" t="s">
+        <v>390</v>
       </c>
       <c r="F61" t="s">
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="H61" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="I61" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="J61" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="K61" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B62" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C62" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="D62" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="F62" t="s">
         <v>15</v>
       </c>
       <c r="H62" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="I62" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="J62" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="K62" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="B63" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C63" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="D63" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="F63" t="s">
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="H63" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="I63" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="J63" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="K63" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="B64" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C64" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="D64" t="s">
-        <v>400</v>
+        <v>407</v>
+      </c>
+      <c r="E64" t="s">
+        <v>283</v>
       </c>
       <c r="F64" t="s">
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="H64" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="I64" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="J64" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="K64" t="s">
-        <v>404</v>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" t="s">
+        <v>400</v>
+      </c>
+      <c r="B65" t="s">
+        <v>328</v>
+      </c>
+      <c r="C65" t="s">
+        <v>381</v>
+      </c>
+      <c r="D65" t="s">
+        <v>413</v>
+      </c>
+      <c r="F65" t="s">
+        <v>15</v>
+      </c>
+      <c r="G65" t="s">
+        <v>414</v>
+      </c>
+      <c r="H65" t="s">
+        <v>415</v>
+      </c>
+      <c r="I65" t="s">
+        <v>415</v>
+      </c>
+      <c r="J65" t="s">
+        <v>416</v>
+      </c>
+      <c r="K65" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" t="s">
+        <v>418</v>
+      </c>
+      <c r="B66" t="s">
+        <v>328</v>
+      </c>
+      <c r="C66" t="s">
+        <v>381</v>
+      </c>
+      <c r="D66" t="s">
+        <v>419</v>
+      </c>
+      <c r="F66" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" t="s">
+        <v>420</v>
+      </c>
+      <c r="I66" t="s">
+        <v>421</v>
+      </c>
+      <c r="J66" t="s">
+        <v>422</v>
+      </c>
+      <c r="K66" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" t="s">
+        <v>424</v>
+      </c>
+      <c r="B67" t="s">
+        <v>328</v>
+      </c>
+      <c r="C67" t="s">
+        <v>381</v>
+      </c>
+      <c r="D67" t="s">
+        <v>425</v>
+      </c>
+      <c r="F67" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s">
+        <v>426</v>
+      </c>
+      <c r="H67" t="s">
+        <v>427</v>
+      </c>
+      <c r="I67" t="s">
+        <v>427</v>
+      </c>
+      <c r="J67" t="s">
+        <v>428</v>
+      </c>
+      <c r="K67" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" t="s">
+        <v>430</v>
+      </c>
+      <c r="B68" t="s">
+        <v>328</v>
+      </c>
+      <c r="C68" t="s">
+        <v>381</v>
+      </c>
+      <c r="D68" t="s">
+        <v>431</v>
+      </c>
+      <c r="F68" t="s">
+        <v>15</v>
+      </c>
+      <c r="G68" t="s">
+        <v>432</v>
+      </c>
+      <c r="H68" t="s">
+        <v>433</v>
+      </c>
+      <c r="I68" t="s">
+        <v>434</v>
+      </c>
+      <c r="J68" t="s">
+        <v>435</v>
+      </c>
+      <c r="K68" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" t="s">
+        <v>437</v>
+      </c>
+      <c r="B69" t="s">
+        <v>328</v>
+      </c>
+      <c r="C69" t="s">
+        <v>381</v>
+      </c>
+      <c r="D69" t="s">
+        <v>438</v>
+      </c>
+      <c r="E69" t="s">
+        <v>390</v>
+      </c>
+      <c r="F69" t="s">
+        <v>15</v>
+      </c>
+      <c r="G69" t="s">
+        <v>439</v>
+      </c>
+      <c r="H69" t="s">
+        <v>440</v>
+      </c>
+      <c r="I69" t="s">
+        <v>441</v>
+      </c>
+      <c r="J69" t="s">
+        <v>442</v>
+      </c>
+      <c r="K69" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" t="s">
+        <v>444</v>
+      </c>
+      <c r="B70" t="s">
+        <v>328</v>
+      </c>
+      <c r="C70" t="s">
+        <v>381</v>
+      </c>
+      <c r="D70" t="s">
+        <v>445</v>
+      </c>
+      <c r="F70" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70" t="s">
+        <v>446</v>
+      </c>
+      <c r="H70" t="s">
+        <v>447</v>
+      </c>
+      <c r="I70" t="s">
+        <v>447</v>
+      </c>
+      <c r="J70" t="s">
+        <v>448</v>
+      </c>
+      <c r="K70" t="s">
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -4819,7 +5173,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39EA8986-82CF-4065-B488-659BF03572F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944AE346-DC81-4D40-8AA3-E0FF73D9CB6F}">
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -4841,22 +5195,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>405</v>
+        <v>450</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>406</v>
+        <v>451</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>407</v>
+        <v>452</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>408</v>
+        <v>453</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>409</v>
+        <v>454</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>410</v>
+        <v>455</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
@@ -4873,645 +5227,645 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>411</v>
+        <v>456</v>
       </c>
       <c r="B2" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="C2" t="s">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="D2" t="s">
-        <v>414</v>
+        <v>459</v>
       </c>
       <c r="E2" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="F2" t="s">
-        <v>416</v>
+        <v>461</v>
       </c>
       <c r="G2" t="s">
-        <v>417</v>
+        <v>462</v>
       </c>
       <c r="H2" t="s">
-        <v>418</v>
+        <v>463</v>
       </c>
       <c r="I2" t="s">
-        <v>418</v>
+        <v>463</v>
       </c>
       <c r="J2" t="s">
-        <v>419</v>
+        <v>464</v>
       </c>
       <c r="K2" t="s">
-        <v>420</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>421</v>
+        <v>466</v>
       </c>
       <c r="B3" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="C3" t="s">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="D3" t="s">
-        <v>422</v>
+        <v>467</v>
       </c>
       <c r="E3" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="F3" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H3" t="s">
-        <v>424</v>
+        <v>469</v>
       </c>
       <c r="I3" t="s">
-        <v>424</v>
+        <v>469</v>
       </c>
       <c r="J3" t="s">
-        <v>425</v>
+        <v>470</v>
       </c>
       <c r="K3" t="s">
-        <v>426</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>427</v>
+        <v>472</v>
       </c>
       <c r="B4" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="C4" t="s">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="D4" t="s">
-        <v>428</v>
+        <v>473</v>
       </c>
       <c r="E4" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="F4" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H4" t="s">
-        <v>429</v>
+        <v>474</v>
       </c>
       <c r="I4" t="s">
-        <v>429</v>
+        <v>474</v>
       </c>
       <c r="J4" t="s">
-        <v>430</v>
+        <v>475</v>
       </c>
       <c r="K4" t="s">
-        <v>431</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>432</v>
+        <v>477</v>
       </c>
       <c r="B5" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="C5" t="s">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="D5" t="s">
-        <v>433</v>
+        <v>478</v>
       </c>
       <c r="E5" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="F5" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H5" t="s">
-        <v>434</v>
+        <v>479</v>
       </c>
       <c r="I5" t="s">
-        <v>434</v>
+        <v>479</v>
       </c>
       <c r="J5" t="s">
-        <v>435</v>
+        <v>480</v>
       </c>
       <c r="K5" t="s">
-        <v>436</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>437</v>
+        <v>482</v>
       </c>
       <c r="B6" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="C6" t="s">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="D6" t="s">
-        <v>438</v>
+        <v>483</v>
       </c>
       <c r="E6" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="F6" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H6" t="s">
-        <v>439</v>
+        <v>484</v>
       </c>
       <c r="I6" t="s">
-        <v>439</v>
+        <v>484</v>
       </c>
       <c r="J6" t="s">
-        <v>440</v>
+        <v>485</v>
       </c>
       <c r="K6" t="s">
-        <v>441</v>
+        <v>486</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>442</v>
+        <v>487</v>
       </c>
       <c r="B7" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="C7" t="s">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="D7" t="s">
-        <v>443</v>
+        <v>488</v>
       </c>
       <c r="E7" t="s">
-        <v>444</v>
+        <v>489</v>
       </c>
       <c r="F7" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H7" t="s">
-        <v>445</v>
+        <v>490</v>
       </c>
       <c r="I7" t="s">
-        <v>445</v>
+        <v>490</v>
       </c>
       <c r="J7" t="s">
-        <v>446</v>
+        <v>491</v>
       </c>
       <c r="K7" t="s">
-        <v>447</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>448</v>
+        <v>493</v>
       </c>
       <c r="B8" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="C8" t="s">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="D8" t="s">
-        <v>449</v>
+        <v>494</v>
       </c>
       <c r="E8" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="F8" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H8" t="s">
-        <v>450</v>
+        <v>495</v>
       </c>
       <c r="I8" t="s">
-        <v>451</v>
+        <v>496</v>
       </c>
       <c r="J8" t="s">
-        <v>452</v>
+        <v>497</v>
       </c>
       <c r="K8" t="s">
-        <v>453</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>454</v>
+        <v>499</v>
       </c>
       <c r="B9" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="C9" t="s">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="D9" t="s">
-        <v>455</v>
+        <v>500</v>
       </c>
       <c r="E9" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="F9" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H9" t="s">
-        <v>457</v>
+        <v>502</v>
       </c>
       <c r="I9" t="s">
-        <v>458</v>
+        <v>503</v>
       </c>
       <c r="J9" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="K9" t="s">
-        <v>460</v>
+        <v>505</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="B10" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="C10" t="s">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="D10" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="E10" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="F10" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H10" t="s">
-        <v>464</v>
+        <v>509</v>
       </c>
       <c r="I10" t="s">
-        <v>465</v>
+        <v>510</v>
       </c>
       <c r="J10" t="s">
-        <v>466</v>
+        <v>511</v>
       </c>
       <c r="K10" t="s">
-        <v>467</v>
+        <v>512</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>468</v>
+        <v>513</v>
       </c>
       <c r="B11" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="C11" t="s">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="D11" t="s">
-        <v>469</v>
+        <v>514</v>
       </c>
       <c r="E11" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="F11" t="s">
-        <v>416</v>
+        <v>461</v>
       </c>
       <c r="H11" t="s">
-        <v>470</v>
+        <v>515</v>
       </c>
       <c r="I11" t="s">
-        <v>471</v>
+        <v>516</v>
       </c>
       <c r="J11" t="s">
-        <v>472</v>
+        <v>517</v>
       </c>
       <c r="K11" t="s">
-        <v>473</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>474</v>
+        <v>519</v>
       </c>
       <c r="B12" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="C12" t="s">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="D12" t="s">
-        <v>475</v>
+        <v>520</v>
       </c>
       <c r="E12" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="F12" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H12" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="I12" t="s">
-        <v>476</v>
+        <v>521</v>
       </c>
       <c r="J12" t="s">
-        <v>477</v>
+        <v>522</v>
       </c>
       <c r="K12" t="s">
-        <v>478</v>
+        <v>523</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>479</v>
+        <v>524</v>
       </c>
       <c r="B13" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="C13" t="s">
-        <v>481</v>
+        <v>526</v>
       </c>
       <c r="D13" t="s">
-        <v>482</v>
+        <v>527</v>
       </c>
       <c r="E13" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="F13" t="s">
-        <v>416</v>
+        <v>461</v>
       </c>
       <c r="H13" t="s">
-        <v>483</v>
+        <v>528</v>
       </c>
       <c r="I13" t="s">
-        <v>484</v>
+        <v>529</v>
       </c>
       <c r="J13" t="s">
-        <v>485</v>
+        <v>530</v>
       </c>
       <c r="K13" t="s">
-        <v>486</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>487</v>
+        <v>532</v>
       </c>
       <c r="B14" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="C14" t="s">
-        <v>481</v>
+        <v>526</v>
       </c>
       <c r="D14" t="s">
-        <v>488</v>
+        <v>533</v>
       </c>
       <c r="E14" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="F14" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H14" t="s">
-        <v>489</v>
+        <v>534</v>
       </c>
       <c r="I14" t="s">
-        <v>489</v>
+        <v>534</v>
       </c>
       <c r="J14" t="s">
-        <v>490</v>
+        <v>535</v>
       </c>
       <c r="K14" t="s">
-        <v>491</v>
+        <v>536</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>492</v>
+        <v>537</v>
       </c>
       <c r="B15" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="C15" t="s">
-        <v>481</v>
+        <v>526</v>
       </c>
       <c r="D15" t="s">
-        <v>493</v>
+        <v>538</v>
       </c>
       <c r="E15" t="s">
-        <v>444</v>
+        <v>489</v>
       </c>
       <c r="F15" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H15" t="s">
-        <v>494</v>
+        <v>539</v>
       </c>
       <c r="I15" t="s">
-        <v>495</v>
+        <v>540</v>
       </c>
       <c r="J15" t="s">
-        <v>496</v>
+        <v>541</v>
       </c>
       <c r="K15" t="s">
-        <v>497</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>498</v>
+        <v>543</v>
       </c>
       <c r="B16" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="C16" t="s">
-        <v>481</v>
+        <v>526</v>
       </c>
       <c r="D16" t="s">
-        <v>499</v>
+        <v>544</v>
       </c>
       <c r="E16" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="F16" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H16" t="s">
-        <v>500</v>
+        <v>545</v>
       </c>
       <c r="I16" t="s">
-        <v>501</v>
+        <v>546</v>
       </c>
       <c r="J16" t="s">
-        <v>502</v>
+        <v>547</v>
       </c>
       <c r="K16" t="s">
-        <v>503</v>
+        <v>548</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>504</v>
+        <v>549</v>
       </c>
       <c r="B17" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="C17" t="s">
-        <v>481</v>
+        <v>526</v>
       </c>
       <c r="D17" t="s">
-        <v>505</v>
+        <v>550</v>
       </c>
       <c r="E17" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="F17" t="s">
-        <v>416</v>
+        <v>461</v>
       </c>
       <c r="H17" t="s">
-        <v>506</v>
+        <v>551</v>
       </c>
       <c r="I17" t="s">
-        <v>507</v>
+        <v>552</v>
       </c>
       <c r="J17" t="s">
-        <v>508</v>
+        <v>553</v>
       </c>
       <c r="K17" t="s">
-        <v>509</v>
+        <v>554</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>510</v>
+        <v>555</v>
       </c>
       <c r="B18" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="C18" t="s">
-        <v>481</v>
+        <v>526</v>
       </c>
       <c r="D18" t="s">
-        <v>511</v>
+        <v>556</v>
       </c>
       <c r="E18" t="s">
-        <v>444</v>
+        <v>489</v>
       </c>
       <c r="F18" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H18" t="s">
-        <v>512</v>
+        <v>557</v>
       </c>
       <c r="I18" t="s">
-        <v>513</v>
+        <v>558</v>
       </c>
       <c r="J18" t="s">
-        <v>514</v>
+        <v>559</v>
       </c>
       <c r="K18" t="s">
-        <v>515</v>
+        <v>560</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>516</v>
+        <v>561</v>
       </c>
       <c r="B19" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="C19" t="s">
-        <v>517</v>
+        <v>562</v>
       </c>
       <c r="D19" t="s">
-        <v>518</v>
+        <v>563</v>
       </c>
       <c r="E19" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="F19" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H19" t="s">
-        <v>519</v>
+        <v>564</v>
       </c>
       <c r="I19" t="s">
-        <v>519</v>
+        <v>564</v>
       </c>
       <c r="J19" t="s">
-        <v>520</v>
+        <v>565</v>
       </c>
       <c r="K19" t="s">
-        <v>521</v>
+        <v>566</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>522</v>
+        <v>567</v>
       </c>
       <c r="B20" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="C20" t="s">
-        <v>517</v>
+        <v>562</v>
       </c>
       <c r="D20" t="s">
-        <v>523</v>
+        <v>568</v>
       </c>
       <c r="E20" t="s">
-        <v>444</v>
+        <v>489</v>
       </c>
       <c r="F20" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H20" t="s">
-        <v>524</v>
+        <v>569</v>
       </c>
       <c r="I20" t="s">
-        <v>525</v>
+        <v>570</v>
       </c>
       <c r="J20" t="s">
-        <v>526</v>
+        <v>571</v>
       </c>
       <c r="K20" t="s">
-        <v>527</v>
+        <v>572</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>528</v>
+        <v>573</v>
       </c>
       <c r="B21" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="C21" t="s">
-        <v>517</v>
+        <v>562</v>
       </c>
       <c r="D21" t="s">
-        <v>529</v>
+        <v>574</v>
       </c>
       <c r="E21" t="s">
-        <v>444</v>
+        <v>489</v>
       </c>
       <c r="F21" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="H21" t="s">
-        <v>530</v>
+        <v>575</v>
       </c>
       <c r="I21" t="s">
-        <v>531</v>
+        <v>576</v>
       </c>
       <c r="J21" t="s">
-        <v>532</v>
+        <v>577</v>
       </c>
       <c r="K21" t="s">
-        <v>533</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
@@ -5521,7 +5875,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43136E99-29D0-4A68-B90F-6C25D8CE8256}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F865740-48E8-4E73-B837-DAD528B3468E}">
   <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -5537,696 +5891,696 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>534</v>
+        <v>579</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>535</v>
+        <v>580</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>536</v>
+        <v>581</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>537</v>
+        <v>582</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>538</v>
+        <v>583</v>
       </c>
       <c r="B2" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C2" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D2" t="s">
-        <v>541</v>
+        <v>586</v>
       </c>
       <c r="E2" t="s">
-        <v>542</v>
+        <v>587</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>543</v>
+        <v>588</v>
       </c>
       <c r="B3" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C3" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D3" t="s">
-        <v>544</v>
+        <v>589</v>
       </c>
       <c r="E3" t="s">
-        <v>545</v>
+        <v>590</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>546</v>
+        <v>591</v>
       </c>
       <c r="B4" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C4" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D4" t="s">
-        <v>547</v>
+        <v>592</v>
       </c>
       <c r="E4" t="s">
-        <v>548</v>
+        <v>593</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>549</v>
+        <v>594</v>
       </c>
       <c r="B5" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C5" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D5" t="s">
-        <v>550</v>
+        <v>595</v>
       </c>
       <c r="E5" t="s">
-        <v>551</v>
+        <v>596</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>552</v>
+        <v>597</v>
       </c>
       <c r="B6" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C6" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D6" t="s">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="E6" t="s">
-        <v>554</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>555</v>
+        <v>600</v>
       </c>
       <c r="B7" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C7" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D7" t="s">
-        <v>556</v>
+        <v>601</v>
       </c>
       <c r="E7" t="s">
-        <v>557</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>558</v>
+        <v>603</v>
       </c>
       <c r="B8" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C8" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D8" t="s">
-        <v>559</v>
+        <v>604</v>
       </c>
       <c r="E8" t="s">
-        <v>560</v>
+        <v>605</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>561</v>
+        <v>606</v>
       </c>
       <c r="B9" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C9" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D9" t="s">
-        <v>562</v>
+        <v>607</v>
       </c>
       <c r="E9" t="s">
-        <v>563</v>
+        <v>608</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>564</v>
+        <v>609</v>
       </c>
       <c r="B10" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C10" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D10" t="s">
-        <v>565</v>
+        <v>610</v>
       </c>
       <c r="E10" t="s">
-        <v>566</v>
+        <v>611</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>567</v>
+        <v>612</v>
       </c>
       <c r="B11" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C11" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D11" t="s">
-        <v>568</v>
+        <v>613</v>
       </c>
       <c r="E11" t="s">
-        <v>569</v>
+        <v>614</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>570</v>
+        <v>615</v>
       </c>
       <c r="B12" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C12" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D12" t="s">
-        <v>571</v>
+        <v>616</v>
       </c>
       <c r="E12" t="s">
-        <v>572</v>
+        <v>617</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>573</v>
+        <v>618</v>
       </c>
       <c r="B13" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C13" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D13" t="s">
-        <v>574</v>
+        <v>619</v>
       </c>
       <c r="E13" t="s">
-        <v>575</v>
+        <v>620</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>576</v>
+        <v>621</v>
       </c>
       <c r="B14" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C14" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D14" t="s">
-        <v>577</v>
+        <v>622</v>
       </c>
       <c r="E14" t="s">
-        <v>578</v>
+        <v>623</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>579</v>
+        <v>624</v>
       </c>
       <c r="B15" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C15" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D15" t="s">
-        <v>580</v>
+        <v>625</v>
       </c>
       <c r="E15" t="s">
-        <v>581</v>
+        <v>626</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>582</v>
+        <v>627</v>
       </c>
       <c r="B16" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C16" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D16" t="s">
-        <v>583</v>
+        <v>628</v>
       </c>
       <c r="E16" t="s">
-        <v>584</v>
+        <v>629</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
+        <v>630</v>
+      </c>
+      <c r="B17" t="s">
+        <v>584</v>
+      </c>
+      <c r="C17" t="s">
         <v>585</v>
       </c>
-      <c r="B17" t="s">
-        <v>539</v>
-      </c>
-      <c r="C17" t="s">
-        <v>540</v>
-      </c>
       <c r="D17" t="s">
-        <v>586</v>
+        <v>631</v>
       </c>
       <c r="E17" t="s">
-        <v>587</v>
+        <v>632</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>588</v>
+        <v>633</v>
       </c>
       <c r="B18" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C18" t="s">
-        <v>589</v>
+        <v>634</v>
       </c>
       <c r="D18" t="s">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="E18" t="s">
-        <v>591</v>
+        <v>636</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>592</v>
+        <v>637</v>
       </c>
       <c r="B19" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C19" t="s">
-        <v>589</v>
+        <v>634</v>
       </c>
       <c r="D19" t="s">
-        <v>593</v>
+        <v>638</v>
       </c>
       <c r="E19" t="s">
-        <v>594</v>
+        <v>639</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>595</v>
+        <v>640</v>
       </c>
       <c r="B20" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C20" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D20" t="s">
-        <v>596</v>
+        <v>641</v>
       </c>
       <c r="E20" t="s">
-        <v>597</v>
+        <v>642</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>598</v>
+        <v>643</v>
       </c>
       <c r="B21" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C21" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D21" t="s">
-        <v>599</v>
+        <v>644</v>
       </c>
       <c r="E21" t="s">
-        <v>600</v>
+        <v>645</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>601</v>
+        <v>646</v>
       </c>
       <c r="B22" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C22" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D22" t="s">
-        <v>602</v>
+        <v>647</v>
       </c>
       <c r="E22" t="s">
-        <v>603</v>
+        <v>648</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>604</v>
+        <v>649</v>
       </c>
       <c r="B23" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C23" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D23" t="s">
-        <v>605</v>
+        <v>650</v>
       </c>
       <c r="E23" t="s">
-        <v>606</v>
+        <v>651</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>607</v>
+        <v>652</v>
       </c>
       <c r="B24" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C24" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D24" t="s">
-        <v>608</v>
+        <v>653</v>
       </c>
       <c r="E24" t="s">
-        <v>609</v>
+        <v>654</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>610</v>
+        <v>655</v>
       </c>
       <c r="B25" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C25" t="s">
-        <v>611</v>
+        <v>656</v>
       </c>
       <c r="D25" t="s">
-        <v>612</v>
+        <v>657</v>
       </c>
       <c r="E25" t="s">
-        <v>613</v>
+        <v>658</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>614</v>
+        <v>659</v>
       </c>
       <c r="B26" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C26" t="s">
-        <v>589</v>
+        <v>634</v>
       </c>
       <c r="D26" t="s">
-        <v>615</v>
+        <v>660</v>
       </c>
       <c r="E26" t="s">
-        <v>616</v>
+        <v>661</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>617</v>
+        <v>662</v>
       </c>
       <c r="B27" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C27" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D27" t="s">
-        <v>618</v>
+        <v>663</v>
       </c>
       <c r="E27" t="s">
-        <v>619</v>
+        <v>664</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>620</v>
+        <v>665</v>
       </c>
       <c r="B28" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C28" t="s">
-        <v>589</v>
+        <v>634</v>
       </c>
       <c r="D28" t="s">
-        <v>621</v>
+        <v>666</v>
       </c>
       <c r="E28" t="s">
-        <v>622</v>
+        <v>667</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>623</v>
+        <v>668</v>
       </c>
       <c r="B29" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C29" t="s">
-        <v>611</v>
+        <v>656</v>
       </c>
       <c r="D29" t="s">
-        <v>624</v>
+        <v>669</v>
       </c>
       <c r="E29" t="s">
-        <v>625</v>
+        <v>670</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>626</v>
+        <v>671</v>
       </c>
       <c r="B30" t="s">
-        <v>627</v>
+        <v>672</v>
       </c>
       <c r="C30" t="s">
-        <v>589</v>
+        <v>634</v>
       </c>
       <c r="D30" t="s">
-        <v>628</v>
+        <v>673</v>
       </c>
       <c r="E30" t="s">
-        <v>629</v>
+        <v>674</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>630</v>
+        <v>675</v>
       </c>
       <c r="B31" t="s">
-        <v>627</v>
+        <v>672</v>
       </c>
       <c r="C31" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D31" t="s">
-        <v>631</v>
+        <v>676</v>
       </c>
       <c r="E31" t="s">
-        <v>632</v>
+        <v>677</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>633</v>
+        <v>678</v>
       </c>
       <c r="B32" t="s">
-        <v>627</v>
+        <v>672</v>
       </c>
       <c r="C32" t="s">
-        <v>589</v>
+        <v>634</v>
       </c>
       <c r="D32" t="s">
-        <v>634</v>
+        <v>679</v>
       </c>
       <c r="E32" t="s">
-        <v>635</v>
+        <v>680</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>636</v>
+        <v>681</v>
       </c>
       <c r="B33" t="s">
-        <v>627</v>
+        <v>672</v>
       </c>
       <c r="C33" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D33" t="s">
-        <v>637</v>
+        <v>682</v>
       </c>
       <c r="E33" t="s">
-        <v>638</v>
+        <v>683</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>639</v>
+        <v>684</v>
       </c>
       <c r="B34" t="s">
-        <v>640</v>
+        <v>685</v>
       </c>
       <c r="C34" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D34" t="s">
-        <v>641</v>
+        <v>686</v>
       </c>
       <c r="E34" t="s">
-        <v>642</v>
+        <v>687</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>643</v>
+        <v>688</v>
       </c>
       <c r="B35" t="s">
-        <v>640</v>
+        <v>685</v>
       </c>
       <c r="C35" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D35" t="s">
-        <v>644</v>
+        <v>689</v>
       </c>
       <c r="E35" t="s">
-        <v>645</v>
+        <v>690</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>646</v>
+        <v>691</v>
       </c>
       <c r="B36" t="s">
-        <v>640</v>
+        <v>685</v>
       </c>
       <c r="C36" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D36" t="s">
-        <v>647</v>
+        <v>692</v>
       </c>
       <c r="E36" t="s">
-        <v>648</v>
+        <v>693</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>649</v>
+        <v>694</v>
       </c>
       <c r="B37" t="s">
-        <v>640</v>
+        <v>685</v>
       </c>
       <c r="C37" t="s">
-        <v>589</v>
+        <v>634</v>
       </c>
       <c r="D37" t="s">
-        <v>650</v>
+        <v>695</v>
       </c>
       <c r="E37" t="s">
-        <v>651</v>
+        <v>696</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>652</v>
+        <v>697</v>
       </c>
       <c r="B38" t="s">
-        <v>640</v>
+        <v>685</v>
       </c>
       <c r="C38" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D38" t="s">
-        <v>653</v>
+        <v>698</v>
       </c>
       <c r="E38" t="s">
-        <v>654</v>
+        <v>699</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>655</v>
+        <v>700</v>
       </c>
       <c r="B39" t="s">
-        <v>656</v>
+        <v>701</v>
       </c>
       <c r="C39" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D39" t="s">
-        <v>657</v>
+        <v>702</v>
       </c>
       <c r="E39" t="s">
-        <v>658</v>
+        <v>703</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>659</v>
+        <v>704</v>
       </c>
       <c r="B40" t="s">
-        <v>656</v>
+        <v>701</v>
       </c>
       <c r="C40" t="s">
-        <v>589</v>
+        <v>634</v>
       </c>
       <c r="D40" t="s">
-        <v>660</v>
+        <v>705</v>
       </c>
       <c r="E40" t="s">
-        <v>661</v>
+        <v>706</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>662</v>
+        <v>707</v>
       </c>
       <c r="B41" t="s">
-        <v>656</v>
+        <v>701</v>
       </c>
       <c r="C41" t="s">
-        <v>589</v>
+        <v>634</v>
       </c>
       <c r="D41" t="s">
-        <v>663</v>
+        <v>708</v>
       </c>
       <c r="E41" t="s">
-        <v>664</v>
+        <v>709</v>
       </c>
     </row>
   </sheetData>
@@ -6236,7 +6590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F552A4D2-FB82-4063-862C-E2CD3384FC8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BBABED-2C5B-4190-B266-EE29E03ACB04}">
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -6255,363 +6609,363 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>665</v>
+        <v>710</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>666</v>
+        <v>711</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>667</v>
+        <v>712</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>668</v>
+        <v>713</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>669</v>
+        <v>714</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>670</v>
+        <v>715</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>671</v>
+        <v>716</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>672</v>
+        <v>717</v>
       </c>
       <c r="B2" t="s">
-        <v>673</v>
+        <v>718</v>
       </c>
       <c r="C2" t="s">
-        <v>674</v>
+        <v>719</v>
       </c>
       <c r="D2" t="s">
-        <v>675</v>
+        <v>720</v>
       </c>
       <c r="E2" t="s">
-        <v>676</v>
+        <v>721</v>
       </c>
       <c r="F2" t="s">
-        <v>677</v>
+        <v>722</v>
       </c>
       <c r="G2" t="s">
-        <v>678</v>
+        <v>723</v>
       </c>
       <c r="H2" t="s">
-        <v>679</v>
+        <v>724</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>680</v>
+        <v>725</v>
       </c>
       <c r="B3" t="s">
-        <v>673</v>
+        <v>718</v>
       </c>
       <c r="C3" t="s">
-        <v>681</v>
+        <v>726</v>
       </c>
       <c r="D3" t="s">
-        <v>682</v>
+        <v>727</v>
       </c>
       <c r="E3" t="s">
-        <v>683</v>
+        <v>728</v>
       </c>
       <c r="F3" t="s">
-        <v>684</v>
+        <v>729</v>
       </c>
       <c r="G3" t="s">
-        <v>685</v>
+        <v>730</v>
       </c>
       <c r="H3" t="s">
-        <v>679</v>
+        <v>724</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>686</v>
+        <v>731</v>
       </c>
       <c r="B4" t="s">
-        <v>673</v>
+        <v>718</v>
       </c>
       <c r="C4" t="s">
-        <v>687</v>
+        <v>732</v>
       </c>
       <c r="D4" t="s">
-        <v>682</v>
+        <v>727</v>
       </c>
       <c r="E4" t="s">
-        <v>688</v>
+        <v>733</v>
       </c>
       <c r="F4" t="s">
-        <v>689</v>
+        <v>734</v>
       </c>
       <c r="G4" t="s">
-        <v>690</v>
+        <v>735</v>
       </c>
       <c r="H4" t="s">
-        <v>679</v>
+        <v>724</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>691</v>
+        <v>736</v>
       </c>
       <c r="B5" t="s">
-        <v>673</v>
+        <v>718</v>
       </c>
       <c r="C5" t="s">
-        <v>692</v>
+        <v>737</v>
       </c>
       <c r="D5" t="s">
-        <v>693</v>
+        <v>738</v>
       </c>
       <c r="E5" t="s">
-        <v>694</v>
+        <v>739</v>
       </c>
       <c r="F5" t="s">
-        <v>695</v>
+        <v>740</v>
       </c>
       <c r="G5" t="s">
-        <v>696</v>
+        <v>741</v>
       </c>
       <c r="H5" t="s">
-        <v>697</v>
+        <v>742</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>698</v>
+        <v>743</v>
       </c>
       <c r="B6" t="s">
-        <v>673</v>
+        <v>718</v>
       </c>
       <c r="C6" t="s">
-        <v>699</v>
+        <v>744</v>
       </c>
       <c r="D6" t="s">
-        <v>675</v>
+        <v>720</v>
       </c>
       <c r="E6" t="s">
-        <v>700</v>
+        <v>745</v>
       </c>
       <c r="F6" t="s">
-        <v>701</v>
+        <v>746</v>
       </c>
       <c r="G6" t="s">
-        <v>702</v>
+        <v>747</v>
       </c>
       <c r="H6" t="s">
-        <v>703</v>
+        <v>748</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>704</v>
+        <v>749</v>
       </c>
       <c r="B7" t="s">
-        <v>673</v>
+        <v>718</v>
       </c>
       <c r="C7" t="s">
-        <v>705</v>
+        <v>750</v>
       </c>
       <c r="D7" t="s">
-        <v>706</v>
+        <v>751</v>
       </c>
       <c r="E7" t="s">
-        <v>707</v>
+        <v>752</v>
       </c>
       <c r="F7" t="s">
-        <v>708</v>
+        <v>753</v>
       </c>
       <c r="G7" t="s">
-        <v>709</v>
+        <v>754</v>
       </c>
       <c r="H7" t="s">
-        <v>710</v>
+        <v>755</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>711</v>
+        <v>756</v>
       </c>
       <c r="B8" t="s">
-        <v>712</v>
+        <v>757</v>
       </c>
       <c r="C8" t="s">
-        <v>713</v>
+        <v>758</v>
       </c>
       <c r="D8" t="s">
-        <v>675</v>
+        <v>720</v>
       </c>
       <c r="E8" t="s">
-        <v>714</v>
+        <v>759</v>
       </c>
       <c r="F8" t="s">
-        <v>715</v>
+        <v>760</v>
       </c>
       <c r="G8" t="s">
-        <v>716</v>
+        <v>761</v>
       </c>
       <c r="H8" t="s">
-        <v>717</v>
+        <v>762</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>718</v>
+        <v>763</v>
       </c>
       <c r="B9" t="s">
-        <v>712</v>
+        <v>757</v>
       </c>
       <c r="C9" t="s">
-        <v>719</v>
+        <v>764</v>
       </c>
       <c r="D9" t="s">
-        <v>675</v>
+        <v>720</v>
       </c>
       <c r="E9" t="s">
-        <v>720</v>
+        <v>765</v>
       </c>
       <c r="F9" t="s">
-        <v>721</v>
+        <v>766</v>
       </c>
       <c r="G9" t="s">
-        <v>722</v>
+        <v>767</v>
       </c>
       <c r="H9" t="s">
-        <v>717</v>
+        <v>762</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>723</v>
+        <v>768</v>
       </c>
       <c r="B10" t="s">
-        <v>724</v>
+        <v>769</v>
       </c>
       <c r="C10" t="s">
-        <v>725</v>
+        <v>770</v>
       </c>
       <c r="D10" t="s">
-        <v>726</v>
+        <v>771</v>
       </c>
       <c r="E10" t="s">
-        <v>727</v>
+        <v>772</v>
       </c>
       <c r="F10" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="G10" t="s">
-        <v>729</v>
+        <v>774</v>
       </c>
       <c r="H10" t="s">
-        <v>730</v>
+        <v>775</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>731</v>
+        <v>776</v>
       </c>
       <c r="B11" t="s">
-        <v>732</v>
+        <v>777</v>
       </c>
       <c r="C11" t="s">
-        <v>733</v>
+        <v>778</v>
       </c>
       <c r="D11" t="s">
-        <v>726</v>
+        <v>771</v>
       </c>
       <c r="E11" t="s">
-        <v>734</v>
+        <v>779</v>
       </c>
       <c r="F11" t="s">
-        <v>735</v>
+        <v>780</v>
       </c>
       <c r="G11" t="s">
-        <v>736</v>
+        <v>781</v>
       </c>
       <c r="H11" t="s">
-        <v>737</v>
+        <v>782</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>738</v>
+        <v>783</v>
       </c>
       <c r="B12" t="s">
-        <v>739</v>
+        <v>784</v>
       </c>
       <c r="C12" t="s">
-        <v>740</v>
+        <v>785</v>
       </c>
       <c r="D12" t="s">
-        <v>682</v>
+        <v>727</v>
       </c>
       <c r="E12" t="s">
-        <v>741</v>
+        <v>786</v>
       </c>
       <c r="F12" t="s">
-        <v>742</v>
+        <v>787</v>
       </c>
       <c r="G12" t="s">
-        <v>743</v>
+        <v>788</v>
       </c>
       <c r="H12" t="s">
-        <v>744</v>
+        <v>789</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>745</v>
+        <v>790</v>
       </c>
       <c r="B13" t="s">
-        <v>746</v>
+        <v>791</v>
       </c>
       <c r="C13" t="s">
-        <v>747</v>
+        <v>792</v>
       </c>
       <c r="D13" t="s">
-        <v>682</v>
+        <v>727</v>
       </c>
       <c r="E13" t="s">
-        <v>748</v>
+        <v>793</v>
       </c>
       <c r="F13" t="s">
-        <v>749</v>
+        <v>794</v>
       </c>
       <c r="G13" t="s">
-        <v>743</v>
+        <v>788</v>
       </c>
       <c r="H13" t="s">
-        <v>744</v>
+        <v>789</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>750</v>
+        <v>795</v>
       </c>
       <c r="B14" t="s">
-        <v>751</v>
+        <v>796</v>
       </c>
       <c r="C14" t="s">
-        <v>752</v>
+        <v>797</v>
       </c>
       <c r="D14" t="s">
-        <v>726</v>
+        <v>771</v>
       </c>
       <c r="E14" t="s">
-        <v>753</v>
+        <v>798</v>
       </c>
       <c r="F14" t="s">
-        <v>754</v>
+        <v>799</v>
       </c>
       <c r="G14" t="s">
-        <v>755</v>
+        <v>800</v>
       </c>
       <c r="H14" t="s">
-        <v>744</v>
+        <v>789</v>
       </c>
     </row>
   </sheetData>
@@ -6621,7 +6975,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A5589B3-69BE-4DFD-BEA2-5F5F989622B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4956A2F2-F43A-4EF9-8583-5FD7E412FE5E}">
   <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -6646,132 +7000,132 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>756</v>
+        <v>801</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>757</v>
+        <v>802</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>758</v>
+        <v>803</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>759</v>
+        <v>804</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>760</v>
+        <v>805</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>761</v>
+        <v>806</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>762</v>
+        <v>807</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>763</v>
+        <v>808</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>764</v>
+        <v>809</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>765</v>
+        <v>810</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>766</v>
+        <v>811</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>767</v>
+        <v>812</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>768</v>
+        <v>813</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>769</v>
+        <v>814</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>770</v>
+        <v>815</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>771</v>
+        <v>816</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>772</v>
+        <v>817</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>773</v>
+        <v>818</v>
       </c>
       <c r="B2" t="s">
-        <v>774</v>
+        <v>819</v>
       </c>
       <c r="C2" t="s">
-        <v>775</v>
+        <v>820</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>776</v>
+        <v>821</v>
       </c>
       <c r="B3" t="s">
-        <v>777</v>
+        <v>822</v>
       </c>
       <c r="C3" t="s">
-        <v>778</v>
+        <v>823</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>779</v>
+        <v>824</v>
       </c>
       <c r="B4" t="s">
-        <v>780</v>
+        <v>825</v>
       </c>
       <c r="C4" t="s">
-        <v>781</v>
+        <v>826</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>782</v>
+        <v>827</v>
       </c>
       <c r="B5" t="s">
-        <v>783</v>
+        <v>828</v>
       </c>
       <c r="C5" t="s">
-        <v>784</v>
+        <v>829</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>785</v>
+        <v>830</v>
       </c>
       <c r="B6" t="s">
-        <v>786</v>
+        <v>831</v>
       </c>
       <c r="C6" t="s">
-        <v>787</v>
+        <v>832</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>788</v>
+        <v>833</v>
       </c>
       <c r="B7" t="s">
-        <v>789</v>
+        <v>834</v>
       </c>
       <c r="C7" t="s">
-        <v>790</v>
+        <v>835</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>791</v>
+        <v>836</v>
       </c>
       <c r="B8" t="s">
-        <v>792</v>
+        <v>837</v>
       </c>
       <c r="C8" t="s">
-        <v>793</v>
+        <v>838</v>
       </c>
     </row>
   </sheetData>
@@ -6781,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC931DD-2A80-4CE3-BD8D-6EBD7186602B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DEBE49F-CFDD-4A45-A2DF-199F855CA052}">
   <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -6800,40 +7154,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>794</v>
+        <v>839</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>795</v>
+        <v>840</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>796</v>
+        <v>841</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>797</v>
+        <v>842</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>798</v>
+        <v>843</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>799</v>
+        <v>844</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>800</v>
+        <v>845</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>801</v>
+        <v>846</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>802</v>
+        <v>847</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>803</v>
+        <v>848</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>804</v>
+        <v>849</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>805</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>

--- a/출산준비물_통합데이터.xlsx
+++ b/출산준비물_통합데이터.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\진규어플\출산준비물어플\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://m100001874-my.sharepoint.com/personal/kong090821_cbsn-e_cbe_go_kr/Documents/2026학년도/인공지능/출산준비물어플/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EB126D0-4C70-4786-815D-FDE69C05E852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{532F4B02-A066-404B-8811-D037DBEAA8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5340" yWindow="3030" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="5" xr2:uid="{529BC0EA-11C5-48AB-B786-C56AF9AD1BF9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{070A16D8-99D2-45CE-8B35-4F36DF64D5CD}"/>
   </bookViews>
   <sheets>
     <sheet name="출산가방 체크리스트" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="854">
   <si>
     <t>ID</t>
   </si>
@@ -75,6 +75,15 @@
   </si>
   <si>
     <t>선배맘 추천 TOP3</t>
+  </si>
+  <si>
+    <t>쿠팡 1위 링크(선택)</t>
+  </si>
+  <si>
+    <t>쿠팡 2위 링크(선택)</t>
+  </si>
+  <si>
+    <t>쿠팡 3위 링크(선택)</t>
   </si>
   <si>
     <t>m_cloth_1</t>
@@ -2974,8 +2983,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF1F800-C143-404B-BD22-AF7A7E2C8C39}">
-  <dimension ref="A1:K70"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{608A9FB4-C32C-450F-98B0-5FE8427DCDD2}">
+  <dimension ref="A1:N70"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
@@ -2989,9 +2998,10 @@
     <col min="9" max="9" width="45.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="43.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="43.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="19.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27.95" customHeight="1">
+    <row r="1" spans="1:14" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3025,2156 +3035,2165 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="H4" t="s">
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J11" t="s">
         <v>28</v>
       </c>
-      <c r="I4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="K11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
         <v>15</v>
       </c>
-      <c r="H6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" t="s">
+        <v>86</v>
+      </c>
+      <c r="J13" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
         <v>15</v>
       </c>
-      <c r="H7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" t="s">
-        <v>48</v>
-      </c>
-      <c r="K7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" t="s">
+        <v>92</v>
+      </c>
+      <c r="J14" t="s">
+        <v>93</v>
+      </c>
+      <c r="K14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="G8" t="s">
-        <v>52</v>
-      </c>
-      <c r="H8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" t="s">
         <v>15</v>
       </c>
-      <c r="G9" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" t="s">
-        <v>59</v>
-      </c>
-      <c r="J9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10" t="s">
-        <v>67</v>
-      </c>
-      <c r="K10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" t="s">
-        <v>72</v>
-      </c>
-      <c r="I11" t="s">
-        <v>72</v>
-      </c>
-      <c r="J11" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="C16" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" t="s">
-        <v>76</v>
-      </c>
-      <c r="I12" t="s">
-        <v>77</v>
-      </c>
-      <c r="J12" t="s">
-        <v>78</v>
-      </c>
-      <c r="K12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" t="s">
-        <v>82</v>
-      </c>
-      <c r="I13" t="s">
-        <v>83</v>
-      </c>
-      <c r="J13" t="s">
-        <v>84</v>
-      </c>
-      <c r="K13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" t="s">
-        <v>88</v>
-      </c>
-      <c r="I14" t="s">
-        <v>89</v>
-      </c>
-      <c r="J14" t="s">
-        <v>90</v>
-      </c>
-      <c r="K14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" t="s">
-        <v>93</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" t="s">
-        <v>94</v>
-      </c>
-      <c r="I15" t="s">
-        <v>95</v>
-      </c>
-      <c r="J15" t="s">
-        <v>96</v>
-      </c>
-      <c r="K15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>70</v>
-      </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H16" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I16" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J16" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H17" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I17" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J17" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K17" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G18" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J18" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K18" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G20" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H20" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I20" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K20" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H21" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I21" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J21" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K21" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H22" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I22" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J22" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K22" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D23" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H23" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I23" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J23" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K23" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D24" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H24" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I24" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J24" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K24" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H25" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I25" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J25" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K25" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D26" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H26" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I26" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J26" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K26" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D27" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F27" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H27" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I27" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J27" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K27" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D28" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G28" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H28" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I28" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J28" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K28" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D29" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F29" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G29" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H29" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I29" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J29" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K29" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F30" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G30" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H30" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I30" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J30" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K30" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D31" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F31" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G31" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H31" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I31" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="J31" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K31" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D32" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E32" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G32" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H32" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I32" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J32" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K32" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B33" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C33" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D33" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F33" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H33" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I33" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J33" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K33" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B34" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C34" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D34" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F34" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H34" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I34" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J34" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K34" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B35" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C35" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D35" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F35" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G35" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H35" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="I35" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J35" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K35" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B36" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C36" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D36" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F36" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G36" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H36" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I36" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="J36" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K36" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B37" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C37" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D37" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F37" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H37" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I37" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J37" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="K37" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B38" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C38" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D38" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F38" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H38" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I38" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="J38" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K38" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B39" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C39" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D39" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F39" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G39" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H39" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="I39" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J39" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K39" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B40" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C40" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D40" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F40" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G40" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H40" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I40" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="J40" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="K40" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B41" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C41" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D41" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F41" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H41" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="I41" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="J41" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K41" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B42" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C42" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D42" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F42" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H42" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I42" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="J42" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K42" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B43" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C43" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D43" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F43" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G43" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H43" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I43" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="J43" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K43" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B44" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C44" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D44" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F44" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H44" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I44" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="J44" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K44" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B45" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C45" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D45" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E45" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F45" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G45" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H45" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I45" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J45" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K45" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B46" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C46" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D46" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E46" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F46" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G46" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H46" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="I46" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="J46" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K46" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B47" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C47" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D47" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E47" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F47" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H47" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="I47" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="J47" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="K47" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B48" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C48" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D48" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F48" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G48" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H48" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I48" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="J48" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="K48" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B49" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C49" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F49" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="I49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="J49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K49" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B50" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C50" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D50" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F50" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G50" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H50" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="I50" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J50" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K50" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B51" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D51" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F51" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G51" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H51" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="I51" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="J51" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K51" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B52" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C52" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D52" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F52" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G52" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H52" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I52" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J52" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K52" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B53" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C53" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D53" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F53" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G53" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H53" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I53" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="J53" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K53" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B54" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C54" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D54" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F54" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G54" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H54" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I54" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J54" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="K54" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B55" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C55" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D55" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F55" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G55" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="H55" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="I55" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J55" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K55" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B56" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C56" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D56" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F56" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H56" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="I56" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J56" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K56" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B57" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C57" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D57" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F57" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G57" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H57" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="I57" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="J57" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="K57" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B58" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C58" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D58" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F58" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H58" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="I58" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J58" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K58" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B59" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C59" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D59" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F59" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G59" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="H59" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="I59" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="J59" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K59" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B60" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C60" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D60" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F60" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G60" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="H60" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="I60" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J60" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="K60" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B61" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C61" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D61" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E61" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F61" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G61" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H61" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="I61" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="J61" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="K61" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B62" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C62" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D62" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F62" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H62" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I62" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="J62" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K62" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B63" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C63" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D63" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F63" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G63" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="H63" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="I63" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="J63" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="K63" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B64" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C64" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D64" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E64" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F64" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G64" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="H64" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="I64" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="J64" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K64" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C65" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D65" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F65" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G65" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="H65" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="I65" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J65" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="K65" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C66" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D66" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F66" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H66" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="I66" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="J66" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K66" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B67" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C67" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D67" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F67" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G67" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="H67" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="I67" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J67" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K67" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B68" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C68" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D68" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F68" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G68" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="H68" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="I68" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J68" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="K68" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B69" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C69" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D69" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E69" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F69" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G69" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="H69" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="I69" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="J69" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="K69" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B70" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C70" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D70" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F70" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G70" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="H70" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="I70" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J70" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="K70" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944AE346-DC81-4D40-8AA3-E0FF73D9CB6F}">
-  <dimension ref="A1:K21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7DF49F1-A40A-4419-8D7C-BFC8568FABFD}">
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.625" bestFit="1" customWidth="1"/>
@@ -5188,29 +5207,30 @@
     <col min="9" max="9" width="43.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="38" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="42.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="19.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27.95" customHeight="1">
+    <row r="1" spans="1:14" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
@@ -5224,648 +5244,657 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E2" t="s">
+        <v>463</v>
+      </c>
+      <c r="F2" t="s">
+        <v>464</v>
+      </c>
+      <c r="G2" t="s">
+        <v>465</v>
+      </c>
+      <c r="H2" t="s">
+        <v>466</v>
+      </c>
+      <c r="I2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J2" t="s">
+        <v>467</v>
+      </c>
+      <c r="K2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B3" t="s">
         <v>460</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C3" t="s">
         <v>461</v>
       </c>
-      <c r="G2" t="s">
-        <v>462</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="D3" t="s">
+        <v>470</v>
+      </c>
+      <c r="E3" t="s">
         <v>463</v>
       </c>
-      <c r="I2" t="s">
+      <c r="F3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H3" t="s">
+        <v>472</v>
+      </c>
+      <c r="I3" t="s">
+        <v>472</v>
+      </c>
+      <c r="J3" t="s">
+        <v>473</v>
+      </c>
+      <c r="K3" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>475</v>
+      </c>
+      <c r="B4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C4" t="s">
+        <v>461</v>
+      </c>
+      <c r="D4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E4" t="s">
         <v>463</v>
       </c>
-      <c r="J2" t="s">
+      <c r="F4" t="s">
+        <v>471</v>
+      </c>
+      <c r="H4" t="s">
+        <v>477</v>
+      </c>
+      <c r="I4" t="s">
+        <v>477</v>
+      </c>
+      <c r="J4" t="s">
+        <v>478</v>
+      </c>
+      <c r="K4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B5" t="s">
+        <v>460</v>
+      </c>
+      <c r="C5" t="s">
+        <v>461</v>
+      </c>
+      <c r="D5" t="s">
+        <v>481</v>
+      </c>
+      <c r="E5" t="s">
+        <v>463</v>
+      </c>
+      <c r="F5" t="s">
+        <v>471</v>
+      </c>
+      <c r="H5" t="s">
+        <v>482</v>
+      </c>
+      <c r="I5" t="s">
+        <v>482</v>
+      </c>
+      <c r="J5" t="s">
+        <v>483</v>
+      </c>
+      <c r="K5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>485</v>
+      </c>
+      <c r="B6" t="s">
+        <v>460</v>
+      </c>
+      <c r="C6" t="s">
+        <v>461</v>
+      </c>
+      <c r="D6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E6" t="s">
+        <v>463</v>
+      </c>
+      <c r="F6" t="s">
+        <v>471</v>
+      </c>
+      <c r="H6" t="s">
+        <v>487</v>
+      </c>
+      <c r="I6" t="s">
+        <v>487</v>
+      </c>
+      <c r="J6" t="s">
+        <v>488</v>
+      </c>
+      <c r="K6" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>490</v>
+      </c>
+      <c r="B7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C7" t="s">
+        <v>461</v>
+      </c>
+      <c r="D7" t="s">
+        <v>491</v>
+      </c>
+      <c r="E7" t="s">
+        <v>492</v>
+      </c>
+      <c r="F7" t="s">
+        <v>471</v>
+      </c>
+      <c r="H7" t="s">
+        <v>493</v>
+      </c>
+      <c r="I7" t="s">
+        <v>493</v>
+      </c>
+      <c r="J7" t="s">
+        <v>494</v>
+      </c>
+      <c r="K7" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>496</v>
+      </c>
+      <c r="B8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C8" t="s">
+        <v>461</v>
+      </c>
+      <c r="D8" t="s">
+        <v>497</v>
+      </c>
+      <c r="E8" t="s">
+        <v>463</v>
+      </c>
+      <c r="F8" t="s">
+        <v>471</v>
+      </c>
+      <c r="H8" t="s">
+        <v>498</v>
+      </c>
+      <c r="I8" t="s">
+        <v>499</v>
+      </c>
+      <c r="J8" t="s">
+        <v>500</v>
+      </c>
+      <c r="K8" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>502</v>
+      </c>
+      <c r="B9" t="s">
+        <v>460</v>
+      </c>
+      <c r="C9" t="s">
+        <v>461</v>
+      </c>
+      <c r="D9" t="s">
+        <v>503</v>
+      </c>
+      <c r="E9" t="s">
+        <v>504</v>
+      </c>
+      <c r="F9" t="s">
+        <v>471</v>
+      </c>
+      <c r="H9" t="s">
+        <v>505</v>
+      </c>
+      <c r="I9" t="s">
+        <v>506</v>
+      </c>
+      <c r="J9" t="s">
+        <v>507</v>
+      </c>
+      <c r="K9" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>509</v>
+      </c>
+      <c r="B10" t="s">
+        <v>460</v>
+      </c>
+      <c r="C10" t="s">
+        <v>461</v>
+      </c>
+      <c r="D10" t="s">
+        <v>510</v>
+      </c>
+      <c r="E10" t="s">
+        <v>511</v>
+      </c>
+      <c r="F10" t="s">
+        <v>471</v>
+      </c>
+      <c r="H10" t="s">
+        <v>512</v>
+      </c>
+      <c r="I10" t="s">
+        <v>513</v>
+      </c>
+      <c r="J10" t="s">
+        <v>514</v>
+      </c>
+      <c r="K10" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>516</v>
+      </c>
+      <c r="B11" t="s">
+        <v>460</v>
+      </c>
+      <c r="C11" t="s">
+        <v>461</v>
+      </c>
+      <c r="D11" t="s">
+        <v>517</v>
+      </c>
+      <c r="E11" t="s">
+        <v>504</v>
+      </c>
+      <c r="F11" t="s">
         <v>464</v>
       </c>
-      <c r="K2" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>466</v>
-      </c>
-      <c r="B3" t="s">
-        <v>457</v>
-      </c>
-      <c r="C3" t="s">
-        <v>458</v>
-      </c>
-      <c r="D3" t="s">
-        <v>467</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="H11" t="s">
+        <v>518</v>
+      </c>
+      <c r="I11" t="s">
+        <v>519</v>
+      </c>
+      <c r="J11" t="s">
+        <v>520</v>
+      </c>
+      <c r="K11" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>522</v>
+      </c>
+      <c r="B12" t="s">
         <v>460</v>
       </c>
-      <c r="F3" t="s">
-        <v>468</v>
-      </c>
-      <c r="H3" t="s">
-        <v>469</v>
-      </c>
-      <c r="I3" t="s">
-        <v>469</v>
-      </c>
-      <c r="J3" t="s">
-        <v>470</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="C12" t="s">
+        <v>461</v>
+      </c>
+      <c r="D12" t="s">
+        <v>523</v>
+      </c>
+      <c r="E12" t="s">
+        <v>463</v>
+      </c>
+      <c r="F12" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>472</v>
-      </c>
-      <c r="B4" t="s">
-        <v>457</v>
-      </c>
-      <c r="C4" t="s">
-        <v>458</v>
-      </c>
-      <c r="D4" t="s">
-        <v>473</v>
-      </c>
-      <c r="E4" t="s">
-        <v>460</v>
-      </c>
-      <c r="F4" t="s">
-        <v>468</v>
-      </c>
-      <c r="H4" t="s">
-        <v>474</v>
-      </c>
-      <c r="I4" t="s">
-        <v>474</v>
-      </c>
-      <c r="J4" t="s">
-        <v>475</v>
-      </c>
-      <c r="K4" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>477</v>
-      </c>
-      <c r="B5" t="s">
-        <v>457</v>
-      </c>
-      <c r="C5" t="s">
-        <v>458</v>
-      </c>
-      <c r="D5" t="s">
-        <v>478</v>
-      </c>
-      <c r="E5" t="s">
-        <v>460</v>
-      </c>
-      <c r="F5" t="s">
-        <v>468</v>
-      </c>
-      <c r="H5" t="s">
-        <v>479</v>
-      </c>
-      <c r="I5" t="s">
-        <v>479</v>
-      </c>
-      <c r="J5" t="s">
-        <v>480</v>
-      </c>
-      <c r="K5" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>482</v>
-      </c>
-      <c r="B6" t="s">
-        <v>457</v>
-      </c>
-      <c r="C6" t="s">
-        <v>458</v>
-      </c>
-      <c r="D6" t="s">
-        <v>483</v>
-      </c>
-      <c r="E6" t="s">
-        <v>460</v>
-      </c>
-      <c r="F6" t="s">
-        <v>468</v>
-      </c>
-      <c r="H6" t="s">
-        <v>484</v>
-      </c>
-      <c r="I6" t="s">
-        <v>484</v>
-      </c>
-      <c r="J6" t="s">
-        <v>485</v>
-      </c>
-      <c r="K6" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>487</v>
-      </c>
-      <c r="B7" t="s">
-        <v>457</v>
-      </c>
-      <c r="C7" t="s">
-        <v>458</v>
-      </c>
-      <c r="D7" t="s">
-        <v>488</v>
-      </c>
-      <c r="E7" t="s">
-        <v>489</v>
-      </c>
-      <c r="F7" t="s">
-        <v>468</v>
-      </c>
-      <c r="H7" t="s">
-        <v>490</v>
-      </c>
-      <c r="I7" t="s">
-        <v>490</v>
-      </c>
-      <c r="J7" t="s">
-        <v>491</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="H12" t="s">
+        <v>320</v>
+      </c>
+      <c r="I12" t="s">
+        <v>524</v>
+      </c>
+      <c r="J12" t="s">
+        <v>525</v>
+      </c>
+      <c r="K12" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>527</v>
+      </c>
+      <c r="B13" t="s">
+        <v>528</v>
+      </c>
+      <c r="C13" t="s">
+        <v>529</v>
+      </c>
+      <c r="D13" t="s">
+        <v>530</v>
+      </c>
+      <c r="E13" t="s">
+        <v>504</v>
+      </c>
+      <c r="F13" t="s">
+        <v>464</v>
+      </c>
+      <c r="H13" t="s">
+        <v>531</v>
+      </c>
+      <c r="I13" t="s">
+        <v>532</v>
+      </c>
+      <c r="J13" t="s">
+        <v>533</v>
+      </c>
+      <c r="K13" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>535</v>
+      </c>
+      <c r="B14" t="s">
+        <v>528</v>
+      </c>
+      <c r="C14" t="s">
+        <v>529</v>
+      </c>
+      <c r="D14" t="s">
+        <v>536</v>
+      </c>
+      <c r="E14" t="s">
+        <v>463</v>
+      </c>
+      <c r="F14" t="s">
+        <v>471</v>
+      </c>
+      <c r="H14" t="s">
+        <v>537</v>
+      </c>
+      <c r="I14" t="s">
+        <v>537</v>
+      </c>
+      <c r="J14" t="s">
+        <v>538</v>
+      </c>
+      <c r="K14" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>540</v>
+      </c>
+      <c r="B15" t="s">
+        <v>528</v>
+      </c>
+      <c r="C15" t="s">
+        <v>529</v>
+      </c>
+      <c r="D15" t="s">
+        <v>541</v>
+      </c>
+      <c r="E15" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>493</v>
-      </c>
-      <c r="B8" t="s">
-        <v>457</v>
-      </c>
-      <c r="C8" t="s">
-        <v>458</v>
-      </c>
-      <c r="D8" t="s">
-        <v>494</v>
-      </c>
-      <c r="E8" t="s">
-        <v>460</v>
-      </c>
-      <c r="F8" t="s">
-        <v>468</v>
-      </c>
-      <c r="H8" t="s">
-        <v>495</v>
-      </c>
-      <c r="I8" t="s">
-        <v>496</v>
-      </c>
-      <c r="J8" t="s">
-        <v>497</v>
-      </c>
-      <c r="K8" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>499</v>
-      </c>
-      <c r="B9" t="s">
-        <v>457</v>
-      </c>
-      <c r="C9" t="s">
-        <v>458</v>
-      </c>
-      <c r="D9" t="s">
-        <v>500</v>
-      </c>
-      <c r="E9" t="s">
-        <v>501</v>
-      </c>
-      <c r="F9" t="s">
-        <v>468</v>
-      </c>
-      <c r="H9" t="s">
-        <v>502</v>
-      </c>
-      <c r="I9" t="s">
-        <v>503</v>
-      </c>
-      <c r="J9" t="s">
-        <v>504</v>
-      </c>
-      <c r="K9" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>506</v>
-      </c>
-      <c r="B10" t="s">
-        <v>457</v>
-      </c>
-      <c r="C10" t="s">
-        <v>458</v>
-      </c>
-      <c r="D10" t="s">
-        <v>507</v>
-      </c>
-      <c r="E10" t="s">
-        <v>508</v>
-      </c>
-      <c r="F10" t="s">
-        <v>468</v>
-      </c>
-      <c r="H10" t="s">
-        <v>509</v>
-      </c>
-      <c r="I10" t="s">
-        <v>510</v>
-      </c>
-      <c r="J10" t="s">
-        <v>511</v>
-      </c>
-      <c r="K10" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>513</v>
-      </c>
-      <c r="B11" t="s">
-        <v>457</v>
-      </c>
-      <c r="C11" t="s">
-        <v>458</v>
-      </c>
-      <c r="D11" t="s">
-        <v>514</v>
-      </c>
-      <c r="E11" t="s">
-        <v>501</v>
-      </c>
-      <c r="F11" t="s">
-        <v>461</v>
-      </c>
-      <c r="H11" t="s">
-        <v>515</v>
-      </c>
-      <c r="I11" t="s">
-        <v>516</v>
-      </c>
-      <c r="J11" t="s">
-        <v>517</v>
-      </c>
-      <c r="K11" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>519</v>
-      </c>
-      <c r="B12" t="s">
-        <v>457</v>
-      </c>
-      <c r="C12" t="s">
-        <v>458</v>
-      </c>
-      <c r="D12" t="s">
-        <v>520</v>
-      </c>
-      <c r="E12" t="s">
-        <v>460</v>
-      </c>
-      <c r="F12" t="s">
-        <v>468</v>
-      </c>
-      <c r="H12" t="s">
-        <v>317</v>
-      </c>
-      <c r="I12" t="s">
-        <v>521</v>
-      </c>
-      <c r="J12" t="s">
-        <v>522</v>
-      </c>
-      <c r="K12" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>524</v>
-      </c>
-      <c r="B13" t="s">
-        <v>525</v>
-      </c>
-      <c r="C13" t="s">
-        <v>526</v>
-      </c>
-      <c r="D13" t="s">
-        <v>527</v>
-      </c>
-      <c r="E13" t="s">
-        <v>501</v>
-      </c>
-      <c r="F13" t="s">
-        <v>461</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="F15" t="s">
+        <v>471</v>
+      </c>
+      <c r="H15" t="s">
+        <v>542</v>
+      </c>
+      <c r="I15" t="s">
+        <v>543</v>
+      </c>
+      <c r="J15" t="s">
+        <v>544</v>
+      </c>
+      <c r="K15" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>546</v>
+      </c>
+      <c r="B16" t="s">
         <v>528</v>
       </c>
-      <c r="I13" t="s">
+      <c r="C16" t="s">
         <v>529</v>
       </c>
-      <c r="J13" t="s">
-        <v>530</v>
-      </c>
-      <c r="K13" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>532</v>
-      </c>
-      <c r="B14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C14" t="s">
-        <v>526</v>
-      </c>
-      <c r="D14" t="s">
-        <v>533</v>
-      </c>
-      <c r="E14" t="s">
-        <v>460</v>
-      </c>
-      <c r="F14" t="s">
-        <v>468</v>
-      </c>
-      <c r="H14" t="s">
-        <v>534</v>
-      </c>
-      <c r="I14" t="s">
-        <v>534</v>
-      </c>
-      <c r="J14" t="s">
-        <v>535</v>
-      </c>
-      <c r="K14" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>537</v>
-      </c>
-      <c r="B15" t="s">
-        <v>525</v>
-      </c>
-      <c r="C15" t="s">
-        <v>526</v>
-      </c>
-      <c r="D15" t="s">
-        <v>538</v>
-      </c>
-      <c r="E15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F15" t="s">
-        <v>468</v>
-      </c>
-      <c r="H15" t="s">
-        <v>539</v>
-      </c>
-      <c r="I15" t="s">
-        <v>540</v>
-      </c>
-      <c r="J15" t="s">
-        <v>541</v>
-      </c>
-      <c r="K15" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>543</v>
-      </c>
-      <c r="B16" t="s">
-        <v>525</v>
-      </c>
-      <c r="C16" t="s">
-        <v>526</v>
-      </c>
       <c r="D16" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E16" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F16" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="H16" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="I16" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="J16" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K16" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B17" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C17" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D17" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E17" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F17" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="H17" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="I17" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="J17" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K17" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B18" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C18" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D18" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E18" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F18" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="H18" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="I18" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="J18" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="K18" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B19" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C19" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D19" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E19" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F19" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="H19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="I19" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="J19" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K19" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B20" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C20" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D20" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E20" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F20" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="H20" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="I20" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="J20" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K20" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B21" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C21" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D21" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E21" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F21" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="H21" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="I21" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="J21" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="K21" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -5875,7 +5904,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F865740-48E8-4E73-B837-DAD528B3468E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4343418-7E20-4F96-BDD2-550CFAB37097}">
   <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -5891,696 +5920,696 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
+        <v>591</v>
+      </c>
+      <c r="B3" t="s">
+        <v>587</v>
+      </c>
+      <c r="C3" t="s">
         <v>588</v>
       </c>
-      <c r="B3" t="s">
-        <v>584</v>
-      </c>
-      <c r="C3" t="s">
-        <v>585</v>
-      </c>
       <c r="D3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="E3" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B4" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C4" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D4" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B5" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C5" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B6" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C6" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D6" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E6" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B7" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C7" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D7" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E7" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B8" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C8" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D8" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E8" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B9" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C9" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D9" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E9" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B10" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C10" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D10" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E10" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B11" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C11" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D11" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E11" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B12" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C12" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D12" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E12" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B13" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C13" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D13" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E13" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B14" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C14" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D14" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="E14" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B15" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C15" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D15" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E15" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B16" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C16" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D16" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E16" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B17" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C17" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D17" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E17" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B18" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C18" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D18" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="E18" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
+        <v>640</v>
+      </c>
+      <c r="B19" t="s">
+        <v>587</v>
+      </c>
+      <c r="C19" t="s">
         <v>637</v>
       </c>
-      <c r="B19" t="s">
-        <v>584</v>
-      </c>
-      <c r="C19" t="s">
-        <v>634</v>
-      </c>
       <c r="D19" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="E19" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B20" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C20" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D20" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E20" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B21" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C21" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D21" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="E21" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B22" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C22" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D22" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="E22" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B23" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C23" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D23" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="E23" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B24" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C24" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D24" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="E24" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B25" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C25" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="D25" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E25" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="B26" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C26" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D26" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="E26" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B27" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C27" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D27" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E27" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="B28" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C28" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D28" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E28" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="B29" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C29" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="D29" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E29" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B30" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C30" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D30" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="E30" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
+        <v>678</v>
+      </c>
+      <c r="B31" t="s">
         <v>675</v>
       </c>
-      <c r="B31" t="s">
-        <v>672</v>
-      </c>
       <c r="C31" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D31" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="E31" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B32" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C32" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D32" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E32" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="B33" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C33" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D33" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="E33" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B34" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C34" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D34" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E34" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
+        <v>691</v>
+      </c>
+      <c r="B35" t="s">
         <v>688</v>
       </c>
-      <c r="B35" t="s">
-        <v>685</v>
-      </c>
       <c r="C35" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D35" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E35" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B36" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C36" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D36" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="E36" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B37" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C37" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D37" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E37" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B38" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C38" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D38" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="E38" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B39" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C39" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D39" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E39" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
+        <v>707</v>
+      </c>
+      <c r="B40" t="s">
         <v>704</v>
       </c>
-      <c r="B40" t="s">
-        <v>701</v>
-      </c>
       <c r="C40" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D40" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E40" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="B41" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C41" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D41" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="E41" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
     </row>
   </sheetData>
@@ -6590,7 +6619,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BBABED-2C5B-4190-B266-EE29E03ACB04}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1D07730-3D5D-47D7-AE6B-9C93C3220859}">
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -6609,363 +6638,363 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B2" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C2" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="D2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="F2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="G2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="H2" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="B3" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C3" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="D3" t="s">
+        <v>730</v>
+      </c>
+      <c r="E3" t="s">
+        <v>731</v>
+      </c>
+      <c r="F3" t="s">
+        <v>732</v>
+      </c>
+      <c r="G3" t="s">
+        <v>733</v>
+      </c>
+      <c r="H3" t="s">
         <v>727</v>
-      </c>
-      <c r="E3" t="s">
-        <v>728</v>
-      </c>
-      <c r="F3" t="s">
-        <v>729</v>
-      </c>
-      <c r="G3" t="s">
-        <v>730</v>
-      </c>
-      <c r="H3" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B4" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C4" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D4" t="s">
+        <v>730</v>
+      </c>
+      <c r="E4" t="s">
+        <v>736</v>
+      </c>
+      <c r="F4" t="s">
+        <v>737</v>
+      </c>
+      <c r="G4" t="s">
+        <v>738</v>
+      </c>
+      <c r="H4" t="s">
         <v>727</v>
-      </c>
-      <c r="E4" t="s">
-        <v>733</v>
-      </c>
-      <c r="F4" t="s">
-        <v>734</v>
-      </c>
-      <c r="G4" t="s">
-        <v>735</v>
-      </c>
-      <c r="H4" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B5" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C5" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="D5" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="E5" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="F5" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="G5" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="H5" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B6" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C6" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D6" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E6" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="F6" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="G6" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="H6" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B7" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C7" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="D7" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E7" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="F7" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="G7" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="H7" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B8" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="C8" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="D8" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E8" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="F8" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="G8" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="H8" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B9" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="C9" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="D9" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E9" t="s">
+        <v>768</v>
+      </c>
+      <c r="F9" t="s">
+        <v>769</v>
+      </c>
+      <c r="G9" t="s">
+        <v>770</v>
+      </c>
+      <c r="H9" t="s">
         <v>765</v>
-      </c>
-      <c r="F9" t="s">
-        <v>766</v>
-      </c>
-      <c r="G9" t="s">
-        <v>767</v>
-      </c>
-      <c r="H9" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B10" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="C10" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="D10" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="E10" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="F10" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="G10" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="H10" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B11" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C11" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D11" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="E11" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F11" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="G11" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="H11" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B12" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C12" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="D12" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="E12" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="F12" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="G12" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="H12" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="B13" t="s">
+        <v>794</v>
+      </c>
+      <c r="C13" t="s">
+        <v>795</v>
+      </c>
+      <c r="D13" t="s">
+        <v>730</v>
+      </c>
+      <c r="E13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F13" t="s">
+        <v>797</v>
+      </c>
+      <c r="G13" t="s">
         <v>791</v>
       </c>
-      <c r="C13" t="s">
+      <c r="H13" t="s">
         <v>792</v>
-      </c>
-      <c r="D13" t="s">
-        <v>727</v>
-      </c>
-      <c r="E13" t="s">
-        <v>793</v>
-      </c>
-      <c r="F13" t="s">
-        <v>794</v>
-      </c>
-      <c r="G13" t="s">
-        <v>788</v>
-      </c>
-      <c r="H13" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B14" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C14" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D14" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="E14" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="F14" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="G14" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="H14" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
   </sheetData>
@@ -6975,7 +7004,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4956A2F2-F43A-4EF9-8583-5FD7E412FE5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D9DF32-6260-4F06-8106-FA692B8913B1}">
   <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -7000,132 +7029,132 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="B2" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="C2" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B3" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="C3" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="B4" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C4" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B5" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="C5" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B6" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C6" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="B7" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C7" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B8" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C8" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
     </row>
   </sheetData>
@@ -7135,7 +7164,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DEBE49F-CFDD-4A45-A2DF-199F855CA052}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47658C12-34A5-4103-9319-F97CDA82D2FA}">
   <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -7154,40 +7183,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
     </row>
   </sheetData>

--- a/출산준비물_통합데이터.xlsx
+++ b/출산준비물_통합데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://m100001874-my.sharepoint.com/personal/kong090821_cbsn-e_cbe_go_kr/Documents/2026학년도/인공지능/출산준비물어플/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{532F4B02-A066-404B-8811-D037DBEAA8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98710532-BBB6-4AE2-9B42-5B1E4A8157A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{070A16D8-99D2-45CE-8B35-4F36DF64D5CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{2AB02095-D9A4-4E06-ABA4-2F7B367BFB5F}"/>
   </bookViews>
   <sheets>
     <sheet name="출산가방 체크리스트" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="833">
   <si>
     <t>ID</t>
   </si>
@@ -98,6 +98,9 @@
     <t>수유브라 / 수유나시 (3~4개)</t>
   </si>
   <si>
+    <t>1개</t>
+  </si>
+  <si>
     <t>#병원, #조리원</t>
   </si>
   <si>
@@ -575,7 +578,7 @@
     <t>개인 위생 &amp; 스킨케어</t>
   </si>
   <si>
-    <t>산모 세면용품 세트 (1세트)</t>
+    <t>산모 세면도구 세트 (1세트)</t>
   </si>
   <si>
     <t>(샴푸·바디워시·칫솔치약 등)</t>
@@ -653,16 +656,592 @@
     <t>콜라브 드라이샴푸 무향 저자극 파우더</t>
   </si>
   <si>
-    <t>m_sk_5</t>
-  </si>
-  <si>
-    <t>엄마용 영양제 (비타민, 철분 등)</t>
-  </si>
-  <si>
-    <t>1세트</t>
-  </si>
-  <si>
-    <t>(산후 회복·철분·비타민D·유산균)</t>
+    <t>b_cloth_1</t>
+  </si>
+  <si>
+    <t>신생아 용품</t>
+  </si>
+  <si>
+    <t>의류 &amp; 패브릭</t>
+  </si>
+  <si>
+    <t>배냇저고리 / 배냇수트 (1~2벌)</t>
+  </si>
+  <si>
+    <t>압소바 순면 배냇저고리 2종 세트</t>
+  </si>
+  <si>
+    <t>아가방 오가닉 코튼 배냇가운</t>
+  </si>
+  <si>
+    <t>에뜨와 텐셀 소프트 신생아 배냇</t>
+  </si>
+  <si>
+    <t>b_cloth_2</t>
+  </si>
+  <si>
+    <t>신생아 속싸개 (1~2장)</t>
+  </si>
+  <si>
+    <t>스와들업 오리지널 속싸개</t>
+  </si>
+  <si>
+    <t>스와들업 오리지널 속싸개 (기적의 속싸개)</t>
+  </si>
+  <si>
+    <t>말랑하니 스와들 스트랩</t>
+  </si>
+  <si>
+    <t>보네스트 밤부 모달 스와들 블랭킷</t>
+  </si>
+  <si>
+    <t>b_cloth_3</t>
+  </si>
+  <si>
+    <t>신생아 겉싸개 (1장)</t>
+  </si>
+  <si>
+    <t>(계절 고려)</t>
+  </si>
+  <si>
+    <t>아가방 베이직 사계절 겉싸개</t>
+  </si>
+  <si>
+    <t>밍크뮤 애니멀 자수 신생아 겉싸개</t>
+  </si>
+  <si>
+    <t>압소바 퀼팅 보온 겉싸개</t>
+  </si>
+  <si>
+    <t>b_cloth_4</t>
+  </si>
+  <si>
+    <t>신생아 모자 (1~2개)</t>
+  </si>
+  <si>
+    <t>(체온 유지용)</t>
+  </si>
+  <si>
+    <t>아가방 베이직 요정 신생아 모자</t>
+  </si>
+  <si>
+    <t>에뜨와 밤부 보닛 모자</t>
+  </si>
+  <si>
+    <t>밤부베베 순면 꼬깔 골지 비니</t>
+  </si>
+  <si>
+    <t>b_cloth_5</t>
+  </si>
+  <si>
+    <t>손싸개 &amp; 발싸개 (1~2세트)</t>
+  </si>
+  <si>
+    <t>밤부베베 시그니처 신생아 손싸개 발싸개</t>
+  </si>
+  <si>
+    <t>압소바 오가닉 무형광 소프트 싸개</t>
+  </si>
+  <si>
+    <t>아가방 순면 밴딩 신생아 케어세트</t>
+  </si>
+  <si>
+    <t>b_cloth_6</t>
+  </si>
+  <si>
+    <t>신생아 양말 (1~2켤레)</t>
+  </si>
+  <si>
+    <t>마더케이 베이비 골지 발목 양말 3족</t>
+  </si>
+  <si>
+    <t>해피프린스 신생아 입체 레이스 양말</t>
+  </si>
+  <si>
+    <t>압소바 오가닉 코튼 포근 신생아 삭스</t>
+  </si>
+  <si>
+    <t>b_care_1</t>
+  </si>
+  <si>
+    <t>기저귀 &amp; 케어</t>
+  </si>
+  <si>
+    <t>가제 손수건 (10~20장)</t>
+  </si>
+  <si>
+    <t>(모유수유/얼굴닦기)</t>
+  </si>
+  <si>
+    <t>밤부베베 시그니처 거즈 손수건</t>
+  </si>
+  <si>
+    <t>밤부베베 시그니처 거즈 손수건 (10장)</t>
+  </si>
+  <si>
+    <t>마더케이 순면 엠보 손수건 (15장)</t>
+  </si>
+  <si>
+    <t>무루 땅콩 거즈 &amp; 엠보 혼합세트</t>
+  </si>
+  <si>
+    <t>b_care_2</t>
+  </si>
+  <si>
+    <t>신생아 밴드 기저귀 (소량/필요시)</t>
+  </si>
+  <si>
+    <t>(병원/조리원 제공 여부 확인)</t>
+  </si>
+  <si>
+    <t>하기스 네이처메이드 신생아용 1단계</t>
+  </si>
+  <si>
+    <t>하기스 네이처메이드 신생아용 1단계 (밴드형)</t>
+  </si>
+  <si>
+    <t>팸퍼스 스와들러 신생아 1단계</t>
+  </si>
+  <si>
+    <t>군(GOO.N) 플러스 테이프형 신생아용</t>
+  </si>
+  <si>
+    <t>b_care_3</t>
+  </si>
+  <si>
+    <t>신생아 물티슈 (1~2팩)</t>
+  </si>
+  <si>
+    <t>베베숲 시그니처 레드 에코 물티슈</t>
+  </si>
+  <si>
+    <t>베베숲 시그니처 레드 에코 물티슈 (캡형)</t>
+  </si>
+  <si>
+    <t>페넬로페 본보야지 루브르 물티슈</t>
+  </si>
+  <si>
+    <t>앙블랑 블랙 프리미엄 아기물티슈</t>
+  </si>
+  <si>
+    <t>b_care_4</t>
+  </si>
+  <si>
+    <t>기저귀 발진 크림 (필요시)</t>
+  </si>
+  <si>
+    <t>바이엘 비판텐 베이비 100g</t>
+  </si>
+  <si>
+    <t>아쿠아퍼 베이비 오인트먼트 힐링밤</t>
+  </si>
+  <si>
+    <t>수도크림(Sudocrem) 베이비 진정크림</t>
+  </si>
+  <si>
+    <t>b_care_5</t>
+  </si>
+  <si>
+    <t>아기 로션 / 바스 (필요시)</t>
+  </si>
+  <si>
+    <t>(조리원 모자동실용)</t>
+  </si>
+  <si>
+    <t>아토팜 MLE 베이비 크림 &amp; 바스</t>
+  </si>
+  <si>
+    <t>아토팜 MLE 베이비 로션 &amp; 크림 세트</t>
+  </si>
+  <si>
+    <t>피지오겔 베이비 페이셜 &amp; 바디로션</t>
+  </si>
+  <si>
+    <t>몽디에스 엑설런트 아토클렌저 &amp; 로션</t>
+  </si>
+  <si>
+    <t>b_care_6</t>
+  </si>
+  <si>
+    <t>신생아 면봉 / 손톱깎이 세트</t>
+  </si>
+  <si>
+    <t>마더케이 신생아 안심 안전 면봉 &amp; 가위</t>
+  </si>
+  <si>
+    <t>마더케이 신생아 안심 안전 면봉 &amp; 가위 4종</t>
+  </si>
+  <si>
+    <t>더블하트 신생아용 네일케어 가위 세트</t>
+  </si>
+  <si>
+    <t>말랑하니 유아 전동 손톱트리머</t>
+  </si>
+  <si>
+    <t>b_safe_1</t>
+  </si>
+  <si>
+    <t>안전 &amp; 이동</t>
+  </si>
+  <si>
+    <t>신생아 카시트 / 바구니 카시트</t>
+  </si>
+  <si>
+    <t>(차량 이동 시 필수)</t>
+  </si>
+  <si>
+    <t>다이치 원픽스 360 올인원 카시트</t>
+  </si>
+  <si>
+    <t>다이치 원픽스 360 올인원 ISOFIX 카시트</t>
+  </si>
+  <si>
+    <t>조이 아이스핀 360 회전형 카시트</t>
+  </si>
+  <si>
+    <t>맥시코시 카브리오픽스 i-Size 바구니 카시트</t>
+  </si>
+  <si>
+    <t>b_safe_2</t>
+  </si>
+  <si>
+    <t>아기 띠 / 슬링 아기띠 (필요시)</t>
+  </si>
+  <si>
+    <t>코니 턱받이 세트 메쉬 플렉스 아기띠</t>
+  </si>
+  <si>
+    <t>베이비뵨 미니 에어 메쉬 신생아 아기띠</t>
+  </si>
+  <si>
+    <t>포그내 맥스 올인원 힙시트 아기띠</t>
+  </si>
+  <si>
+    <t>b_safe_3</t>
+  </si>
+  <si>
+    <t>쪽쪽이 / 노리개 젖꼭지 (1개)</t>
+  </si>
+  <si>
+    <t>(소아과 진료/이동용)</t>
+  </si>
+  <si>
+    <t>빕스(BIBS) 데 루스 천연고무 쪽쪽이</t>
+  </si>
+  <si>
+    <t>모윰 올실리콘 마카롱 신생아 쪽쪽이</t>
+  </si>
+  <si>
+    <t>아벤트 울트라에어 실리콘 노리개</t>
+  </si>
+  <si>
+    <t>b_safe_4</t>
+  </si>
+  <si>
+    <t>신생아 분유 / 젖병 1개 (필요시)</t>
+  </si>
+  <si>
+    <t>(장거리 이동 시 대비)</t>
+  </si>
+  <si>
+    <t>압타밀 프로푸트라 프레 독일 내수용</t>
+  </si>
+  <si>
+    <t>압타밀 프로푸트라 프레 독일 내수용 (800g)</t>
+  </si>
+  <si>
+    <t>더블하트 모유실감 소형 젖병 160ml</t>
+  </si>
+  <si>
+    <t>남양 아이엠마더 1단계 액상분유 키트</t>
+  </si>
+  <si>
+    <t>g_doc_1</t>
+  </si>
+  <si>
+    <t>보호자 &amp; 공통</t>
+  </si>
+  <si>
+    <t>필수 서류 &amp; 결제</t>
+  </si>
+  <si>
+    <t>산모 신분증 &amp; 결제 카드</t>
+  </si>
+  <si>
+    <t>(국민행복카드 등)</t>
+  </si>
+  <si>
+    <t>심플 포켓 카드지갑 신분증 홀더</t>
+  </si>
+  <si>
+    <t>심플 포켓 카드지갑 신분증 케이스</t>
+  </si>
+  <si>
+    <t>슬림 RFID 차단 가죽 카드케이스</t>
+  </si>
+  <si>
+    <t>다이어리형 산모수첩 카드 보관 파우치</t>
+  </si>
+  <si>
+    <t>g_doc_2</t>
+  </si>
+  <si>
+    <t>산모수첩 (임산부 수첩)</t>
+  </si>
+  <si>
+    <t>(병원 진료 기록용)</t>
+  </si>
+  <si>
+    <t>오둥이 산모수첩 프리미엄 커버 파우치</t>
+  </si>
+  <si>
+    <t>마더케이 초음파 앨범 &amp; 수첩 바인더</t>
+  </si>
+  <si>
+    <t>디어마이베이비 패브릭 산모수첩 케이스</t>
+  </si>
+  <si>
+    <t>g_doc_3</t>
+  </si>
+  <si>
+    <t>진료기록부 / 소견서 (해당자)</t>
+  </si>
+  <si>
+    <t>(전원 산모 및 기저질환자)</t>
+  </si>
+  <si>
+    <t>투명 L홀더 A4 서류 보관 바인더</t>
+  </si>
+  <si>
+    <t>투명 L홀더 A4 서류 보관 바인더 (10P)</t>
+  </si>
+  <si>
+    <t>방수 지퍼 파일포켓 서류 파우치</t>
+  </si>
+  <si>
+    <t>아코디언 멀티 포켓 서류정리함</t>
+  </si>
+  <si>
+    <t>g_doc_4</t>
+  </si>
+  <si>
+    <t>조리원 계약서 (조리원 이용자)</t>
+  </si>
+  <si>
+    <t>(입소 확인 및 잔금 결제용)</t>
+  </si>
+  <si>
+    <t>지퍼형 3단 패브릭 서류 파일 바인더</t>
+  </si>
+  <si>
+    <t>슬림 마그네틱 포켓 바인더</t>
+  </si>
+  <si>
+    <t>오피스 서류 지퍼백 멀티백</t>
+  </si>
+  <si>
+    <t>g_dad_1</t>
+  </si>
+  <si>
+    <t>보호자 용품</t>
+  </si>
+  <si>
+    <t>보호자 편한 옷 &amp; 속옷 (2~3벌)</t>
+  </si>
+  <si>
+    <t>탑텐 쿨에어 컴포트 라운드티 &amp; 반바지</t>
+  </si>
+  <si>
+    <t>탑텐 쿨에어 컴포트 라운드티 &amp; 반바지 홈웨어</t>
+  </si>
+  <si>
+    <t>스파오 이지웨어 순면 파자마 세트</t>
+  </si>
+  <si>
+    <t>유니클로 에어리즘 심리스 크루넥 &amp; 조거팬츠</t>
+  </si>
+  <si>
+    <t>g_dad_2</t>
+  </si>
+  <si>
+    <t>보호자 세면도구 &amp; 면도기</t>
+  </si>
+  <si>
+    <t>질레트 프로글라이드 플렉스볼 여행용 키트</t>
+  </si>
+  <si>
+    <t>질레트 프로글라이드 플렉스볼 여행용 세트</t>
+  </si>
+  <si>
+    <t>도루코 페이스7 휴대용 면도기 &amp; 폼</t>
+  </si>
+  <si>
+    <t>필립스 휴대용 전동면도기 미니 1000시리즈</t>
+  </si>
+  <si>
+    <t>g_dad_3</t>
+  </si>
+  <si>
+    <t>보호자용 실내 슬리퍼 (1켤레)</t>
+  </si>
+  <si>
+    <t>삼선 EVA 극경량 쿠션 실내 슬리퍼</t>
+  </si>
+  <si>
+    <t>무인양품 면 테리 룸슈즈</t>
+  </si>
+  <si>
+    <t>아치형 미끄럼 방지 욕실 실내 슬리퍼</t>
+  </si>
+  <si>
+    <t>g_dad_4</t>
+  </si>
+  <si>
+    <t>보호자용 침구 / 이불 (필요시)</t>
+  </si>
+  <si>
+    <t>(보호자 침구 미제공 병원 확인)</t>
+  </si>
+  <si>
+    <t>자주(JAJU) 접이식 극세사 캠핑 무릎담요</t>
+  </si>
+  <si>
+    <t>데코뷰 사계절 차렵이불 단품</t>
+  </si>
+  <si>
+    <t>휴대용 에어 목베개 &amp; 안대 귀마개 세트</t>
+  </si>
+  <si>
+    <t>g_life_1</t>
+  </si>
+  <si>
+    <t>생활 &amp; 편의 도구</t>
+  </si>
+  <si>
+    <t>구부러지는 꺾임 빨대 / 텀블러</t>
+  </si>
+  <si>
+    <t>(누워서 수분 섭취 시 필수)</t>
+  </si>
+  <si>
+    <t>아띠빠스 실리콘 꺾임 빨대 텀블러 세트</t>
+  </si>
+  <si>
+    <t>글라스락 셰프토프 보온보냉 스트로우 텀블러</t>
+  </si>
+  <si>
+    <t>다이소 개별포장 주름 자바라 빨대 (100입)</t>
+  </si>
+  <si>
+    <t>g_life_2</t>
+  </si>
+  <si>
+    <t>생수 및 보온 보냉병</t>
+  </si>
+  <si>
+    <t>스탠리 클래식 진공 보틀 텀블러 1L</t>
+  </si>
+  <si>
+    <t>써모스 데일리 원터치 보온병 500ml</t>
+  </si>
+  <si>
+    <t>락앤락 메트로 머그 텀블러 600ml</t>
+  </si>
+  <si>
+    <t>g_life_3</t>
+  </si>
+  <si>
+    <t>스마트폰 충전기 &amp; 멀티탭 (3~5구)</t>
+  </si>
+  <si>
+    <t>(콘센트 거리 먼 경우 대비 2m 이상)</t>
+  </si>
+  <si>
+    <t>벨킨 부스트업 초고속 3in1 멀티 충전기</t>
+  </si>
+  <si>
+    <t>샤오미 멀티탭 3구 USB 3포트 (2m)</t>
+  </si>
+  <si>
+    <t>신지모루 60W C타입 3미터 롱 케이블</t>
+  </si>
+  <si>
+    <t>g_life_4</t>
+  </si>
+  <si>
+    <t>휴대폰 거치대 (자바라/스탠드)</t>
+  </si>
+  <si>
+    <t>(수유/침대 누워서 영상 시청)</t>
+  </si>
+  <si>
+    <t>신지모루 탄소강 침대 자바라 거치대</t>
+  </si>
+  <si>
+    <t>루나틱 침대 헤드 클립 스마트폰 거치대</t>
+  </si>
+  <si>
+    <t>베이스어스 360도 회전 탁상용 태블릿 거치대</t>
+  </si>
+  <si>
+    <t>g_life_5</t>
+  </si>
+  <si>
+    <t>두루마리 휴지 &amp; 갑티슈 (각 1개)</t>
+  </si>
+  <si>
+    <t>크리넥스 3겹 데코앤소프트 미용티슈</t>
+  </si>
+  <si>
+    <t>크리넥스 3겹 데코앤소프트 미용티슈 3입</t>
+  </si>
+  <si>
+    <t>코디 에코소프트 롤화장지 30롤</t>
+  </si>
+  <si>
+    <t>모나리자 자연이좋은 무형광 티슈</t>
+  </si>
+  <si>
+    <t>g_life_6</t>
+  </si>
+  <si>
+    <t>지퍼백 / 비닐봉투 (크기별 5~10장)</t>
+  </si>
+  <si>
+    <t>(빨랫감 분리 및 물품 보관)</t>
+  </si>
+  <si>
+    <t>지플락 스마트 지퍼백 냉동/냉장 혼합팩</t>
+  </si>
+  <si>
+    <t>크린랩 손잡이형 위생백 대형 100매</t>
+  </si>
+  <si>
+    <t>마더케이 에코 안심 항균 지퍼백 세트</t>
+  </si>
+  <si>
+    <t>g_life_7</t>
+  </si>
+  <si>
+    <t>손 소독제 &amp; 알코올 스왑</t>
+  </si>
+  <si>
+    <t>유한양행 알코올 스왑 100매 개별포장</t>
+  </si>
+  <si>
+    <t>데톨 오리지널 손소독 젤 200ml</t>
+  </si>
+  <si>
+    <t>닥터스에이 겔형 에탄올 손소독제</t>
+  </si>
+  <si>
+    <t>g_life_8</t>
+  </si>
+  <si>
+    <t>멀티 비타민 &amp; 철분제 &amp; 유산균</t>
+  </si>
+  <si>
+    <t>(산후 회복 및 수유 영양 보충)</t>
   </si>
   <si>
     <t>솔가 철분 25mg 식물성 캡슐 (90일분)</t>
@@ -671,718 +1250,7 @@
     <t>닥터에디션 맘스 프로바이오틱스 유산균</t>
   </si>
   <si>
-    <t>종근당건강 락토핏 생유산균 맘스</t>
-  </si>
-  <si>
-    <t>b_cloth_1</t>
-  </si>
-  <si>
-    <t>신생아 용품</t>
-  </si>
-  <si>
-    <t>의류 &amp; 패브릭</t>
-  </si>
-  <si>
-    <t>배냇저고리 / 배냇수트 (1~2벌)</t>
-  </si>
-  <si>
-    <t>압소바 순면 배냇저고리 2종 세트</t>
-  </si>
-  <si>
-    <t>아가방 오가닉 코튼 배냇가운</t>
-  </si>
-  <si>
-    <t>에뜨와 텐셀 소프트 신생아 배냇</t>
-  </si>
-  <si>
-    <t>b_cloth_2</t>
-  </si>
-  <si>
-    <t>신생아 속싸개 (1~2장)</t>
-  </si>
-  <si>
-    <t>스와들업 오리지널 속싸개</t>
-  </si>
-  <si>
-    <t>스와들업 오리지널 속싸개 (기적의 속싸개)</t>
-  </si>
-  <si>
-    <t>말랑하니 스와들 스트랩</t>
-  </si>
-  <si>
-    <t>보네스트 밤부 모달 스와들 블랭킷</t>
-  </si>
-  <si>
-    <t>b_cloth_3</t>
-  </si>
-  <si>
-    <t>신생아 겉싸개 (1장)</t>
-  </si>
-  <si>
-    <t>(계절 고려)</t>
-  </si>
-  <si>
-    <t>아가방 베이직 사계절 겉싸개</t>
-  </si>
-  <si>
-    <t>밍크뮤 애니멀 자수 신생아 겉싸개</t>
-  </si>
-  <si>
-    <t>압소바 퀼팅 보온 겉싸개</t>
-  </si>
-  <si>
-    <t>b_cloth_4</t>
-  </si>
-  <si>
-    <t>신생아 모자 (1~2개)</t>
-  </si>
-  <si>
-    <t>(체온 유지용)</t>
-  </si>
-  <si>
-    <t>아가방 베이직 요정 신생아 모자</t>
-  </si>
-  <si>
-    <t>에뜨와 밤부 보닛 모자</t>
-  </si>
-  <si>
-    <t>밤부베베 순면 꼬깔 골지 비니</t>
-  </si>
-  <si>
-    <t>b_cloth_5</t>
-  </si>
-  <si>
-    <t>손싸개 &amp; 발싸개 (1~2세트)</t>
-  </si>
-  <si>
-    <t>밤부베베 시그니처 신생아 손싸개 발싸개</t>
-  </si>
-  <si>
-    <t>압소바 오가닉 무형광 소프트 싸개</t>
-  </si>
-  <si>
-    <t>아가방 순면 밴딩 신생아 케어세트</t>
-  </si>
-  <si>
-    <t>b_cloth_6</t>
-  </si>
-  <si>
-    <t>신생아 양말 (1~2켤레)</t>
-  </si>
-  <si>
-    <t>마더케이 베이비 골지 발목 양말 3족</t>
-  </si>
-  <si>
-    <t>해피프린스 신생아 입체 레이스 양말</t>
-  </si>
-  <si>
-    <t>압소바 오가닉 코튼 포근 신생아 삭스</t>
-  </si>
-  <si>
-    <t>b_care_1</t>
-  </si>
-  <si>
-    <t>기저귀 &amp; 케어</t>
-  </si>
-  <si>
-    <t>가제 손수건 (10~20장)</t>
-  </si>
-  <si>
-    <t>(모유수유/얼굴닦기)</t>
-  </si>
-  <si>
-    <t>밤부베베 시그니처 거즈 손수건</t>
-  </si>
-  <si>
-    <t>밤부베베 시그니처 거즈 손수건 (10장)</t>
-  </si>
-  <si>
-    <t>마더케이 순면 엠보 손수건 (15장)</t>
-  </si>
-  <si>
-    <t>무루 땅콩 거즈 &amp; 엠보 혼합세트</t>
-  </si>
-  <si>
-    <t>b_care_2</t>
-  </si>
-  <si>
-    <t>신생아 밴드 기저귀 (소량/필요시)</t>
-  </si>
-  <si>
-    <t>(병원/조리원 제공 여부 확인)</t>
-  </si>
-  <si>
-    <t>하기스 네이처메이드 신생아용 1단계</t>
-  </si>
-  <si>
-    <t>하기스 네이처메이드 신생아용 1단계 (밴드형)</t>
-  </si>
-  <si>
-    <t>팸퍼스 스와들러 신생아 1단계</t>
-  </si>
-  <si>
-    <t>군(GOO.N) 플러스 테이프형 신생아용</t>
-  </si>
-  <si>
-    <t>b_care_3</t>
-  </si>
-  <si>
-    <t>신생아 물티슈 (1~2팩)</t>
-  </si>
-  <si>
-    <t>베베숲 시그니처 레드 에코 물티슈</t>
-  </si>
-  <si>
-    <t>베베숲 시그니처 레드 에코 물티슈 (캡형)</t>
-  </si>
-  <si>
-    <t>페넬로페 본보야지 루브르 물티슈</t>
-  </si>
-  <si>
-    <t>앙블랑 블랙 프리미엄 아기물티슈</t>
-  </si>
-  <si>
-    <t>b_care_4</t>
-  </si>
-  <si>
-    <t>기저귀 발진 크림 (필요시)</t>
-  </si>
-  <si>
-    <t>바이엘 비판텐 베이비 100g</t>
-  </si>
-  <si>
-    <t>아쿠아퍼 베이비 오인트먼트 힐링밤</t>
-  </si>
-  <si>
-    <t>수도크림(Sudocrem) 베이비 진정크림</t>
-  </si>
-  <si>
-    <t>b_care_5</t>
-  </si>
-  <si>
-    <t>아기 로션 / 바스 (필요시)</t>
-  </si>
-  <si>
-    <t>(조리원 모자동실용)</t>
-  </si>
-  <si>
-    <t>아토팜 MLE 베이비 크림 &amp; 바스</t>
-  </si>
-  <si>
-    <t>아토팜 MLE 베이비 로션 &amp; 크림 세트</t>
-  </si>
-  <si>
-    <t>피지오겔 베이비 페이셜 &amp; 바디로션</t>
-  </si>
-  <si>
-    <t>몽디에스 엑설런트 아토클렌저 &amp; 로션</t>
-  </si>
-  <si>
-    <t>b_care_6</t>
-  </si>
-  <si>
-    <t>신생아 면봉 / 손톱깎이 세트</t>
-  </si>
-  <si>
-    <t>마더케이 신생아 안심 안전 면봉 &amp; 가위</t>
-  </si>
-  <si>
-    <t>마더케이 신생아 안심 안전 면봉 &amp; 가위 4종</t>
-  </si>
-  <si>
-    <t>더블하트 신생아용 네일케어 가위 세트</t>
-  </si>
-  <si>
-    <t>말랑하니 유아 전동 손톱트리머</t>
-  </si>
-  <si>
-    <t>b_care_dday</t>
-  </si>
-  <si>
-    <t>디데이달력 (모자동실 성장 촬영용)</t>
-  </si>
-  <si>
-    <t>1개</t>
-  </si>
-  <si>
-    <t>(모자동실 기념사진 및 성장 기록)</t>
-  </si>
-  <si>
-    <t>말랑하니 아기 디데이달력 우드 스탠드형</t>
-  </si>
-  <si>
-    <t>달콤한기억 신생아 성장 디데이 캘린더</t>
-  </si>
-  <si>
-    <t>리틀포레스트 원목 감성 디데이달력</t>
-  </si>
-  <si>
-    <t>b_care_focusbook</t>
-  </si>
-  <si>
-    <t>초점책 (모자동실 흑백/컬러 초점책)</t>
-  </si>
-  <si>
-    <t>1권</t>
-  </si>
-  <si>
-    <t>(신생아 시각 발달 놀이용)</t>
-  </si>
-  <si>
-    <t>애플비 아기 초점책 병풍형 (흑백+컬러)</t>
-  </si>
-  <si>
-    <t>블루래빗 첫 두뇌계발 초점 플래시북</t>
-  </si>
-  <si>
-    <t>튤립사운드북 흑백 초점 병풍 세트</t>
-  </si>
-  <si>
-    <t>b_care_nightlight</t>
-  </si>
-  <si>
-    <t>수유등 (모자동실/조리원 밤 수유용)</t>
-  </si>
-  <si>
-    <t>(조도 조절 가능한 수유 무드등)</t>
-  </si>
-  <si>
-    <t>말랑하니 아기 무드등 LED 터치 수유등</t>
-  </si>
-  <si>
-    <t>바깃(Bagit) 모션인식 센서 터치 수유등</t>
-  </si>
-  <si>
-    <t>아르떼미데 톨로메오 미니 핀차 수유등</t>
-  </si>
-  <si>
-    <t>b_safe_1</t>
-  </si>
-  <si>
-    <t>안전 &amp; 이동</t>
-  </si>
-  <si>
-    <t>신생아 카시트 / 바구니 카시트</t>
-  </si>
-  <si>
-    <t>(차량 이동 시 필수)</t>
-  </si>
-  <si>
-    <t>다이치 원픽스 360 올인원 카시트</t>
-  </si>
-  <si>
-    <t>다이치 원픽스 360 올인원 ISOFIX 카시트</t>
-  </si>
-  <si>
-    <t>조이 아이스핀 360 회전형 카시트</t>
-  </si>
-  <si>
-    <t>맥시코시 카브리오픽스 i-Size 바구니 카시트</t>
-  </si>
-  <si>
-    <t>b_safe_2</t>
-  </si>
-  <si>
-    <t>아기 띠 / 슬링 아기띠 (필요시)</t>
-  </si>
-  <si>
-    <t>코니 턱받이 세트 메쉬 플렉스 아기띠</t>
-  </si>
-  <si>
-    <t>베이비뵨 미니 에어 메쉬 신생아 아기띠</t>
-  </si>
-  <si>
-    <t>포그내 맥스 올인원 힙시트 아기띠</t>
-  </si>
-  <si>
-    <t>b_safe_3</t>
-  </si>
-  <si>
-    <t>쪽쪽이 / 노리개 젖꼭지 (1개)</t>
-  </si>
-  <si>
-    <t>(소아과 진료/이동용)</t>
-  </si>
-  <si>
-    <t>빕스(BIBS) 데 루스 천연고무 쪽쪽이</t>
-  </si>
-  <si>
-    <t>모윰 올실리콘 마카롱 신생아 쪽쪽이</t>
-  </si>
-  <si>
-    <t>아벤트 울트라에어 실리콘 노리개</t>
-  </si>
-  <si>
-    <t>b_safe_4</t>
-  </si>
-  <si>
-    <t>신생아 분유 / 젖병 1개 (필요시)</t>
-  </si>
-  <si>
-    <t>(장거리 이동 시 대비)</t>
-  </si>
-  <si>
-    <t>압타밀 프로푸트라 프레 독일 내수용</t>
-  </si>
-  <si>
-    <t>압타밀 프로푸트라 프레 독일 내수용 (800g)</t>
-  </si>
-  <si>
-    <t>더블하트 모유실감 소형 젖병 160ml</t>
-  </si>
-  <si>
-    <t>남양 아이엠마더 1단계 액상분유 키트</t>
-  </si>
-  <si>
-    <t>g_doc_1</t>
-  </si>
-  <si>
-    <t>보호자 &amp; 공통</t>
-  </si>
-  <si>
-    <t>필수 서류 &amp; 결제</t>
-  </si>
-  <si>
-    <t>산모 신분증 &amp; 결제 카드</t>
-  </si>
-  <si>
-    <t>(국민행복카드 등)</t>
-  </si>
-  <si>
-    <t>심플 포켓 카드지갑 신분증 홀더</t>
-  </si>
-  <si>
-    <t>심플 포켓 카드지갑 신분증 케이스</t>
-  </si>
-  <si>
-    <t>슬림 RFID 차단 가죽 카드케이스</t>
-  </si>
-  <si>
-    <t>다이어리형 산모수첩 카드 보관 파우치</t>
-  </si>
-  <si>
-    <t>g_doc_2</t>
-  </si>
-  <si>
-    <t>산모수첩 (임산부 수첩)</t>
-  </si>
-  <si>
-    <t>(병원 진료 기록용)</t>
-  </si>
-  <si>
-    <t>오둥이 산모수첩 프리미엄 커버 파우치</t>
-  </si>
-  <si>
-    <t>마더케이 초음파 앨범 &amp; 수첩 바인더</t>
-  </si>
-  <si>
-    <t>디어마이베이비 패브릭 산모수첩 케이스</t>
-  </si>
-  <si>
-    <t>g_doc_3</t>
-  </si>
-  <si>
-    <t>진료기록부 / 소견서 (해당자)</t>
-  </si>
-  <si>
-    <t>(전원 산모 및 기저질환자)</t>
-  </si>
-  <si>
-    <t>투명 L홀더 A4 서류 보관 바인더</t>
-  </si>
-  <si>
-    <t>투명 L홀더 A4 서류 보관 바인더 (10P)</t>
-  </si>
-  <si>
-    <t>방수 지퍼 파일포켓 서류 파우치</t>
-  </si>
-  <si>
-    <t>아코디언 멀티 포켓 서류정리함</t>
-  </si>
-  <si>
-    <t>g_doc_4</t>
-  </si>
-  <si>
-    <t>조리원 계약서 (조리원 이용자)</t>
-  </si>
-  <si>
-    <t>(입소 확인 및 잔금 결제용)</t>
-  </si>
-  <si>
-    <t>지퍼형 3단 패브릭 서류 파일 바인더</t>
-  </si>
-  <si>
-    <t>슬림 마그네틱 포켓 바인더</t>
-  </si>
-  <si>
-    <t>오피스 서류 지퍼백 멀티백</t>
-  </si>
-  <si>
-    <t>g_dad_1</t>
-  </si>
-  <si>
-    <t>보호자 용품</t>
-  </si>
-  <si>
-    <t>보호자 편한 옷 &amp; 속옷 (2~3벌)</t>
-  </si>
-  <si>
-    <t>탑텐 쿨에어 컴포트 라운드티 &amp; 반바지</t>
-  </si>
-  <si>
-    <t>탑텐 쿨에어 컴포트 라운드티 &amp; 반바지 홈웨어</t>
-  </si>
-  <si>
-    <t>스파오 이지웨어 순면 파자마 세트</t>
-  </si>
-  <si>
-    <t>유니클로 에어리즘 심리스 크루넥 &amp; 조거팬츠</t>
-  </si>
-  <si>
-    <t>g_dad_2</t>
-  </si>
-  <si>
-    <t>보호자(아빠) 세면용품 &amp; 면도기</t>
-  </si>
-  <si>
-    <t>(칫솔·치약·면도기·세안제)</t>
-  </si>
-  <si>
-    <t>질레트 프로글라이드 플렉스볼 여행용 키트</t>
-  </si>
-  <si>
-    <t>질레트 프로글라이드 플렉스볼 여행용 세트</t>
-  </si>
-  <si>
-    <t>도루코 페이스7 휴대용 면도기 &amp; 폼</t>
-  </si>
-  <si>
-    <t>필립스 휴대용 전동면도기 미니 1000시리즈</t>
-  </si>
-  <si>
-    <t>g_dad_3</t>
-  </si>
-  <si>
-    <t>보호자용 실내 슬리퍼 (1켤레)</t>
-  </si>
-  <si>
-    <t>삼선 EVA 극경량 쿠션 실내 슬리퍼</t>
-  </si>
-  <si>
-    <t>무인양품 면 테리 룸슈즈</t>
-  </si>
-  <si>
-    <t>아치형 미끄럼 방지 욕실 실내 슬리퍼</t>
-  </si>
-  <si>
-    <t>g_dad_4</t>
-  </si>
-  <si>
-    <t>아빠용 침구류 (이불·베개 / 필요시)</t>
-  </si>
-  <si>
-    <t>(병원 제공 여부 확인 필요)</t>
-  </si>
-  <si>
-    <t>자주(JAJU) 접이식 극세사 캠핑 무릎담요</t>
-  </si>
-  <si>
-    <t>데코뷰 사계절 차렵이불 단품</t>
-  </si>
-  <si>
-    <t>휴대용 에어 목베개 &amp; 안대 귀마개 세트</t>
-  </si>
-  <si>
-    <t>g_life_1</t>
-  </si>
-  <si>
-    <t>생활 &amp; 편의 도구</t>
-  </si>
-  <si>
-    <t>텀블러 (보온/보냉용)</t>
-  </si>
-  <si>
-    <t>(손잡이형/빨대 호환)</t>
-  </si>
-  <si>
-    <t>스탠리 퀜처 H2.0 진공 텀블러</t>
-  </si>
-  <si>
-    <t>스탠리 퀜처 H2.0 플로우헤븐 진공 텀블러 887ml</t>
-  </si>
-  <si>
-    <t>글라스락 셰프토프 보온보냉 스트로우 텀블러</t>
-  </si>
-  <si>
-    <t>다이소 개별포장 주름 자바라 빨대 (100입)</t>
-  </si>
-  <si>
-    <t>g_life_straw</t>
-  </si>
-  <si>
-    <t>주름빨대 (구부러지는 꺾임 빨대)</t>
-  </si>
-  <si>
-    <t>1팩</t>
-  </si>
-  <si>
-    <t>(누워서 수분 섭취 시 필수)</t>
-  </si>
-  <si>
-    <t>다이소 개별포장 주름 자바라 꺾임빨대 (100입)</t>
-  </si>
-  <si>
-    <t>아띠빠스 실리콘 세척 가능 안심 꺾임 빨대</t>
-  </si>
-  <si>
-    <t>마더케이 일회용 꺾임 위생 빨대 60P</t>
-  </si>
-  <si>
-    <t>g_life_2</t>
-  </si>
-  <si>
-    <t>생수 및 보온 보냉병</t>
-  </si>
-  <si>
-    <t>스탠리 클래식 진공 보틀 텀블러 1L</t>
-  </si>
-  <si>
-    <t>써모스 데일리 원터치 보온병 500ml</t>
-  </si>
-  <si>
-    <t>락앤락 메트로 머그 텀블러 600ml</t>
-  </si>
-  <si>
-    <t>g_life_4</t>
-  </si>
-  <si>
-    <t>휴대폰 충전기 (긴 케이블 권장)</t>
-  </si>
-  <si>
-    <t>(침대 콘센트 거리 대비 2m 이상)</t>
-  </si>
-  <si>
-    <t>벨킨 부스트업 초고속 3in1 멀티 충전기</t>
-  </si>
-  <si>
-    <t>신지모루 60W C타입 3미터 롱 케이블</t>
-  </si>
-  <si>
-    <t>삼성전자 45W 초고속 충전기 키트</t>
-  </si>
-  <si>
-    <t>g_life_multi</t>
-  </si>
-  <si>
-    <t>멀티탭 (3~5구, 긴 줄)</t>
-  </si>
-  <si>
-    <t>(산모 및 보호자 기기 동시 충전)</t>
-  </si>
-  <si>
-    <t>현대일렉트릭 서버탭 안전 멀티탭 4구 (3m)</t>
-  </si>
-  <si>
-    <t>샤오미 멀티탭 3구 USB 3포트 (2m)</t>
-  </si>
-  <si>
-    <t>현대일렉트릭 고용량 개별 멀티탭 4구 (3m)</t>
-  </si>
-  <si>
-    <t>신성 개별 스위치 안전 멀티탭 5구</t>
-  </si>
-  <si>
-    <t>휴대폰 거치대 (자바라/스탠드)</t>
-  </si>
-  <si>
-    <t>(수유/침대 누워서 영상 시청)</t>
-  </si>
-  <si>
-    <t>신지모루 탄소강 침대 자바라 거치대</t>
-  </si>
-  <si>
-    <t>루나틱 침대 헤드 클립 스마트폰 거치대</t>
-  </si>
-  <si>
-    <t>베이스어스 360도 회전 탁상용 태블릿 거치대</t>
-  </si>
-  <si>
-    <t>g_life_5</t>
-  </si>
-  <si>
-    <t>두루마리 휴지 &amp; 갑티슈 (각 1개)</t>
-  </si>
-  <si>
-    <t>크리넥스 3겹 데코앤소프트 미용티슈</t>
-  </si>
-  <si>
-    <t>크리넥스 3겹 데코앤소프트 미용티슈 3입</t>
-  </si>
-  <si>
-    <t>코디 에코소프트 롤화장지 30롤</t>
-  </si>
-  <si>
-    <t>모나리자 자연이좋은 무형광 티슈</t>
-  </si>
-  <si>
-    <t>g_life_6</t>
-  </si>
-  <si>
-    <t>지퍼백 / 비닐봉투 (크기별 5~10장)</t>
-  </si>
-  <si>
-    <t>(빨랫감 분리 및 물품 보관)</t>
-  </si>
-  <si>
-    <t>지플락 스마트 지퍼백 냉동/냉장 혼합팩</t>
-  </si>
-  <si>
-    <t>크린랩 손잡이형 위생백 대형 100매</t>
-  </si>
-  <si>
-    <t>마더케이 에코 안심 항균 지퍼백 세트</t>
-  </si>
-  <si>
-    <t>g_life_7</t>
-  </si>
-  <si>
-    <t>손세정제 (휴대용 손소독제)</t>
-  </si>
-  <si>
-    <t>(신생아 접촉 전 손 소독)</t>
-  </si>
-  <si>
-    <t>아이깨끗해 휴대용 거품형 손세정제</t>
-  </si>
-  <si>
-    <t>아이깨끗해 휴대용 거품형 손세정제 50ml</t>
-  </si>
-  <si>
-    <t>유한양행 알코올 스왑 100매 개별포장</t>
-  </si>
-  <si>
-    <t>데톨 오리지널 손소독 젤 200ml</t>
-  </si>
-  <si>
-    <t>g_life_mask</t>
-  </si>
-  <si>
-    <t>일회용마스크 (KF94/비말 차단, 1팩)</t>
-  </si>
-  <si>
-    <t>(병원·조리원 방역 및 면회용)</t>
-  </si>
-  <si>
-    <t>아에르 KF94 피크 비말차단 마스크</t>
-  </si>
-  <si>
-    <t>아에르 KF94 피크 라이트 마스크 50매</t>
-  </si>
-  <si>
-    <t>크리넥스 데일리 비말차단 입체형 마스크 50매</t>
-  </si>
-  <si>
-    <t>웰킵스 뉴스마트 황사방역마스크 KF94 30매</t>
+    <t>종근당건강 락토핏 생유산균 베베/맘스</t>
   </si>
   <si>
     <t>g_life_9</t>
@@ -2138,10 +2006,10 @@
     <t>todo_c_4</t>
   </si>
   <si>
-    <t>BCG 결핵 예방접종 예약</t>
-  </si>
-  <si>
-    <t>피내용(보건소 무료) 또는 경피용 소아과 접종 예약</t>
+    <t>?뭺 [?덈갑?묒쥌] BCG(寃고빑) ?묒쥌 ?덉빟 諛??묒쥌 (?앺썑 4二??대궡)</t>
+  </si>
+  <si>
+    <t>?쇰궡??蹂닿굔??臾대즺, 二쇱궗?? vs 寃쏀뵾???좊즺, ?꾩옣?? ?ъ쟾 ?좏깮 諛?愿??蹂닿굔???뚯븘怨??ъ쟾 ?덉빟</t>
   </si>
   <si>
     <t>todo_c_5</t>
@@ -2181,6 +2049,75 @@
   </si>
   <si>
     <t>국민건강보험공단 건강iN 문진표 작성 후 소아과 방문</t>
+  </si>
+  <si>
+    <t>todo_b_29</t>
+  </si>
+  <si>
+    <t>1. 異쒖궛 ??(以鍮꾧린)</t>
+  </si>
+  <si>
+    <t>#遺遺</t>
+  </si>
+  <si>
+    <t>?뭺 [?덈갑?묒쥌] 諛깆씪??Tdap) ?묒쥌 (?꾩떊 27~36二?沅뚯옣)</t>
+  </si>
+  <si>
+    <t>?좎깮??諛깆씪???꾩뿼 ?덈갑???꾪빐 ?곕え 諛??⑦렪, ?묒쑁??議곕?紐? ?숈떆 ?묒쥌 沅뚯옣 (?앺썑 2媛쒖썡 ????껜 ?꾨떖)</t>
+  </si>
+  <si>
+    <t>todo_b_30</t>
+  </si>
+  <si>
+    <t>#?꾨쭏</t>
+  </si>
+  <si>
+    <t>?뭺 [?덈갑?묒쥌] ?명뵆猷⑥뿏???낃컧) ?묒쥌 (?꾩떊 二쇱닔 臾닿?)</t>
+  </si>
+  <si>
+    <t>?꾩궛遺 援?? 臾대즺 ?덈갑?묒쥌 吏???ъ뾽 ???(吏???섎즺湲곌? 諛?蹂닿굔?뚯뿉??臾대즺 ?묒쥌 媛??</t>
+  </si>
+  <si>
+    <t>todo_h_5</t>
+  </si>
+  <si>
+    <t>2. 蹂묒썝 (?낆썝 諛?遺꾨쭔湲?</t>
+  </si>
+  <si>
+    <t>?뭺 [?덈갑?묒쥌] ?좎깮??B??媛꾩뿼 1李??묒쥌 ?뺤씤 (異쒖깮 吏곹썑)</t>
+  </si>
+  <si>
+    <t>異쒖깮 ??24?쒓컙 ?대궡 遺꾨쭔 蹂묒썝?먯꽌 湲곕낯 ?묒쥌 吏꾪뻾 (?꾧린?섏꺽 ?묒쥌 湲곕줉 ?뺤씤)</t>
+  </si>
+  <si>
+    <t>todo_f_4</t>
+  </si>
+  <si>
+    <t>4. 媛??(吏?蹂듦? 諛?珥덇린 ?≪븘湲?</t>
+  </si>
+  <si>
+    <t>?뭺 [?덈갑?묒쥌] B??媛꾩뿼 2李??묒쥌 (?앺썑 1媛쒖썡)</t>
+  </si>
+  <si>
+    <t>?앺썑 1媛쒖썡 ?뚯븘怨?諛⑸Ц ?묒쥌 (?앺썑 4~6二?1李??곸쑀??嫄닿컯寃吏꾧낵 ?④퍡 諛⑸Ц 異붿쿇)</t>
+  </si>
+  <si>
+    <t>todo_f_5</t>
+  </si>
+  <si>
+    <t>?뭺 [?덈갑?묒쥌] 5醫??쇳빀諛깆떊(DTaP쨌IPV쨌Hib쨌PCV) 1李?(?앺썑 2媛쒖썡)</t>
+  </si>
+  <si>
+    <t>?뷀봽?뚮━???뚯긽??諛깆씪???뚯븘留덈퉬/?뚯닔留됱뿼/?먮졃援ш퇏 援?? 臾대즺 ?묒쥌 (?묒쥌???鍮??댁뿴???ъ쟾 以鍮?</t>
+  </si>
+  <si>
+    <t>todo_f_6</t>
+  </si>
+  <si>
+    <t>?뭺 [?덈갑?묒쥌] 濡쒗?諛붿씠?ъ뒪 1李??묒쥌 (?앺썑 2媛쒖썡)</t>
+  </si>
+  <si>
+    <t>援?? 臾대즺 吏??癒밸뒗 ???뺥깭). 濡쒗?由?뒪(2???꾨즺) vs 濡쒗???3???꾨즺) 以??좏깮 ????李⑥닔 ?숈씪 諛깆떊 ?좎?</t>
   </si>
   <si>
     <t>지역구분</t>
@@ -2983,20 +2920,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{608A9FB4-C32C-450F-98B0-5FE8427DCDD2}">
-  <dimension ref="A1:N70"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B05096-B3BF-4CC9-8637-6A0EB4BC7BB7}">
+  <dimension ref="A1:N64"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="44.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="43.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="45.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="42.875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="43.125" bestFit="1" customWidth="1"/>
     <col min="12" max="14" width="19.375" bestFit="1" customWidth="1"/>
   </cols>
@@ -3058,25 +2995,28 @@
       <c r="D2" t="s">
         <v>17</v>
       </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -3085,30 +3025,33 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -3117,27 +3060,30 @@
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -3146,27 +3092,30 @@
         <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -3175,27 +3124,30 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -3204,27 +3156,30 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
@@ -3233,30 +3188,33 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -3265,30 +3223,33 @@
         <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
@@ -3297,713 +3258,779 @@
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="E19" t="s">
+        <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="E20" t="s">
+        <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="E21" t="s">
+        <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D22" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="E22" t="s">
+        <v>18</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="E23" t="s">
+        <v>18</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s">
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D24" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
       </c>
       <c r="F24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B25" t="s">
         <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J25" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B26" t="s">
         <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D26" t="s">
-        <v>163</v>
+        <v>164</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I26" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K26" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I27" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D28" t="s">
-        <v>177</v>
+        <v>178</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K28" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D29" t="s">
-        <v>183</v>
+        <v>184</v>
+      </c>
+      <c r="E29" t="s">
+        <v>18</v>
       </c>
       <c r="F29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G29" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H29" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I29" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B30" t="s">
         <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D30" t="s">
-        <v>189</v>
+        <v>190</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G30" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H30" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I30" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J30" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K30" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B31" t="s">
         <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D31" t="s">
-        <v>196</v>
+        <v>197</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G31" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H31" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I31" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J31" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K31" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="C32" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="D32" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E32" t="s">
-        <v>205</v>
+        <v>18</v>
       </c>
       <c r="F32" t="s">
-        <v>18</v>
-      </c>
-      <c r="G32" t="s">
-        <v>206</v>
+        <v>68</v>
       </c>
       <c r="H32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B33" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C33" t="s">
+        <v>206</v>
+      </c>
+      <c r="D33" t="s">
         <v>212</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" t="s">
+        <v>68</v>
+      </c>
+      <c r="H33" t="s">
         <v>213</v>
-      </c>
-      <c r="F33" t="s">
-        <v>67</v>
-      </c>
-      <c r="H33" t="s">
-        <v>214</v>
       </c>
       <c r="I33" t="s">
         <v>214</v>
@@ -4020,19 +4047,25 @@
         <v>217</v>
       </c>
       <c r="B34" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C34" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D34" t="s">
         <v>218</v>
       </c>
+      <c r="E34" t="s">
+        <v>18</v>
+      </c>
       <c r="F34" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="G34" t="s">
+        <v>219</v>
       </c>
       <c r="H34" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I34" t="s">
         <v>220</v>
@@ -4049,16 +4082,19 @@
         <v>223</v>
       </c>
       <c r="B35" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C35" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D35" t="s">
         <v>224</v>
       </c>
+      <c r="E35" t="s">
+        <v>18</v>
+      </c>
       <c r="F35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G35" t="s">
         <v>225</v>
@@ -4081,141 +4117,153 @@
         <v>229</v>
       </c>
       <c r="B36" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C36" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D36" t="s">
         <v>230</v>
       </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
       <c r="F36" t="s">
-        <v>67</v>
-      </c>
-      <c r="G36" t="s">
+        <v>68</v>
+      </c>
+      <c r="H36" t="s">
         <v>231</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
+        <v>231</v>
+      </c>
+      <c r="J36" t="s">
         <v>232</v>
       </c>
-      <c r="I36" t="s">
-        <v>232</v>
-      </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
         <v>233</v>
-      </c>
-      <c r="K36" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
+        <v>234</v>
+      </c>
+      <c r="B37" t="s">
+        <v>205</v>
+      </c>
+      <c r="C37" t="s">
+        <v>206</v>
+      </c>
+      <c r="D37" t="s">
         <v>235</v>
       </c>
-      <c r="B37" t="s">
-        <v>211</v>
-      </c>
-      <c r="C37" t="s">
-        <v>212</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" t="s">
         <v>236</v>
       </c>
-      <c r="F37" t="s">
-        <v>67</v>
-      </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J37" t="s">
         <v>237</v>
       </c>
-      <c r="I37" t="s">
-        <v>237</v>
-      </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>238</v>
-      </c>
-      <c r="K37" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
+        <v>239</v>
+      </c>
+      <c r="B38" t="s">
+        <v>205</v>
+      </c>
+      <c r="C38" t="s">
         <v>240</v>
-      </c>
-      <c r="B38" t="s">
-        <v>211</v>
-      </c>
-      <c r="C38" t="s">
-        <v>212</v>
       </c>
       <c r="D38" t="s">
         <v>241</v>
       </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
       <c r="F38" t="s">
-        <v>67</v>
+        <v>19</v>
+      </c>
+      <c r="G38" t="s">
+        <v>242</v>
       </c>
       <c r="H38" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I38" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="J38" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K38" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B39" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C39" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D39" t="s">
-        <v>247</v>
+        <v>248</v>
+      </c>
+      <c r="E39" t="s">
+        <v>18</v>
       </c>
       <c r="F39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G39" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H39" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I39" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J39" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K39" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B40" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C40" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D40" t="s">
-        <v>254</v>
+        <v>255</v>
+      </c>
+      <c r="E40" t="s">
+        <v>18</v>
       </c>
       <c r="F40" t="s">
-        <v>18</v>
-      </c>
-      <c r="G40" t="s">
-        <v>255</v>
+        <v>19</v>
       </c>
       <c r="H40" t="s">
         <v>256</v>
@@ -4235,77 +4283,86 @@
         <v>260</v>
       </c>
       <c r="B41" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C41" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D41" t="s">
         <v>261</v>
       </c>
+      <c r="E41" t="s">
+        <v>18</v>
+      </c>
       <c r="F41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H41" t="s">
         <v>262</v>
       </c>
       <c r="I41" t="s">
+        <v>262</v>
+      </c>
+      <c r="J41" t="s">
         <v>263</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>264</v>
-      </c>
-      <c r="K41" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
+        <v>265</v>
+      </c>
+      <c r="B42" t="s">
+        <v>205</v>
+      </c>
+      <c r="C42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D42" t="s">
         <v>266</v>
       </c>
-      <c r="B42" t="s">
-        <v>211</v>
-      </c>
-      <c r="C42" t="s">
-        <v>246</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" t="s">
+        <v>171</v>
+      </c>
+      <c r="G42" t="s">
         <v>267</v>
-      </c>
-      <c r="F42" t="s">
-        <v>18</v>
       </c>
       <c r="H42" t="s">
         <v>268</v>
       </c>
       <c r="I42" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J42" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K42" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B43" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C43" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D43" t="s">
-        <v>272</v>
+        <v>273</v>
+      </c>
+      <c r="E43" t="s">
+        <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>170</v>
-      </c>
-      <c r="G43" t="s">
-        <v>273</v>
+        <v>171</v>
       </c>
       <c r="H43" t="s">
         <v>274</v>
@@ -4325,51 +4382,54 @@
         <v>278</v>
       </c>
       <c r="B44" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C44" t="s">
-        <v>246</v>
+        <v>279</v>
       </c>
       <c r="D44" t="s">
-        <v>279</v>
+        <v>280</v>
+      </c>
+      <c r="E44" t="s">
+        <v>18</v>
       </c>
       <c r="F44" t="s">
-        <v>170</v>
+        <v>68</v>
+      </c>
+      <c r="G44" t="s">
+        <v>281</v>
       </c>
       <c r="H44" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I44" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J44" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K44" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B45" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C45" t="s">
-        <v>246</v>
+        <v>279</v>
       </c>
       <c r="D45" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E45" t="s">
-        <v>286</v>
+        <v>18</v>
       </c>
       <c r="F45" t="s">
-        <v>170</v>
-      </c>
-      <c r="G45" t="s">
-        <v>287</v>
+        <v>68</v>
       </c>
       <c r="H45" t="s">
         <v>288</v>
@@ -4389,60 +4449,60 @@
         <v>291</v>
       </c>
       <c r="B46" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C46" t="s">
-        <v>246</v>
+        <v>279</v>
       </c>
       <c r="D46" t="s">
         <v>292</v>
       </c>
       <c r="E46" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" t="s">
+        <v>171</v>
+      </c>
+      <c r="G46" t="s">
         <v>293</v>
       </c>
-      <c r="F46" t="s">
-        <v>170</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>294</v>
       </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
+        <v>294</v>
+      </c>
+      <c r="J46" t="s">
         <v>295</v>
       </c>
-      <c r="I46" t="s">
-        <v>295</v>
-      </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
         <v>296</v>
-      </c>
-      <c r="K46" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
+        <v>297</v>
+      </c>
+      <c r="B47" t="s">
+        <v>205</v>
+      </c>
+      <c r="C47" t="s">
+        <v>279</v>
+      </c>
+      <c r="D47" t="s">
         <v>298</v>
       </c>
-      <c r="B47" t="s">
-        <v>211</v>
-      </c>
-      <c r="C47" t="s">
-        <v>246</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" t="s">
+        <v>68</v>
+      </c>
+      <c r="G47" t="s">
         <v>299</v>
       </c>
-      <c r="E47" t="s">
-        <v>286</v>
-      </c>
-      <c r="F47" t="s">
-        <v>18</v>
-      </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>300</v>
-      </c>
-      <c r="H47" t="s">
-        <v>301</v>
       </c>
       <c r="I47" t="s">
         <v>301</v>
@@ -4459,144 +4519,159 @@
         <v>304</v>
       </c>
       <c r="B48" t="s">
-        <v>211</v>
+        <v>305</v>
       </c>
       <c r="C48" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D48" t="s">
-        <v>306</v>
+        <v>307</v>
+      </c>
+      <c r="E48" t="s">
+        <v>18</v>
       </c>
       <c r="F48" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="G48" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H48" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I48" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B49" t="s">
-        <v>211</v>
+        <v>305</v>
       </c>
       <c r="C49" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D49" t="s">
-        <v>313</v>
+        <v>314</v>
+      </c>
+      <c r="E49" t="s">
+        <v>18</v>
       </c>
       <c r="F49" t="s">
-        <v>67</v>
+        <v>19</v>
+      </c>
+      <c r="G49" t="s">
+        <v>315</v>
       </c>
       <c r="H49" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I49" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J49" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K49" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B50" t="s">
-        <v>211</v>
+        <v>305</v>
       </c>
       <c r="C50" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>320</v>
+      </c>
+      <c r="E50" t="s">
+        <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="G50" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H50" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J50" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K50" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B51" t="s">
-        <v>211</v>
+        <v>305</v>
       </c>
       <c r="C51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D51" t="s">
-        <v>324</v>
+        <v>327</v>
+      </c>
+      <c r="E51" t="s">
+        <v>18</v>
       </c>
       <c r="F51" t="s">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c r="G51" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H51" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I51" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J51" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K51" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B52" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="C52" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D52" t="s">
-        <v>333</v>
+        <v>334</v>
+      </c>
+      <c r="E52" t="s">
+        <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>18</v>
-      </c>
-      <c r="G52" t="s">
-        <v>334</v>
+        <v>19</v>
       </c>
       <c r="H52" t="s">
         <v>335</v>
@@ -4616,22 +4691,22 @@
         <v>339</v>
       </c>
       <c r="B53" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="C53" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D53" t="s">
         <v>340</v>
       </c>
+      <c r="E53" t="s">
+        <v>18</v>
+      </c>
       <c r="F53" t="s">
-        <v>18</v>
-      </c>
-      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
         <v>341</v>
-      </c>
-      <c r="H53" t="s">
-        <v>342</v>
       </c>
       <c r="I53" t="s">
         <v>342</v>
@@ -4648,540 +4723,372 @@
         <v>345</v>
       </c>
       <c r="B54" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="C54" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D54" t="s">
         <v>346</v>
       </c>
+      <c r="E54" t="s">
+        <v>18</v>
+      </c>
       <c r="F54" t="s">
-        <v>18</v>
-      </c>
-      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" t="s">
         <v>347</v>
       </c>
-      <c r="H54" t="s">
+      <c r="I54" t="s">
+        <v>347</v>
+      </c>
+      <c r="J54" t="s">
         <v>348</v>
       </c>
-      <c r="I54" t="s">
+      <c r="K54" t="s">
         <v>349</v>
-      </c>
-      <c r="J54" t="s">
-        <v>350</v>
-      </c>
-      <c r="K54" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
+        <v>350</v>
+      </c>
+      <c r="B55" t="s">
+        <v>305</v>
+      </c>
+      <c r="C55" t="s">
+        <v>333</v>
+      </c>
+      <c r="D55" t="s">
+        <v>351</v>
+      </c>
+      <c r="E55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" t="s">
+        <v>198</v>
+      </c>
+      <c r="G55" t="s">
         <v>352</v>
       </c>
-      <c r="B55" t="s">
-        <v>331</v>
-      </c>
-      <c r="C55" t="s">
-        <v>332</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="H55" t="s">
         <v>353</v>
       </c>
-      <c r="F55" t="s">
-        <v>170</v>
-      </c>
-      <c r="G55" t="s">
+      <c r="I55" t="s">
+        <v>353</v>
+      </c>
+      <c r="J55" t="s">
         <v>354</v>
       </c>
-      <c r="H55" t="s">
+      <c r="K55" t="s">
         <v>355</v>
-      </c>
-      <c r="I55" t="s">
-        <v>355</v>
-      </c>
-      <c r="J55" t="s">
-        <v>356</v>
-      </c>
-      <c r="K55" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
+        <v>356</v>
+      </c>
+      <c r="B56" t="s">
+        <v>305</v>
+      </c>
+      <c r="C56" t="s">
+        <v>357</v>
+      </c>
+      <c r="D56" t="s">
         <v>358</v>
       </c>
-      <c r="B56" t="s">
-        <v>331</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="E56" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" t="s">
         <v>359</v>
       </c>
-      <c r="D56" t="s">
+      <c r="H56" t="s">
         <v>360</v>
       </c>
-      <c r="F56" t="s">
-        <v>18</v>
-      </c>
-      <c r="H56" t="s">
+      <c r="I56" t="s">
+        <v>360</v>
+      </c>
+      <c r="J56" t="s">
         <v>361</v>
       </c>
-      <c r="I56" t="s">
+      <c r="K56" t="s">
         <v>362</v>
-      </c>
-      <c r="J56" t="s">
-        <v>363</v>
-      </c>
-      <c r="K56" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
+        <v>363</v>
+      </c>
+      <c r="B57" t="s">
+        <v>305</v>
+      </c>
+      <c r="C57" t="s">
+        <v>357</v>
+      </c>
+      <c r="D57" t="s">
+        <v>364</v>
+      </c>
+      <c r="E57" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
         <v>365</v>
       </c>
-      <c r="B57" t="s">
-        <v>331</v>
-      </c>
-      <c r="C57" t="s">
-        <v>359</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="I57" t="s">
+        <v>365</v>
+      </c>
+      <c r="J57" t="s">
         <v>366</v>
       </c>
-      <c r="F57" t="s">
-        <v>18</v>
-      </c>
-      <c r="G57" t="s">
+      <c r="K57" t="s">
         <v>367</v>
-      </c>
-      <c r="H57" t="s">
-        <v>368</v>
-      </c>
-      <c r="I57" t="s">
-        <v>369</v>
-      </c>
-      <c r="J57" t="s">
-        <v>370</v>
-      </c>
-      <c r="K57" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
+        <v>368</v>
+      </c>
+      <c r="B58" t="s">
+        <v>305</v>
+      </c>
+      <c r="C58" t="s">
+        <v>357</v>
+      </c>
+      <c r="D58" t="s">
+        <v>369</v>
+      </c>
+      <c r="E58" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" t="s">
+        <v>370</v>
+      </c>
+      <c r="H58" t="s">
+        <v>371</v>
+      </c>
+      <c r="I58" t="s">
+        <v>371</v>
+      </c>
+      <c r="J58" t="s">
         <v>372</v>
       </c>
-      <c r="B58" t="s">
-        <v>331</v>
-      </c>
-      <c r="C58" t="s">
-        <v>359</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="K58" t="s">
         <v>373</v>
-      </c>
-      <c r="F58" t="s">
-        <v>18</v>
-      </c>
-      <c r="H58" t="s">
-        <v>374</v>
-      </c>
-      <c r="I58" t="s">
-        <v>374</v>
-      </c>
-      <c r="J58" t="s">
-        <v>375</v>
-      </c>
-      <c r="K58" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
+        <v>374</v>
+      </c>
+      <c r="B59" t="s">
+        <v>305</v>
+      </c>
+      <c r="C59" t="s">
+        <v>357</v>
+      </c>
+      <c r="D59" t="s">
+        <v>375</v>
+      </c>
+      <c r="E59" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" t="s">
+        <v>376</v>
+      </c>
+      <c r="H59" t="s">
         <v>377</v>
       </c>
-      <c r="B59" t="s">
-        <v>331</v>
-      </c>
-      <c r="C59" t="s">
-        <v>359</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="I59" t="s">
+        <v>377</v>
+      </c>
+      <c r="J59" t="s">
         <v>378</v>
       </c>
-      <c r="F59" t="s">
-        <v>197</v>
-      </c>
-      <c r="G59" t="s">
+      <c r="K59" t="s">
         <v>379</v>
-      </c>
-      <c r="H59" t="s">
-        <v>380</v>
-      </c>
-      <c r="I59" t="s">
-        <v>380</v>
-      </c>
-      <c r="J59" t="s">
-        <v>381</v>
-      </c>
-      <c r="K59" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
+        <v>380</v>
+      </c>
+      <c r="B60" t="s">
+        <v>305</v>
+      </c>
+      <c r="C60" t="s">
+        <v>357</v>
+      </c>
+      <c r="D60" t="s">
+        <v>381</v>
+      </c>
+      <c r="E60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>382</v>
+      </c>
+      <c r="I60" t="s">
         <v>383</v>
       </c>
-      <c r="B60" t="s">
-        <v>331</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="J60" t="s">
         <v>384</v>
       </c>
-      <c r="D60" t="s">
+      <c r="K60" t="s">
         <v>385</v>
-      </c>
-      <c r="F60" t="s">
-        <v>18</v>
-      </c>
-      <c r="G60" t="s">
-        <v>386</v>
-      </c>
-      <c r="H60" t="s">
-        <v>387</v>
-      </c>
-      <c r="I60" t="s">
-        <v>388</v>
-      </c>
-      <c r="J60" t="s">
-        <v>389</v>
-      </c>
-      <c r="K60" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
+        <v>386</v>
+      </c>
+      <c r="B61" t="s">
+        <v>305</v>
+      </c>
+      <c r="C61" t="s">
+        <v>357</v>
+      </c>
+      <c r="D61" t="s">
+        <v>387</v>
+      </c>
+      <c r="E61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" t="s">
+        <v>388</v>
+      </c>
+      <c r="H61" t="s">
+        <v>389</v>
+      </c>
+      <c r="I61" t="s">
+        <v>389</v>
+      </c>
+      <c r="J61" t="s">
+        <v>390</v>
+      </c>
+      <c r="K61" t="s">
         <v>391</v>
-      </c>
-      <c r="B61" t="s">
-        <v>331</v>
-      </c>
-      <c r="C61" t="s">
-        <v>384</v>
-      </c>
-      <c r="D61" t="s">
-        <v>392</v>
-      </c>
-      <c r="E61" t="s">
-        <v>393</v>
-      </c>
-      <c r="F61" t="s">
-        <v>18</v>
-      </c>
-      <c r="G61" t="s">
-        <v>394</v>
-      </c>
-      <c r="H61" t="s">
-        <v>395</v>
-      </c>
-      <c r="I61" t="s">
-        <v>395</v>
-      </c>
-      <c r="J61" t="s">
-        <v>396</v>
-      </c>
-      <c r="K61" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B62" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="C62" t="s">
-        <v>384</v>
+        <v>357</v>
       </c>
       <c r="D62" t="s">
-        <v>399</v>
+        <v>393</v>
+      </c>
+      <c r="E62" t="s">
+        <v>18</v>
       </c>
       <c r="F62" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H62" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="I62" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="J62" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="K62" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B63" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="C63" t="s">
-        <v>384</v>
+        <v>357</v>
       </c>
       <c r="D63" t="s">
-        <v>404</v>
+        <v>398</v>
+      </c>
+      <c r="E63" t="s">
+        <v>18</v>
       </c>
       <c r="F63" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G63" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="H63" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="I63" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="J63" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="K63" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B64" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="C64" t="s">
-        <v>384</v>
+        <v>357</v>
       </c>
       <c r="D64" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E64" t="s">
-        <v>286</v>
+        <v>18</v>
       </c>
       <c r="F64" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G64" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="H64" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="I64" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="J64" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="K64" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
-      <c r="A65" t="s">
-        <v>403</v>
-      </c>
-      <c r="B65" t="s">
-        <v>331</v>
-      </c>
-      <c r="C65" t="s">
-        <v>384</v>
-      </c>
-      <c r="D65" t="s">
-        <v>416</v>
-      </c>
-      <c r="F65" t="s">
-        <v>18</v>
-      </c>
-      <c r="G65" t="s">
-        <v>417</v>
-      </c>
-      <c r="H65" t="s">
-        <v>418</v>
-      </c>
-      <c r="I65" t="s">
-        <v>418</v>
-      </c>
-      <c r="J65" t="s">
-        <v>419</v>
-      </c>
-      <c r="K65" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
-      <c r="A66" t="s">
-        <v>421</v>
-      </c>
-      <c r="B66" t="s">
-        <v>331</v>
-      </c>
-      <c r="C66" t="s">
-        <v>384</v>
-      </c>
-      <c r="D66" t="s">
-        <v>422</v>
-      </c>
-      <c r="F66" t="s">
-        <v>18</v>
-      </c>
-      <c r="H66" t="s">
-        <v>423</v>
-      </c>
-      <c r="I66" t="s">
-        <v>424</v>
-      </c>
-      <c r="J66" t="s">
-        <v>425</v>
-      </c>
-      <c r="K66" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
-      <c r="A67" t="s">
-        <v>427</v>
-      </c>
-      <c r="B67" t="s">
-        <v>331</v>
-      </c>
-      <c r="C67" t="s">
-        <v>384</v>
-      </c>
-      <c r="D67" t="s">
-        <v>428</v>
-      </c>
-      <c r="F67" t="s">
-        <v>18</v>
-      </c>
-      <c r="G67" t="s">
-        <v>429</v>
-      </c>
-      <c r="H67" t="s">
-        <v>430</v>
-      </c>
-      <c r="I67" t="s">
-        <v>430</v>
-      </c>
-      <c r="J67" t="s">
-        <v>431</v>
-      </c>
-      <c r="K67" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11">
-      <c r="A68" t="s">
-        <v>433</v>
-      </c>
-      <c r="B68" t="s">
-        <v>331</v>
-      </c>
-      <c r="C68" t="s">
-        <v>384</v>
-      </c>
-      <c r="D68" t="s">
-        <v>434</v>
-      </c>
-      <c r="F68" t="s">
-        <v>18</v>
-      </c>
-      <c r="G68" t="s">
-        <v>435</v>
-      </c>
-      <c r="H68" t="s">
-        <v>436</v>
-      </c>
-      <c r="I68" t="s">
-        <v>437</v>
-      </c>
-      <c r="J68" t="s">
-        <v>438</v>
-      </c>
-      <c r="K68" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11">
-      <c r="A69" t="s">
-        <v>440</v>
-      </c>
-      <c r="B69" t="s">
-        <v>331</v>
-      </c>
-      <c r="C69" t="s">
-        <v>384</v>
-      </c>
-      <c r="D69" t="s">
-        <v>441</v>
-      </c>
-      <c r="E69" t="s">
-        <v>393</v>
-      </c>
-      <c r="F69" t="s">
-        <v>18</v>
-      </c>
-      <c r="G69" t="s">
-        <v>442</v>
-      </c>
-      <c r="H69" t="s">
-        <v>443</v>
-      </c>
-      <c r="I69" t="s">
-        <v>444</v>
-      </c>
-      <c r="J69" t="s">
-        <v>445</v>
-      </c>
-      <c r="K69" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
-      <c r="A70" t="s">
-        <v>447</v>
-      </c>
-      <c r="B70" t="s">
-        <v>331</v>
-      </c>
-      <c r="C70" t="s">
-        <v>384</v>
-      </c>
-      <c r="D70" t="s">
-        <v>448</v>
-      </c>
-      <c r="F70" t="s">
-        <v>18</v>
-      </c>
-      <c r="G70" t="s">
-        <v>449</v>
-      </c>
-      <c r="H70" t="s">
-        <v>450</v>
-      </c>
-      <c r="I70" t="s">
-        <v>450</v>
-      </c>
-      <c r="J70" t="s">
-        <v>451</v>
-      </c>
-      <c r="K70" t="s">
-        <v>452</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -5192,7 +5099,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7DF49F1-A40A-4419-8D7C-BFC8568FABFD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A7F59B-484F-4252-8C57-D4CDC1099A7E}">
   <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -5215,22 +5122,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>453</v>
+        <v>409</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>454</v>
+        <v>410</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>455</v>
+        <v>411</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>456</v>
+        <v>412</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>457</v>
+        <v>413</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>458</v>
+        <v>414</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
@@ -5256,645 +5163,645 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>459</v>
+        <v>415</v>
       </c>
       <c r="B2" t="s">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="C2" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="D2" t="s">
-        <v>462</v>
+        <v>418</v>
       </c>
       <c r="E2" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="F2" t="s">
-        <v>464</v>
+        <v>420</v>
       </c>
       <c r="G2" t="s">
-        <v>465</v>
+        <v>421</v>
       </c>
       <c r="H2" t="s">
-        <v>466</v>
+        <v>422</v>
       </c>
       <c r="I2" t="s">
-        <v>466</v>
+        <v>422</v>
       </c>
       <c r="J2" t="s">
-        <v>467</v>
+        <v>423</v>
       </c>
       <c r="K2" t="s">
-        <v>468</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>469</v>
+        <v>425</v>
       </c>
       <c r="B3" t="s">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="C3" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="D3" t="s">
-        <v>470</v>
+        <v>426</v>
       </c>
       <c r="E3" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="F3" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="H3" t="s">
-        <v>472</v>
+        <v>428</v>
       </c>
       <c r="I3" t="s">
-        <v>472</v>
+        <v>428</v>
       </c>
       <c r="J3" t="s">
-        <v>473</v>
+        <v>429</v>
       </c>
       <c r="K3" t="s">
-        <v>474</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>475</v>
+        <v>431</v>
       </c>
       <c r="B4" t="s">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="C4" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="D4" t="s">
-        <v>476</v>
+        <v>432</v>
       </c>
       <c r="E4" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="F4" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="H4" t="s">
-        <v>477</v>
+        <v>433</v>
       </c>
       <c r="I4" t="s">
-        <v>477</v>
+        <v>433</v>
       </c>
       <c r="J4" t="s">
-        <v>478</v>
+        <v>434</v>
       </c>
       <c r="K4" t="s">
-        <v>479</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="B5" t="s">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="C5" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="D5" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
       <c r="E5" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="F5" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="H5" t="s">
-        <v>482</v>
+        <v>438</v>
       </c>
       <c r="I5" t="s">
-        <v>482</v>
+        <v>438</v>
       </c>
       <c r="J5" t="s">
-        <v>483</v>
+        <v>439</v>
       </c>
       <c r="K5" t="s">
-        <v>484</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>485</v>
+        <v>441</v>
       </c>
       <c r="B6" t="s">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="C6" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="D6" t="s">
-        <v>486</v>
+        <v>442</v>
       </c>
       <c r="E6" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="F6" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="H6" t="s">
-        <v>487</v>
+        <v>443</v>
       </c>
       <c r="I6" t="s">
-        <v>487</v>
+        <v>443</v>
       </c>
       <c r="J6" t="s">
-        <v>488</v>
+        <v>444</v>
       </c>
       <c r="K6" t="s">
-        <v>489</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>490</v>
+        <v>446</v>
       </c>
       <c r="B7" t="s">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="C7" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="D7" t="s">
-        <v>491</v>
+        <v>447</v>
       </c>
       <c r="E7" t="s">
-        <v>492</v>
+        <v>448</v>
       </c>
       <c r="F7" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="H7" t="s">
-        <v>493</v>
+        <v>449</v>
       </c>
       <c r="I7" t="s">
-        <v>493</v>
+        <v>449</v>
       </c>
       <c r="J7" t="s">
-        <v>494</v>
+        <v>450</v>
       </c>
       <c r="K7" t="s">
-        <v>495</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>496</v>
+        <v>452</v>
       </c>
       <c r="B8" t="s">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="C8" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="D8" t="s">
-        <v>497</v>
+        <v>453</v>
       </c>
       <c r="E8" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="F8" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="H8" t="s">
-        <v>498</v>
+        <v>454</v>
       </c>
       <c r="I8" t="s">
-        <v>499</v>
+        <v>455</v>
       </c>
       <c r="J8" t="s">
-        <v>500</v>
+        <v>456</v>
       </c>
       <c r="K8" t="s">
-        <v>501</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>502</v>
+        <v>458</v>
       </c>
       <c r="B9" t="s">
+        <v>416</v>
+      </c>
+      <c r="C9" t="s">
+        <v>417</v>
+      </c>
+      <c r="D9" t="s">
+        <v>459</v>
+      </c>
+      <c r="E9" t="s">
         <v>460</v>
       </c>
-      <c r="C9" t="s">
+      <c r="F9" t="s">
+        <v>427</v>
+      </c>
+      <c r="H9" t="s">
         <v>461</v>
       </c>
-      <c r="D9" t="s">
-        <v>503</v>
-      </c>
-      <c r="E9" t="s">
-        <v>504</v>
-      </c>
-      <c r="F9" t="s">
-        <v>471</v>
-      </c>
-      <c r="H9" t="s">
-        <v>505</v>
-      </c>
       <c r="I9" t="s">
-        <v>506</v>
+        <v>462</v>
       </c>
       <c r="J9" t="s">
-        <v>507</v>
+        <v>463</v>
       </c>
       <c r="K9" t="s">
-        <v>508</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>509</v>
+        <v>465</v>
       </c>
       <c r="B10" t="s">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="C10" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="D10" t="s">
-        <v>510</v>
+        <v>466</v>
       </c>
       <c r="E10" t="s">
-        <v>511</v>
+        <v>467</v>
       </c>
       <c r="F10" t="s">
+        <v>427</v>
+      </c>
+      <c r="H10" t="s">
+        <v>468</v>
+      </c>
+      <c r="I10" t="s">
+        <v>469</v>
+      </c>
+      <c r="J10" t="s">
+        <v>470</v>
+      </c>
+      <c r="K10" t="s">
         <v>471</v>
-      </c>
-      <c r="H10" t="s">
-        <v>512</v>
-      </c>
-      <c r="I10" t="s">
-        <v>513</v>
-      </c>
-      <c r="J10" t="s">
-        <v>514</v>
-      </c>
-      <c r="K10" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>516</v>
+        <v>472</v>
       </c>
       <c r="B11" t="s">
+        <v>416</v>
+      </c>
+      <c r="C11" t="s">
+        <v>417</v>
+      </c>
+      <c r="D11" t="s">
+        <v>473</v>
+      </c>
+      <c r="E11" t="s">
         <v>460</v>
       </c>
-      <c r="C11" t="s">
-        <v>461</v>
-      </c>
-      <c r="D11" t="s">
-        <v>517</v>
-      </c>
-      <c r="E11" t="s">
-        <v>504</v>
-      </c>
       <c r="F11" t="s">
-        <v>464</v>
+        <v>420</v>
       </c>
       <c r="H11" t="s">
-        <v>518</v>
+        <v>474</v>
       </c>
       <c r="I11" t="s">
-        <v>519</v>
+        <v>475</v>
       </c>
       <c r="J11" t="s">
-        <v>520</v>
+        <v>476</v>
       </c>
       <c r="K11" t="s">
-        <v>521</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>522</v>
+        <v>478</v>
       </c>
       <c r="B12" t="s">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="C12" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="D12" t="s">
-        <v>523</v>
+        <v>479</v>
       </c>
       <c r="E12" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="F12" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="H12" t="s">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="I12" t="s">
-        <v>524</v>
+        <v>480</v>
       </c>
       <c r="J12" t="s">
-        <v>525</v>
+        <v>481</v>
       </c>
       <c r="K12" t="s">
-        <v>526</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>527</v>
+        <v>483</v>
       </c>
       <c r="B13" t="s">
-        <v>528</v>
+        <v>484</v>
       </c>
       <c r="C13" t="s">
-        <v>529</v>
+        <v>485</v>
       </c>
       <c r="D13" t="s">
-        <v>530</v>
+        <v>486</v>
       </c>
       <c r="E13" t="s">
-        <v>504</v>
+        <v>460</v>
       </c>
       <c r="F13" t="s">
-        <v>464</v>
+        <v>420</v>
       </c>
       <c r="H13" t="s">
-        <v>531</v>
+        <v>487</v>
       </c>
       <c r="I13" t="s">
-        <v>532</v>
+        <v>488</v>
       </c>
       <c r="J13" t="s">
-        <v>533</v>
+        <v>489</v>
       </c>
       <c r="K13" t="s">
-        <v>534</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>535</v>
+        <v>491</v>
       </c>
       <c r="B14" t="s">
-        <v>528</v>
+        <v>484</v>
       </c>
       <c r="C14" t="s">
-        <v>529</v>
+        <v>485</v>
       </c>
       <c r="D14" t="s">
-        <v>536</v>
+        <v>492</v>
       </c>
       <c r="E14" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="F14" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="H14" t="s">
-        <v>537</v>
+        <v>493</v>
       </c>
       <c r="I14" t="s">
-        <v>537</v>
+        <v>493</v>
       </c>
       <c r="J14" t="s">
-        <v>538</v>
+        <v>494</v>
       </c>
       <c r="K14" t="s">
-        <v>539</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>540</v>
+        <v>496</v>
       </c>
       <c r="B15" t="s">
-        <v>528</v>
+        <v>484</v>
       </c>
       <c r="C15" t="s">
-        <v>529</v>
+        <v>485</v>
       </c>
       <c r="D15" t="s">
-        <v>541</v>
+        <v>497</v>
       </c>
       <c r="E15" t="s">
-        <v>492</v>
+        <v>448</v>
       </c>
       <c r="F15" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="H15" t="s">
-        <v>542</v>
+        <v>498</v>
       </c>
       <c r="I15" t="s">
-        <v>543</v>
+        <v>499</v>
       </c>
       <c r="J15" t="s">
-        <v>544</v>
+        <v>500</v>
       </c>
       <c r="K15" t="s">
-        <v>545</v>
+        <v>501</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>546</v>
+        <v>502</v>
       </c>
       <c r="B16" t="s">
-        <v>528</v>
+        <v>484</v>
       </c>
       <c r="C16" t="s">
-        <v>529</v>
+        <v>485</v>
       </c>
       <c r="D16" t="s">
-        <v>547</v>
+        <v>503</v>
       </c>
       <c r="E16" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="F16" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="H16" t="s">
-        <v>548</v>
+        <v>504</v>
       </c>
       <c r="I16" t="s">
-        <v>549</v>
+        <v>505</v>
       </c>
       <c r="J16" t="s">
-        <v>550</v>
+        <v>506</v>
       </c>
       <c r="K16" t="s">
-        <v>551</v>
+        <v>507</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>552</v>
+        <v>508</v>
       </c>
       <c r="B17" t="s">
-        <v>528</v>
+        <v>484</v>
       </c>
       <c r="C17" t="s">
-        <v>529</v>
+        <v>485</v>
       </c>
       <c r="D17" t="s">
-        <v>553</v>
+        <v>509</v>
       </c>
       <c r="E17" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="F17" t="s">
-        <v>464</v>
+        <v>420</v>
       </c>
       <c r="H17" t="s">
-        <v>554</v>
+        <v>510</v>
       </c>
       <c r="I17" t="s">
-        <v>555</v>
+        <v>511</v>
       </c>
       <c r="J17" t="s">
-        <v>556</v>
+        <v>512</v>
       </c>
       <c r="K17" t="s">
-        <v>557</v>
+        <v>513</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>558</v>
+        <v>514</v>
       </c>
       <c r="B18" t="s">
-        <v>528</v>
+        <v>484</v>
       </c>
       <c r="C18" t="s">
-        <v>529</v>
+        <v>485</v>
       </c>
       <c r="D18" t="s">
-        <v>559</v>
+        <v>515</v>
       </c>
       <c r="E18" t="s">
-        <v>492</v>
+        <v>448</v>
       </c>
       <c r="F18" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="H18" t="s">
-        <v>560</v>
+        <v>516</v>
       </c>
       <c r="I18" t="s">
-        <v>561</v>
+        <v>517</v>
       </c>
       <c r="J18" t="s">
-        <v>562</v>
+        <v>518</v>
       </c>
       <c r="K18" t="s">
-        <v>563</v>
+        <v>519</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>564</v>
+        <v>520</v>
       </c>
       <c r="B19" t="s">
-        <v>528</v>
+        <v>484</v>
       </c>
       <c r="C19" t="s">
-        <v>565</v>
+        <v>521</v>
       </c>
       <c r="D19" t="s">
-        <v>566</v>
+        <v>522</v>
       </c>
       <c r="E19" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="F19" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="H19" t="s">
-        <v>567</v>
+        <v>523</v>
       </c>
       <c r="I19" t="s">
-        <v>567</v>
+        <v>523</v>
       </c>
       <c r="J19" t="s">
-        <v>568</v>
+        <v>524</v>
       </c>
       <c r="K19" t="s">
-        <v>569</v>
+        <v>525</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>570</v>
+        <v>526</v>
       </c>
       <c r="B20" t="s">
+        <v>484</v>
+      </c>
+      <c r="C20" t="s">
+        <v>521</v>
+      </c>
+      <c r="D20" t="s">
+        <v>527</v>
+      </c>
+      <c r="E20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F20" t="s">
+        <v>427</v>
+      </c>
+      <c r="H20" t="s">
         <v>528</v>
       </c>
-      <c r="C20" t="s">
-        <v>565</v>
-      </c>
-      <c r="D20" t="s">
-        <v>571</v>
-      </c>
-      <c r="E20" t="s">
-        <v>492</v>
-      </c>
-      <c r="F20" t="s">
-        <v>471</v>
-      </c>
-      <c r="H20" t="s">
-        <v>572</v>
-      </c>
       <c r="I20" t="s">
-        <v>573</v>
+        <v>529</v>
       </c>
       <c r="J20" t="s">
-        <v>574</v>
+        <v>530</v>
       </c>
       <c r="K20" t="s">
-        <v>575</v>
+        <v>531</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>576</v>
+        <v>532</v>
       </c>
       <c r="B21" t="s">
-        <v>528</v>
+        <v>484</v>
       </c>
       <c r="C21" t="s">
-        <v>565</v>
+        <v>521</v>
       </c>
       <c r="D21" t="s">
-        <v>577</v>
+        <v>533</v>
       </c>
       <c r="E21" t="s">
-        <v>492</v>
+        <v>448</v>
       </c>
       <c r="F21" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="H21" t="s">
-        <v>578</v>
+        <v>534</v>
       </c>
       <c r="I21" t="s">
-        <v>579</v>
+        <v>535</v>
       </c>
       <c r="J21" t="s">
-        <v>580</v>
+        <v>536</v>
       </c>
       <c r="K21" t="s">
-        <v>581</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -5904,15 +5811,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4343418-7E20-4F96-BDD2-550CFAB37097}">
-  <dimension ref="A1:E41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2190E7C4-5255-4C66-A5B8-E31D4B2E5FBA}">
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="50.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="111.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.95" customHeight="1">
@@ -5920,696 +5827,798 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>582</v>
+        <v>538</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>583</v>
+        <v>539</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>584</v>
+        <v>540</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>585</v>
+        <v>541</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>586</v>
+        <v>542</v>
       </c>
       <c r="B2" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C2" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D2" t="s">
-        <v>589</v>
+        <v>545</v>
       </c>
       <c r="E2" t="s">
-        <v>590</v>
+        <v>546</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>591</v>
+        <v>547</v>
       </c>
       <c r="B3" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C3" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D3" t="s">
-        <v>592</v>
+        <v>548</v>
       </c>
       <c r="E3" t="s">
-        <v>593</v>
+        <v>549</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>594</v>
+        <v>550</v>
       </c>
       <c r="B4" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C4" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D4" t="s">
-        <v>595</v>
+        <v>551</v>
       </c>
       <c r="E4" t="s">
-        <v>596</v>
+        <v>552</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>597</v>
+        <v>553</v>
       </c>
       <c r="B5" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C5" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D5" t="s">
-        <v>598</v>
+        <v>554</v>
       </c>
       <c r="E5" t="s">
-        <v>599</v>
+        <v>555</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>600</v>
+        <v>556</v>
       </c>
       <c r="B6" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C6" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D6" t="s">
-        <v>601</v>
+        <v>557</v>
       </c>
       <c r="E6" t="s">
-        <v>602</v>
+        <v>558</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>603</v>
+        <v>559</v>
       </c>
       <c r="B7" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C7" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D7" t="s">
-        <v>604</v>
+        <v>560</v>
       </c>
       <c r="E7" t="s">
-        <v>605</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>606</v>
+        <v>562</v>
       </c>
       <c r="B8" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C8" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D8" t="s">
-        <v>607</v>
+        <v>563</v>
       </c>
       <c r="E8" t="s">
-        <v>608</v>
+        <v>564</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>609</v>
+        <v>565</v>
       </c>
       <c r="B9" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C9" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D9" t="s">
-        <v>610</v>
+        <v>566</v>
       </c>
       <c r="E9" t="s">
-        <v>611</v>
+        <v>567</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>612</v>
+        <v>568</v>
       </c>
       <c r="B10" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C10" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D10" t="s">
-        <v>613</v>
+        <v>569</v>
       </c>
       <c r="E10" t="s">
-        <v>614</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>615</v>
+        <v>571</v>
       </c>
       <c r="B11" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C11" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D11" t="s">
-        <v>616</v>
+        <v>572</v>
       </c>
       <c r="E11" t="s">
-        <v>617</v>
+        <v>573</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>618</v>
+        <v>574</v>
       </c>
       <c r="B12" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C12" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D12" t="s">
-        <v>619</v>
+        <v>575</v>
       </c>
       <c r="E12" t="s">
-        <v>620</v>
+        <v>576</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>621</v>
+        <v>577</v>
       </c>
       <c r="B13" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C13" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D13" t="s">
-        <v>622</v>
+        <v>578</v>
       </c>
       <c r="E13" t="s">
-        <v>623</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>624</v>
+        <v>580</v>
       </c>
       <c r="B14" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C14" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D14" t="s">
-        <v>625</v>
+        <v>581</v>
       </c>
       <c r="E14" t="s">
-        <v>626</v>
+        <v>582</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="B15" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C15" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D15" t="s">
-        <v>628</v>
+        <v>584</v>
       </c>
       <c r="E15" t="s">
-        <v>629</v>
+        <v>585</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>630</v>
+        <v>586</v>
       </c>
       <c r="B16" t="s">
+        <v>543</v>
+      </c>
+      <c r="C16" t="s">
+        <v>544</v>
+      </c>
+      <c r="D16" t="s">
         <v>587</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>588</v>
-      </c>
-      <c r="D16" t="s">
-        <v>631</v>
-      </c>
-      <c r="E16" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>633</v>
+        <v>589</v>
       </c>
       <c r="B17" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C17" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D17" t="s">
-        <v>634</v>
+        <v>590</v>
       </c>
       <c r="E17" t="s">
-        <v>635</v>
+        <v>591</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>636</v>
+        <v>592</v>
       </c>
       <c r="B18" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C18" t="s">
-        <v>637</v>
+        <v>593</v>
       </c>
       <c r="D18" t="s">
-        <v>638</v>
+        <v>594</v>
       </c>
       <c r="E18" t="s">
-        <v>639</v>
+        <v>595</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>640</v>
+        <v>596</v>
       </c>
       <c r="B19" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C19" t="s">
-        <v>637</v>
+        <v>593</v>
       </c>
       <c r="D19" t="s">
-        <v>641</v>
+        <v>597</v>
       </c>
       <c r="E19" t="s">
-        <v>642</v>
+        <v>598</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>643</v>
+        <v>599</v>
       </c>
       <c r="B20" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C20" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D20" t="s">
-        <v>644</v>
+        <v>600</v>
       </c>
       <c r="E20" t="s">
-        <v>645</v>
+        <v>601</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>646</v>
+        <v>602</v>
       </c>
       <c r="B21" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C21" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D21" t="s">
-        <v>647</v>
+        <v>603</v>
       </c>
       <c r="E21" t="s">
-        <v>648</v>
+        <v>604</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>649</v>
+        <v>605</v>
       </c>
       <c r="B22" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C22" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D22" t="s">
-        <v>650</v>
+        <v>606</v>
       </c>
       <c r="E22" t="s">
-        <v>651</v>
+        <v>607</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>652</v>
+        <v>608</v>
       </c>
       <c r="B23" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C23" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D23" t="s">
-        <v>653</v>
+        <v>609</v>
       </c>
       <c r="E23" t="s">
-        <v>654</v>
+        <v>610</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>655</v>
+        <v>611</v>
       </c>
       <c r="B24" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C24" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D24" t="s">
-        <v>656</v>
+        <v>612</v>
       </c>
       <c r="E24" t="s">
-        <v>657</v>
+        <v>613</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>658</v>
+        <v>614</v>
       </c>
       <c r="B25" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C25" t="s">
-        <v>659</v>
+        <v>615</v>
       </c>
       <c r="D25" t="s">
-        <v>660</v>
+        <v>616</v>
       </c>
       <c r="E25" t="s">
-        <v>661</v>
+        <v>617</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>662</v>
+        <v>618</v>
       </c>
       <c r="B26" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C26" t="s">
-        <v>637</v>
+        <v>593</v>
       </c>
       <c r="D26" t="s">
-        <v>663</v>
+        <v>619</v>
       </c>
       <c r="E26" t="s">
-        <v>664</v>
+        <v>620</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>665</v>
+        <v>621</v>
       </c>
       <c r="B27" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C27" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D27" t="s">
-        <v>666</v>
+        <v>622</v>
       </c>
       <c r="E27" t="s">
-        <v>667</v>
+        <v>623</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>668</v>
+        <v>624</v>
       </c>
       <c r="B28" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C28" t="s">
-        <v>637</v>
+        <v>593</v>
       </c>
       <c r="D28" t="s">
-        <v>669</v>
+        <v>625</v>
       </c>
       <c r="E28" t="s">
-        <v>670</v>
+        <v>626</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>671</v>
+        <v>627</v>
       </c>
       <c r="B29" t="s">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="C29" t="s">
-        <v>659</v>
+        <v>615</v>
       </c>
       <c r="D29" t="s">
-        <v>672</v>
+        <v>628</v>
       </c>
       <c r="E29" t="s">
-        <v>673</v>
+        <v>629</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>674</v>
+        <v>630</v>
       </c>
       <c r="B30" t="s">
-        <v>675</v>
+        <v>631</v>
       </c>
       <c r="C30" t="s">
-        <v>637</v>
+        <v>593</v>
       </c>
       <c r="D30" t="s">
-        <v>676</v>
+        <v>632</v>
       </c>
       <c r="E30" t="s">
-        <v>677</v>
+        <v>633</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>678</v>
+        <v>634</v>
       </c>
       <c r="B31" t="s">
-        <v>675</v>
+        <v>631</v>
       </c>
       <c r="C31" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D31" t="s">
-        <v>679</v>
+        <v>635</v>
       </c>
       <c r="E31" t="s">
-        <v>680</v>
+        <v>636</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>681</v>
+        <v>637</v>
       </c>
       <c r="B32" t="s">
-        <v>675</v>
+        <v>631</v>
       </c>
       <c r="C32" t="s">
-        <v>637</v>
+        <v>593</v>
       </c>
       <c r="D32" t="s">
-        <v>682</v>
+        <v>638</v>
       </c>
       <c r="E32" t="s">
-        <v>683</v>
+        <v>639</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>684</v>
+        <v>640</v>
       </c>
       <c r="B33" t="s">
-        <v>675</v>
+        <v>631</v>
       </c>
       <c r="C33" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D33" t="s">
-        <v>685</v>
+        <v>641</v>
       </c>
       <c r="E33" t="s">
-        <v>686</v>
+        <v>642</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>687</v>
+        <v>643</v>
       </c>
       <c r="B34" t="s">
-        <v>688</v>
+        <v>644</v>
       </c>
       <c r="C34" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D34" t="s">
-        <v>689</v>
+        <v>645</v>
       </c>
       <c r="E34" t="s">
-        <v>690</v>
+        <v>646</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>691</v>
+        <v>647</v>
       </c>
       <c r="B35" t="s">
-        <v>688</v>
+        <v>644</v>
       </c>
       <c r="C35" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D35" t="s">
-        <v>692</v>
+        <v>648</v>
       </c>
       <c r="E35" t="s">
-        <v>693</v>
+        <v>649</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>694</v>
+        <v>650</v>
       </c>
       <c r="B36" t="s">
-        <v>688</v>
+        <v>644</v>
       </c>
       <c r="C36" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D36" t="s">
-        <v>695</v>
+        <v>651</v>
       </c>
       <c r="E36" t="s">
-        <v>696</v>
+        <v>652</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>697</v>
+        <v>653</v>
       </c>
       <c r="B37" t="s">
-        <v>688</v>
+        <v>644</v>
       </c>
       <c r="C37" t="s">
-        <v>637</v>
+        <v>593</v>
       </c>
       <c r="D37" t="s">
-        <v>698</v>
+        <v>654</v>
       </c>
       <c r="E37" t="s">
-        <v>699</v>
+        <v>655</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>700</v>
+        <v>656</v>
       </c>
       <c r="B38" t="s">
-        <v>688</v>
+        <v>644</v>
       </c>
       <c r="C38" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D38" t="s">
-        <v>701</v>
+        <v>657</v>
       </c>
       <c r="E38" t="s">
-        <v>702</v>
+        <v>658</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>703</v>
+        <v>659</v>
       </c>
       <c r="B39" t="s">
-        <v>704</v>
+        <v>660</v>
       </c>
       <c r="C39" t="s">
-        <v>588</v>
+        <v>544</v>
       </c>
       <c r="D39" t="s">
-        <v>705</v>
+        <v>661</v>
       </c>
       <c r="E39" t="s">
-        <v>706</v>
+        <v>662</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>707</v>
+        <v>663</v>
       </c>
       <c r="B40" t="s">
-        <v>704</v>
+        <v>660</v>
       </c>
       <c r="C40" t="s">
-        <v>637</v>
+        <v>593</v>
       </c>
       <c r="D40" t="s">
-        <v>708</v>
+        <v>664</v>
       </c>
       <c r="E40" t="s">
-        <v>709</v>
+        <v>665</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>710</v>
+        <v>666</v>
       </c>
       <c r="B41" t="s">
-        <v>704</v>
+        <v>660</v>
       </c>
       <c r="C41" t="s">
-        <v>637</v>
+        <v>593</v>
       </c>
       <c r="D41" t="s">
-        <v>711</v>
+        <v>667</v>
       </c>
       <c r="E41" t="s">
-        <v>712</v>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>669</v>
+      </c>
+      <c r="B42" t="s">
+        <v>670</v>
+      </c>
+      <c r="C42" t="s">
+        <v>671</v>
+      </c>
+      <c r="D42" t="s">
+        <v>672</v>
+      </c>
+      <c r="E42" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>674</v>
+      </c>
+      <c r="B43" t="s">
+        <v>670</v>
+      </c>
+      <c r="C43" t="s">
+        <v>675</v>
+      </c>
+      <c r="D43" t="s">
+        <v>676</v>
+      </c>
+      <c r="E43" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>678</v>
+      </c>
+      <c r="B44" t="s">
+        <v>679</v>
+      </c>
+      <c r="C44" t="s">
+        <v>671</v>
+      </c>
+      <c r="D44" t="s">
+        <v>680</v>
+      </c>
+      <c r="E44" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>682</v>
+      </c>
+      <c r="B45" t="s">
+        <v>683</v>
+      </c>
+      <c r="C45" t="s">
+        <v>671</v>
+      </c>
+      <c r="D45" t="s">
+        <v>684</v>
+      </c>
+      <c r="E45" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>686</v>
+      </c>
+      <c r="B46" t="s">
+        <v>683</v>
+      </c>
+      <c r="C46" t="s">
+        <v>671</v>
+      </c>
+      <c r="D46" t="s">
+        <v>687</v>
+      </c>
+      <c r="E46" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>689</v>
+      </c>
+      <c r="B47" t="s">
+        <v>683</v>
+      </c>
+      <c r="C47" t="s">
+        <v>671</v>
+      </c>
+      <c r="D47" t="s">
+        <v>690</v>
+      </c>
+      <c r="E47" t="s">
+        <v>691</v>
       </c>
     </row>
   </sheetData>
@@ -6619,7 +6628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1D07730-3D5D-47D7-AE6B-9C93C3220859}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B16A584-0321-47E4-921F-2D47868734B3}">
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -6638,363 +6647,363 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>713</v>
+        <v>692</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>714</v>
+        <v>693</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>715</v>
+        <v>694</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>716</v>
+        <v>695</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>717</v>
+        <v>696</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>718</v>
+        <v>697</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>720</v>
+        <v>699</v>
       </c>
       <c r="B2" t="s">
-        <v>721</v>
+        <v>700</v>
       </c>
       <c r="C2" t="s">
-        <v>722</v>
+        <v>701</v>
       </c>
       <c r="D2" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="E2" t="s">
-        <v>724</v>
+        <v>703</v>
       </c>
       <c r="F2" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
       <c r="G2" t="s">
-        <v>726</v>
+        <v>705</v>
       </c>
       <c r="H2" t="s">
-        <v>727</v>
+        <v>706</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>728</v>
+        <v>707</v>
       </c>
       <c r="B3" t="s">
-        <v>721</v>
+        <v>700</v>
       </c>
       <c r="C3" t="s">
-        <v>729</v>
+        <v>708</v>
       </c>
       <c r="D3" t="s">
-        <v>730</v>
+        <v>709</v>
       </c>
       <c r="E3" t="s">
-        <v>731</v>
+        <v>710</v>
       </c>
       <c r="F3" t="s">
-        <v>732</v>
+        <v>711</v>
       </c>
       <c r="G3" t="s">
-        <v>733</v>
+        <v>712</v>
       </c>
       <c r="H3" t="s">
-        <v>727</v>
+        <v>706</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>734</v>
+        <v>713</v>
       </c>
       <c r="B4" t="s">
-        <v>721</v>
+        <v>700</v>
       </c>
       <c r="C4" t="s">
-        <v>735</v>
+        <v>714</v>
       </c>
       <c r="D4" t="s">
-        <v>730</v>
+        <v>709</v>
       </c>
       <c r="E4" t="s">
-        <v>736</v>
+        <v>715</v>
       </c>
       <c r="F4" t="s">
-        <v>737</v>
+        <v>716</v>
       </c>
       <c r="G4" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="H4" t="s">
-        <v>727</v>
+        <v>706</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>739</v>
+        <v>718</v>
       </c>
       <c r="B5" t="s">
+        <v>700</v>
+      </c>
+      <c r="C5" t="s">
+        <v>719</v>
+      </c>
+      <c r="D5" t="s">
+        <v>720</v>
+      </c>
+      <c r="E5" t="s">
         <v>721</v>
       </c>
-      <c r="C5" t="s">
-        <v>740</v>
-      </c>
-      <c r="D5" t="s">
-        <v>741</v>
-      </c>
-      <c r="E5" t="s">
-        <v>742</v>
-      </c>
       <c r="F5" t="s">
-        <v>743</v>
+        <v>722</v>
       </c>
       <c r="G5" t="s">
-        <v>744</v>
+        <v>723</v>
       </c>
       <c r="H5" t="s">
-        <v>745</v>
+        <v>724</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>746</v>
+        <v>725</v>
       </c>
       <c r="B6" t="s">
-        <v>721</v>
+        <v>700</v>
       </c>
       <c r="C6" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
       <c r="D6" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="E6" t="s">
-        <v>748</v>
+        <v>727</v>
       </c>
       <c r="F6" t="s">
-        <v>749</v>
+        <v>728</v>
       </c>
       <c r="G6" t="s">
-        <v>750</v>
+        <v>729</v>
       </c>
       <c r="H6" t="s">
-        <v>751</v>
+        <v>730</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>752</v>
+        <v>731</v>
       </c>
       <c r="B7" t="s">
-        <v>721</v>
+        <v>700</v>
       </c>
       <c r="C7" t="s">
-        <v>753</v>
+        <v>732</v>
       </c>
       <c r="D7" t="s">
-        <v>754</v>
+        <v>733</v>
       </c>
       <c r="E7" t="s">
-        <v>755</v>
+        <v>734</v>
       </c>
       <c r="F7" t="s">
-        <v>756</v>
+        <v>735</v>
       </c>
       <c r="G7" t="s">
-        <v>757</v>
+        <v>736</v>
       </c>
       <c r="H7" t="s">
-        <v>758</v>
+        <v>737</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>759</v>
+        <v>738</v>
       </c>
       <c r="B8" t="s">
-        <v>760</v>
+        <v>739</v>
       </c>
       <c r="C8" t="s">
-        <v>761</v>
+        <v>740</v>
       </c>
       <c r="D8" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="E8" t="s">
-        <v>762</v>
+        <v>741</v>
       </c>
       <c r="F8" t="s">
-        <v>763</v>
+        <v>742</v>
       </c>
       <c r="G8" t="s">
-        <v>764</v>
+        <v>743</v>
       </c>
       <c r="H8" t="s">
-        <v>765</v>
+        <v>744</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="B9" t="s">
-        <v>760</v>
+        <v>739</v>
       </c>
       <c r="C9" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="D9" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="E9" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F9" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="G9" t="s">
-        <v>770</v>
+        <v>749</v>
       </c>
       <c r="H9" t="s">
-        <v>765</v>
+        <v>744</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>771</v>
+        <v>750</v>
       </c>
       <c r="B10" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="C10" t="s">
-        <v>773</v>
+        <v>752</v>
       </c>
       <c r="D10" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="E10" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F10" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="G10" t="s">
-        <v>777</v>
+        <v>756</v>
       </c>
       <c r="H10" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>779</v>
+        <v>758</v>
       </c>
       <c r="B11" t="s">
-        <v>780</v>
+        <v>759</v>
       </c>
       <c r="C11" t="s">
-        <v>781</v>
+        <v>760</v>
       </c>
       <c r="D11" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="E11" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F11" t="s">
-        <v>783</v>
+        <v>762</v>
       </c>
       <c r="G11" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="H11" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>786</v>
+        <v>765</v>
       </c>
       <c r="B12" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="C12" t="s">
-        <v>788</v>
+        <v>767</v>
       </c>
       <c r="D12" t="s">
-        <v>730</v>
+        <v>709</v>
       </c>
       <c r="E12" t="s">
-        <v>789</v>
+        <v>768</v>
       </c>
       <c r="F12" t="s">
-        <v>790</v>
+        <v>769</v>
       </c>
       <c r="G12" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="H12" t="s">
-        <v>792</v>
+        <v>771</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>793</v>
+        <v>772</v>
       </c>
       <c r="B13" t="s">
-        <v>794</v>
+        <v>773</v>
       </c>
       <c r="C13" t="s">
-        <v>795</v>
+        <v>774</v>
       </c>
       <c r="D13" t="s">
-        <v>730</v>
+        <v>709</v>
       </c>
       <c r="E13" t="s">
-        <v>796</v>
+        <v>775</v>
       </c>
       <c r="F13" t="s">
-        <v>797</v>
+        <v>776</v>
       </c>
       <c r="G13" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="H13" t="s">
-        <v>792</v>
+        <v>771</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>798</v>
+        <v>777</v>
       </c>
       <c r="B14" t="s">
-        <v>799</v>
+        <v>778</v>
       </c>
       <c r="C14" t="s">
-        <v>800</v>
+        <v>779</v>
       </c>
       <c r="D14" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="E14" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="F14" t="s">
-        <v>802</v>
+        <v>781</v>
       </c>
       <c r="G14" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="H14" t="s">
-        <v>792</v>
+        <v>771</v>
       </c>
     </row>
   </sheetData>
@@ -7004,7 +7013,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D9DF32-6260-4F06-8106-FA692B8913B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBBAAF34-BB1A-4F90-8A32-5D52F2C6AC55}">
   <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -7029,132 +7038,132 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>804</v>
+        <v>783</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>805</v>
+        <v>784</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>806</v>
+        <v>785</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>807</v>
+        <v>786</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>808</v>
+        <v>787</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>809</v>
+        <v>788</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>810</v>
+        <v>789</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>811</v>
+        <v>790</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>812</v>
+        <v>791</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>813</v>
+        <v>792</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>814</v>
+        <v>793</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>816</v>
+        <v>795</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>817</v>
+        <v>796</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>818</v>
+        <v>797</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>819</v>
+        <v>798</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>820</v>
+        <v>799</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>821</v>
+        <v>800</v>
       </c>
       <c r="B2" t="s">
-        <v>822</v>
+        <v>801</v>
       </c>
       <c r="C2" t="s">
-        <v>823</v>
+        <v>802</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>824</v>
+        <v>803</v>
       </c>
       <c r="B3" t="s">
-        <v>825</v>
+        <v>804</v>
       </c>
       <c r="C3" t="s">
-        <v>826</v>
+        <v>805</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>827</v>
+        <v>806</v>
       </c>
       <c r="B4" t="s">
-        <v>828</v>
+        <v>807</v>
       </c>
       <c r="C4" t="s">
-        <v>829</v>
+        <v>808</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>830</v>
+        <v>809</v>
       </c>
       <c r="B5" t="s">
-        <v>831</v>
+        <v>810</v>
       </c>
       <c r="C5" t="s">
-        <v>832</v>
+        <v>811</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>833</v>
+        <v>812</v>
       </c>
       <c r="B6" t="s">
-        <v>834</v>
+        <v>813</v>
       </c>
       <c r="C6" t="s">
-        <v>835</v>
+        <v>814</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>836</v>
+        <v>815</v>
       </c>
       <c r="B7" t="s">
-        <v>837</v>
+        <v>816</v>
       </c>
       <c r="C7" t="s">
-        <v>838</v>
+        <v>817</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>839</v>
+        <v>818</v>
       </c>
       <c r="B8" t="s">
-        <v>840</v>
+        <v>819</v>
       </c>
       <c r="C8" t="s">
-        <v>841</v>
+        <v>820</v>
       </c>
     </row>
   </sheetData>
@@ -7164,7 +7173,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47658C12-34A5-4103-9319-F97CDA82D2FA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50BE589E-6782-40FD-8D1F-B6EDACC23572}">
   <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -7183,40 +7192,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>842</v>
+        <v>821</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>843</v>
+        <v>822</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>844</v>
+        <v>823</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>845</v>
+        <v>824</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>846</v>
+        <v>825</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>847</v>
+        <v>826</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>848</v>
+        <v>827</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>849</v>
+        <v>828</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>850</v>
+        <v>829</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>851</v>
+        <v>830</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>852</v>
+        <v>831</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>853</v>
+        <v>832</v>
       </c>
     </row>
   </sheetData>

--- a/출산준비물_통합데이터.xlsx
+++ b/출산준비물_통합데이터.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://m100001874-my.sharepoint.com/personal/kong090821_cbsn-e_cbe_go_kr/Documents/2026학년도/인공지능/출산준비물어플/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98710532-BBB6-4AE2-9B42-5B1E4A8157A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{98710532-BBB6-4AE2-9B42-5B1E4A8157A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8F983EA-94C6-436C-B8B3-9BAB50C50EAD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{2AB02095-D9A4-4E06-ABA4-2F7B367BFB5F}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="837">
   <si>
     <t>ID</t>
   </si>
@@ -2006,21 +2006,9 @@
     <t>todo_c_4</t>
   </si>
   <si>
-    <t>?뭺 [?덈갑?묒쥌] BCG(寃고빑) ?묒쥌 ?덉빟 諛??묒쥌 (?앺썑 4二??대궡)</t>
-  </si>
-  <si>
-    <t>?쇰궡??蹂닿굔??臾대즺, 二쇱궗?? vs 寃쏀뵾???좊즺, ?꾩옣?? ?ъ쟾 ?좏깮 諛?愿??蹂닿굔???뚯븘怨??ъ쟾 ?덉빟</t>
-  </si>
-  <si>
     <t>todo_c_5</t>
   </si>
   <si>
-    <t>태아보험 피보험자 아기 이름 등록</t>
-  </si>
-  <si>
-    <t>주민등록번호 발급 후 보험사 고객센터 등록</t>
-  </si>
-  <si>
     <t>todo_f_1</t>
   </si>
   <si>
@@ -2054,72 +2042,21 @@
     <t>todo_b_29</t>
   </si>
   <si>
-    <t>1. 異쒖궛 ??(以鍮꾧린)</t>
-  </si>
-  <si>
-    <t>#遺遺</t>
-  </si>
-  <si>
-    <t>?뭺 [?덈갑?묒쥌] 諛깆씪??Tdap) ?묒쥌 (?꾩떊 27~36二?沅뚯옣)</t>
-  </si>
-  <si>
-    <t>?좎깮??諛깆씪???꾩뿼 ?덈갑???꾪빐 ?곕え 諛??⑦렪, ?묒쑁??議곕?紐? ?숈떆 ?묒쥌 沅뚯옣 (?앺썑 2媛쒖썡 ????껜 ?꾨떖)</t>
-  </si>
-  <si>
     <t>todo_b_30</t>
   </si>
   <si>
-    <t>#?꾨쭏</t>
-  </si>
-  <si>
-    <t>?뭺 [?덈갑?묒쥌] ?명뵆猷⑥뿏???낃컧) ?묒쥌 (?꾩떊 二쇱닔 臾닿?)</t>
-  </si>
-  <si>
-    <t>?꾩궛遺 援?? 臾대즺 ?덈갑?묒쥌 吏???ъ뾽 ???(吏???섎즺湲곌? 諛?蹂닿굔?뚯뿉??臾대즺 ?묒쥌 媛??</t>
-  </si>
-  <si>
     <t>todo_h_5</t>
   </si>
   <si>
-    <t>2. 蹂묒썝 (?낆썝 諛?遺꾨쭔湲?</t>
-  </si>
-  <si>
-    <t>?뭺 [?덈갑?묒쥌] ?좎깮??B??媛꾩뿼 1李??묒쥌 ?뺤씤 (異쒖깮 吏곹썑)</t>
-  </si>
-  <si>
-    <t>異쒖깮 ??24?쒓컙 ?대궡 遺꾨쭔 蹂묒썝?먯꽌 湲곕낯 ?묒쥌 吏꾪뻾 (?꾧린?섏꺽 ?묒쥌 湲곕줉 ?뺤씤)</t>
-  </si>
-  <si>
     <t>todo_f_4</t>
   </si>
   <si>
-    <t>4. 媛??(吏?蹂듦? 諛?珥덇린 ?≪븘湲?</t>
-  </si>
-  <si>
-    <t>?뭺 [?덈갑?묒쥌] B??媛꾩뿼 2李??묒쥌 (?앺썑 1媛쒖썡)</t>
-  </si>
-  <si>
-    <t>?앺썑 1媛쒖썡 ?뚯븘怨?諛⑸Ц ?묒쥌 (?앺썑 4~6二?1李??곸쑀??嫄닿컯寃吏꾧낵 ?④퍡 諛⑸Ц 異붿쿇)</t>
-  </si>
-  <si>
     <t>todo_f_5</t>
   </si>
   <si>
-    <t>?뭺 [?덈갑?묒쥌] 5醫??쇳빀諛깆떊(DTaP쨌IPV쨌Hib쨌PCV) 1李?(?앺썑 2媛쒖썡)</t>
-  </si>
-  <si>
-    <t>?뷀봽?뚮━???뚯긽??諛깆씪???뚯븘留덈퉬/?뚯닔留됱뿼/?먮졃援ш퇏 援?? 臾대즺 ?묒쥌 (?묒쥌???鍮??댁뿴???ъ쟾 以鍮?</t>
-  </si>
-  <si>
     <t>todo_f_6</t>
   </si>
   <si>
-    <t>?뭺 [?덈갑?묒쥌] 濡쒗?諛붿씠?ъ뒪 1李??묒쥌 (?앺썑 2媛쒖썡)</t>
-  </si>
-  <si>
-    <t>援?? 臾대즺 吏??癒밸뒗 ???뺥깭). 濡쒗?由?뒪(2???꾨즺) vs 濡쒗???3???꾨즺) 以??좏깮 ????李⑥닔 ?숈씪 諛깆떊 ?좎?</t>
-  </si>
-  <si>
     <t>지역구분</t>
   </si>
   <si>
@@ -2541,6 +2478,81 @@
   </si>
   <si>
     <t>담은_육아용품_품목ID</t>
+  </si>
+  <si>
+    <t>💉 [예방접종] 백일해(Tdap) 접종 (임신 27~36주 권장)</t>
+  </si>
+  <si>
+    <t>신생아 백일해 감염 예방을 위해 산모 및 남편, 양육자(조부모) 동시 접종 권장 (생후 2개월 전 항체 전달).</t>
+  </si>
+  <si>
+    <t>💉 [예방접종] 인플루엔자(독감) 접종 (임신 주수 무관)</t>
+  </si>
+  <si>
+    <t>임산부 국가 무료 예방접종 지원 사업 대상 (지정 의료기관 및 보건소에서 무료 접종 가능).</t>
+  </si>
+  <si>
+    <t>todo_b_31</t>
+  </si>
+  <si>
+    <t>태아보험 가입 (11주차 이전 권장)</t>
+  </si>
+  <si>
+    <t>1차 기형아 검사(11~13주) 전 가입 필수(검사 결과 이상 소견 발생 시 가입 거절 또는 승인 보완 요청 가능). 산모 특약 및 신생아 선천이상·저체중·인큐베이터 입원일당 등 필수 특약 비교 선택.</t>
+  </si>
+  <si>
+    <t>💉 [예방접종] 신생아 B형 간염 1차 접종 확인 (출생 직후)</t>
+  </si>
+  <si>
+    <t>출생 후 24시간 이내 분만 병원에서 기본 접종 진행 (아기수첩 접종 기록 확인).</t>
+  </si>
+  <si>
+    <t>todo_h_6</t>
+  </si>
+  <si>
+    <t>퇴원 시 보험 청구용 필수 서류 발급 요청</t>
+  </si>
+  <si>
+    <t>퇴원 전 원무과에 사전 요청: 진단서(질병분류코드 필수), 입퇴원확인서, 진료비 계산서·영수증, 진료비 세부내역서 원본 2부 수령 (보험금 청구 및 회사/연말정산 제출용).</t>
+  </si>
+  <si>
+    <t>💉 [예방접종] BCG(결핵) 접종 예약 및 접종 (생후 4주 이내)</t>
+  </si>
+  <si>
+    <t>피내용(보건소 무료, 주사형) vs 경피용(유료, 도장형) 사전 선택 및 관할 보건소/소아과 사전 예약.</t>
+  </si>
+  <si>
+    <t>태아보험 피보험자 등록 &amp; 성별(남아·여아) 보험료 정산</t>
+  </si>
+  <si>
+    <t>출생신고(등본 발급) 후 아기 주민번호 등록 및 태아→영유아 피보험자 확정. 가입 시 남아 기준 보험료에서 여아 출생 시 기납입 보험료 차액 환급 및 출생 후 보험료/약관 재정산 확인.</t>
+  </si>
+  <si>
+    <t>todo_c_6</t>
+  </si>
+  <si>
+    <t>출산·신생아 보험금 청구 (수술·입원 특약 신청)</t>
+  </si>
+  <si>
+    <t>제왕절개 수술비, 신생아 입원/인큐베이터/치료비 등 특약 보험금 청구. 병원에서 발급받은 진단서(질병코드 기재), 입퇴원확인서, 진료비 영수증, 세부내역서 구비 후 각 보험사 모바일 앱으로 간편 접수.</t>
+  </si>
+  <si>
+    <t>💉 [예방접종] B형 간염 2차 접종 (생후 1개월)</t>
+  </si>
+  <si>
+    <t>생후 1개월 소아과 방문 접종 (생후 4~6주 1차 영유아 건강검진과 함께 방문 추천).</t>
+  </si>
+  <si>
+    <t>💉 [예방접종] 5종 혼합백신(DTaP·IPV·Hib·PCV) 1차 (생후 2개월)</t>
+  </si>
+  <si>
+    <t>디프테리아/파상풍/백일해/소아마비/뇌수막염/폐렴구균 국가 무료 접종 (접종열 대비 해열제 사전 준비).</t>
+  </si>
+  <si>
+    <t>💉 [예방접종] 로타바이러스 1차 접종 (생후 2개월)</t>
+  </si>
+  <si>
+    <t>국가 무료 지원 (먹는 약 형태). 로타릭스(2회 완료) vs 로타텍(3회 완료) 중 선택 후 전 차수 동일 백신 유지.</t>
   </si>
 </sst>
 </file>
@@ -5812,7 +5824,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2190E7C4-5255-4C66-A5B8-E31D4B2E5FBA}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.125" bestFit="1" customWidth="1"/>
@@ -6317,313 +6329,365 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>630</v>
+        <v>665</v>
       </c>
       <c r="B30" t="s">
-        <v>631</v>
+        <v>543</v>
       </c>
       <c r="C30" t="s">
         <v>593</v>
       </c>
       <c r="D30" t="s">
-        <v>632</v>
+        <v>812</v>
       </c>
       <c r="E30" t="s">
-        <v>633</v>
+        <v>813</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>634</v>
+        <v>666</v>
       </c>
       <c r="B31" t="s">
-        <v>631</v>
+        <v>543</v>
       </c>
       <c r="C31" t="s">
-        <v>544</v>
+        <v>615</v>
       </c>
       <c r="D31" t="s">
-        <v>635</v>
+        <v>814</v>
       </c>
       <c r="E31" t="s">
-        <v>636</v>
+        <v>815</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>637</v>
+        <v>816</v>
       </c>
       <c r="B32" t="s">
-        <v>631</v>
+        <v>543</v>
       </c>
       <c r="C32" t="s">
         <v>593</v>
       </c>
       <c r="D32" t="s">
-        <v>638</v>
+        <v>817</v>
       </c>
       <c r="E32" t="s">
-        <v>639</v>
+        <v>818</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="B33" t="s">
         <v>631</v>
       </c>
       <c r="C33" t="s">
-        <v>544</v>
+        <v>593</v>
       </c>
       <c r="D33" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="E33" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="B34" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="C34" t="s">
         <v>544</v>
       </c>
       <c r="D34" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="E34" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="B35" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="C35" t="s">
-        <v>544</v>
+        <v>593</v>
       </c>
       <c r="D35" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="E35" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="B36" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="C36" t="s">
         <v>544</v>
       </c>
       <c r="D36" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="E36" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>653</v>
+        <v>667</v>
       </c>
       <c r="B37" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="C37" t="s">
         <v>593</v>
       </c>
       <c r="D37" t="s">
-        <v>654</v>
+        <v>819</v>
       </c>
       <c r="E37" t="s">
-        <v>655</v>
+        <v>820</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>656</v>
+        <v>821</v>
       </c>
       <c r="B38" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="C38" t="s">
         <v>544</v>
       </c>
       <c r="D38" t="s">
-        <v>657</v>
+        <v>822</v>
       </c>
       <c r="E38" t="s">
-        <v>658</v>
+        <v>823</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
       <c r="B39" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="C39" t="s">
         <v>544</v>
       </c>
       <c r="D39" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="E39" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="B40" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="C40" t="s">
-        <v>593</v>
+        <v>544</v>
       </c>
       <c r="D40" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
       <c r="E40" t="s">
-        <v>665</v>
+        <v>649</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>666</v>
+        <v>650</v>
       </c>
       <c r="B41" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="C41" t="s">
-        <v>593</v>
+        <v>544</v>
       </c>
       <c r="D41" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="E41" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="B42" t="s">
-        <v>670</v>
+        <v>644</v>
       </c>
       <c r="C42" t="s">
-        <v>671</v>
+        <v>593</v>
       </c>
       <c r="D42" t="s">
-        <v>672</v>
+        <v>824</v>
       </c>
       <c r="E42" t="s">
-        <v>673</v>
+        <v>825</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>674</v>
+        <v>654</v>
       </c>
       <c r="B43" t="s">
-        <v>670</v>
+        <v>644</v>
       </c>
       <c r="C43" t="s">
-        <v>675</v>
+        <v>544</v>
       </c>
       <c r="D43" t="s">
-        <v>676</v>
+        <v>826</v>
       </c>
       <c r="E43" t="s">
-        <v>677</v>
+        <v>827</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>678</v>
+        <v>828</v>
       </c>
       <c r="B44" t="s">
-        <v>679</v>
+        <v>644</v>
       </c>
       <c r="C44" t="s">
-        <v>671</v>
+        <v>593</v>
       </c>
       <c r="D44" t="s">
-        <v>680</v>
+        <v>829</v>
       </c>
       <c r="E44" t="s">
-        <v>681</v>
+        <v>830</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>682</v>
+        <v>655</v>
       </c>
       <c r="B45" t="s">
-        <v>683</v>
+        <v>656</v>
       </c>
       <c r="C45" t="s">
-        <v>671</v>
+        <v>544</v>
       </c>
       <c r="D45" t="s">
-        <v>684</v>
+        <v>657</v>
       </c>
       <c r="E45" t="s">
-        <v>685</v>
+        <v>658</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>686</v>
+        <v>659</v>
       </c>
       <c r="B46" t="s">
-        <v>683</v>
+        <v>656</v>
       </c>
       <c r="C46" t="s">
-        <v>671</v>
+        <v>593</v>
       </c>
       <c r="D46" t="s">
-        <v>687</v>
+        <v>660</v>
       </c>
       <c r="E46" t="s">
-        <v>688</v>
+        <v>661</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>689</v>
+        <v>662</v>
       </c>
       <c r="B47" t="s">
-        <v>683</v>
+        <v>656</v>
       </c>
       <c r="C47" t="s">
-        <v>671</v>
+        <v>593</v>
       </c>
       <c r="D47" t="s">
-        <v>690</v>
+        <v>663</v>
       </c>
       <c r="E47" t="s">
-        <v>691</v>
+        <v>664</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>668</v>
+      </c>
+      <c r="B48" t="s">
+        <v>656</v>
+      </c>
+      <c r="C48" t="s">
+        <v>593</v>
+      </c>
+      <c r="D48" t="s">
+        <v>831</v>
+      </c>
+      <c r="E48" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>669</v>
+      </c>
+      <c r="B49" t="s">
+        <v>656</v>
+      </c>
+      <c r="C49" t="s">
+        <v>593</v>
+      </c>
+      <c r="D49" t="s">
+        <v>833</v>
+      </c>
+      <c r="E49" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>670</v>
+      </c>
+      <c r="B50" t="s">
+        <v>656</v>
+      </c>
+      <c r="C50" t="s">
+        <v>593</v>
+      </c>
+      <c r="D50" t="s">
+        <v>835</v>
+      </c>
+      <c r="E50" t="s">
+        <v>836</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6647,363 +6711,363 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>692</v>
+        <v>671</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>693</v>
+        <v>672</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>694</v>
+        <v>673</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>695</v>
+        <v>674</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>696</v>
+        <v>675</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>697</v>
+        <v>676</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>698</v>
+        <v>677</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>699</v>
+        <v>678</v>
       </c>
       <c r="B2" t="s">
-        <v>700</v>
+        <v>679</v>
       </c>
       <c r="C2" t="s">
-        <v>701</v>
+        <v>680</v>
       </c>
       <c r="D2" t="s">
-        <v>702</v>
+        <v>681</v>
       </c>
       <c r="E2" t="s">
-        <v>703</v>
+        <v>682</v>
       </c>
       <c r="F2" t="s">
-        <v>704</v>
+        <v>683</v>
       </c>
       <c r="G2" t="s">
-        <v>705</v>
+        <v>684</v>
       </c>
       <c r="H2" t="s">
-        <v>706</v>
+        <v>685</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>707</v>
+        <v>686</v>
       </c>
       <c r="B3" t="s">
-        <v>700</v>
+        <v>679</v>
       </c>
       <c r="C3" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="D3" t="s">
-        <v>709</v>
+        <v>688</v>
       </c>
       <c r="E3" t="s">
-        <v>710</v>
+        <v>689</v>
       </c>
       <c r="F3" t="s">
-        <v>711</v>
+        <v>690</v>
       </c>
       <c r="G3" t="s">
-        <v>712</v>
+        <v>691</v>
       </c>
       <c r="H3" t="s">
-        <v>706</v>
+        <v>685</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>713</v>
+        <v>692</v>
       </c>
       <c r="B4" t="s">
-        <v>700</v>
+        <v>679</v>
       </c>
       <c r="C4" t="s">
-        <v>714</v>
+        <v>693</v>
       </c>
       <c r="D4" t="s">
-        <v>709</v>
+        <v>688</v>
       </c>
       <c r="E4" t="s">
-        <v>715</v>
+        <v>694</v>
       </c>
       <c r="F4" t="s">
-        <v>716</v>
+        <v>695</v>
       </c>
       <c r="G4" t="s">
-        <v>717</v>
+        <v>696</v>
       </c>
       <c r="H4" t="s">
-        <v>706</v>
+        <v>685</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>718</v>
+        <v>697</v>
       </c>
       <c r="B5" t="s">
+        <v>679</v>
+      </c>
+      <c r="C5" t="s">
+        <v>698</v>
+      </c>
+      <c r="D5" t="s">
+        <v>699</v>
+      </c>
+      <c r="E5" t="s">
         <v>700</v>
       </c>
-      <c r="C5" t="s">
-        <v>719</v>
-      </c>
-      <c r="D5" t="s">
-        <v>720</v>
-      </c>
-      <c r="E5" t="s">
-        <v>721</v>
-      </c>
       <c r="F5" t="s">
-        <v>722</v>
+        <v>701</v>
       </c>
       <c r="G5" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="H5" t="s">
-        <v>724</v>
+        <v>703</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
       <c r="B6" t="s">
-        <v>700</v>
+        <v>679</v>
       </c>
       <c r="C6" t="s">
-        <v>726</v>
+        <v>705</v>
       </c>
       <c r="D6" t="s">
-        <v>702</v>
+        <v>681</v>
       </c>
       <c r="E6" t="s">
-        <v>727</v>
+        <v>706</v>
       </c>
       <c r="F6" t="s">
-        <v>728</v>
+        <v>707</v>
       </c>
       <c r="G6" t="s">
-        <v>729</v>
+        <v>708</v>
       </c>
       <c r="H6" t="s">
-        <v>730</v>
+        <v>709</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>731</v>
+        <v>710</v>
       </c>
       <c r="B7" t="s">
-        <v>700</v>
+        <v>679</v>
       </c>
       <c r="C7" t="s">
-        <v>732</v>
+        <v>711</v>
       </c>
       <c r="D7" t="s">
-        <v>733</v>
+        <v>712</v>
       </c>
       <c r="E7" t="s">
-        <v>734</v>
+        <v>713</v>
       </c>
       <c r="F7" t="s">
-        <v>735</v>
+        <v>714</v>
       </c>
       <c r="G7" t="s">
-        <v>736</v>
+        <v>715</v>
       </c>
       <c r="H7" t="s">
-        <v>737</v>
+        <v>716</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="B8" t="s">
-        <v>739</v>
+        <v>718</v>
       </c>
       <c r="C8" t="s">
-        <v>740</v>
+        <v>719</v>
       </c>
       <c r="D8" t="s">
-        <v>702</v>
+        <v>681</v>
       </c>
       <c r="E8" t="s">
-        <v>741</v>
+        <v>720</v>
       </c>
       <c r="F8" t="s">
-        <v>742</v>
+        <v>721</v>
       </c>
       <c r="G8" t="s">
-        <v>743</v>
+        <v>722</v>
       </c>
       <c r="H8" t="s">
-        <v>744</v>
+        <v>723</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>745</v>
+        <v>724</v>
       </c>
       <c r="B9" t="s">
-        <v>739</v>
+        <v>718</v>
       </c>
       <c r="C9" t="s">
-        <v>746</v>
+        <v>725</v>
       </c>
       <c r="D9" t="s">
-        <v>702</v>
+        <v>681</v>
       </c>
       <c r="E9" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
       <c r="F9" t="s">
-        <v>748</v>
+        <v>727</v>
       </c>
       <c r="G9" t="s">
-        <v>749</v>
+        <v>728</v>
       </c>
       <c r="H9" t="s">
-        <v>744</v>
+        <v>723</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>750</v>
+        <v>729</v>
       </c>
       <c r="B10" t="s">
-        <v>751</v>
+        <v>730</v>
       </c>
       <c r="C10" t="s">
-        <v>752</v>
+        <v>731</v>
       </c>
       <c r="D10" t="s">
-        <v>753</v>
+        <v>732</v>
       </c>
       <c r="E10" t="s">
-        <v>754</v>
+        <v>733</v>
       </c>
       <c r="F10" t="s">
-        <v>755</v>
+        <v>734</v>
       </c>
       <c r="G10" t="s">
-        <v>756</v>
+        <v>735</v>
       </c>
       <c r="H10" t="s">
-        <v>757</v>
+        <v>736</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>758</v>
+        <v>737</v>
       </c>
       <c r="B11" t="s">
-        <v>759</v>
+        <v>738</v>
       </c>
       <c r="C11" t="s">
-        <v>760</v>
+        <v>739</v>
       </c>
       <c r="D11" t="s">
-        <v>753</v>
+        <v>732</v>
       </c>
       <c r="E11" t="s">
-        <v>761</v>
+        <v>740</v>
       </c>
       <c r="F11" t="s">
-        <v>762</v>
+        <v>741</v>
       </c>
       <c r="G11" t="s">
-        <v>763</v>
+        <v>742</v>
       </c>
       <c r="H11" t="s">
-        <v>764</v>
+        <v>743</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>765</v>
+        <v>744</v>
       </c>
       <c r="B12" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="C12" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="D12" t="s">
-        <v>709</v>
+        <v>688</v>
       </c>
       <c r="E12" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F12" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="G12" t="s">
-        <v>770</v>
+        <v>749</v>
       </c>
       <c r="H12" t="s">
-        <v>771</v>
+        <v>750</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="B13" t="s">
-        <v>773</v>
+        <v>752</v>
       </c>
       <c r="C13" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="D13" t="s">
-        <v>709</v>
+        <v>688</v>
       </c>
       <c r="E13" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F13" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="G13" t="s">
-        <v>770</v>
+        <v>749</v>
       </c>
       <c r="H13" t="s">
-        <v>771</v>
+        <v>750</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>777</v>
+        <v>756</v>
       </c>
       <c r="B14" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="C14" t="s">
-        <v>779</v>
+        <v>758</v>
       </c>
       <c r="D14" t="s">
-        <v>753</v>
+        <v>732</v>
       </c>
       <c r="E14" t="s">
-        <v>780</v>
+        <v>759</v>
       </c>
       <c r="F14" t="s">
-        <v>781</v>
+        <v>760</v>
       </c>
       <c r="G14" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="H14" t="s">
-        <v>771</v>
+        <v>750</v>
       </c>
     </row>
   </sheetData>
@@ -7038,132 +7102,132 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>783</v>
+        <v>762</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>786</v>
+        <v>765</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>788</v>
+        <v>767</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>789</v>
+        <v>768</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>790</v>
+        <v>769</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>792</v>
+        <v>771</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>793</v>
+        <v>772</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>794</v>
+        <v>773</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>795</v>
+        <v>774</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>796</v>
+        <v>775</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>797</v>
+        <v>776</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>798</v>
+        <v>777</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>799</v>
+        <v>778</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>800</v>
+        <v>779</v>
       </c>
       <c r="B2" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="C2" t="s">
-        <v>802</v>
+        <v>781</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="B3" t="s">
-        <v>804</v>
+        <v>783</v>
       </c>
       <c r="C3" t="s">
-        <v>805</v>
+        <v>784</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>806</v>
+        <v>785</v>
       </c>
       <c r="B4" t="s">
-        <v>807</v>
+        <v>786</v>
       </c>
       <c r="C4" t="s">
-        <v>808</v>
+        <v>787</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>809</v>
+        <v>788</v>
       </c>
       <c r="B5" t="s">
-        <v>810</v>
+        <v>789</v>
       </c>
       <c r="C5" t="s">
-        <v>811</v>
+        <v>790</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>812</v>
+        <v>791</v>
       </c>
       <c r="B6" t="s">
-        <v>813</v>
+        <v>792</v>
       </c>
       <c r="C6" t="s">
-        <v>814</v>
+        <v>793</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="B7" t="s">
-        <v>816</v>
+        <v>795</v>
       </c>
       <c r="C7" t="s">
-        <v>817</v>
+        <v>796</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>818</v>
+        <v>797</v>
       </c>
       <c r="B8" t="s">
-        <v>819</v>
+        <v>798</v>
       </c>
       <c r="C8" t="s">
-        <v>820</v>
+        <v>799</v>
       </c>
     </row>
   </sheetData>
@@ -7192,40 +7256,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>821</v>
+        <v>800</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>822</v>
+        <v>801</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>823</v>
+        <v>802</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>824</v>
+        <v>803</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>825</v>
+        <v>804</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>826</v>
+        <v>805</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>827</v>
+        <v>806</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>828</v>
+        <v>807</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>829</v>
+        <v>808</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>830</v>
+        <v>809</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>831</v>
+        <v>810</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>832</v>
+        <v>811</v>
       </c>
     </row>
   </sheetData>

--- a/출산준비물_통합데이터.xlsx
+++ b/출산준비물_통합데이터.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://m100001874-my.sharepoint.com/personal/kong090821_cbsn-e_cbe_go_kr/Documents/2026학년도/인공지능/출산준비물어플/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{98710532-BBB6-4AE2-9B42-5B1E4A8157A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8F983EA-94C6-436C-B8B3-9BAB50C50EAD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25313034-6AC3-4C81-B80F-DD7EA9DDF693}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{2AB02095-D9A4-4E06-ABA4-2F7B367BFB5F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{2AB02095-D9A4-4E06-ABA4-2F7B367BFB5F}"/>
   </bookViews>
   <sheets>
     <sheet name="출산가방 체크리스트" sheetId="1" r:id="rId1"/>
@@ -25,15 +25,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -42,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="1335">
   <si>
     <t>ID</t>
   </si>
@@ -1670,412 +1661,1538 @@
     <t>상세팁/가이드</t>
   </si>
   <si>
+    <t>지역구분</t>
+  </si>
+  <si>
+    <t>혜택명</t>
+  </si>
+  <si>
+    <t>지원형태(바우처/현금)</t>
+  </si>
+  <si>
+    <t>지원금액 및 내용</t>
+  </si>
+  <si>
+    <t>신청자격</t>
+  </si>
+  <si>
+    <t>신청시기</t>
+  </si>
+  <si>
+    <t>신청처</t>
+  </si>
+  <si>
+    <t>구분</t>
+  </si>
+  <si>
+    <t>추천품목ID1</t>
+  </si>
+  <si>
+    <t>품목명1</t>
+  </si>
+  <si>
+    <t>추천품목ID2</t>
+  </si>
+  <si>
+    <t>품목명2</t>
+  </si>
+  <si>
+    <t>추천품목ID3</t>
+  </si>
+  <si>
+    <t>품목명3</t>
+  </si>
+  <si>
+    <t>추천품목ID4</t>
+  </si>
+  <si>
+    <t>품목명4</t>
+  </si>
+  <si>
+    <t>추천품목ID5</t>
+  </si>
+  <si>
+    <t>품목명5</t>
+  </si>
+  <si>
+    <t>추천품목ID6</t>
+  </si>
+  <si>
+    <t>품목명6</t>
+  </si>
+  <si>
+    <t>추천품목ID7</t>
+  </si>
+  <si>
+    <t>품목명7</t>
+  </si>
+  <si>
+    <t>추천품목ID8</t>
+  </si>
+  <si>
+    <t>품목명8</t>
+  </si>
+  <si>
+    <t>제왕절개</t>
+  </si>
+  <si>
+    <t>m_cloth_7, m_hyg_7, m_hyg_1, m_cloth_5, g_life_1</t>
+  </si>
+  <si>
+    <t>산후복대, 흉터시트, 맘스안심팬티, 압박스타킹, 꺾인빨대 텀블러</t>
+  </si>
+  <si>
+    <t>자연분만</t>
+  </si>
+  <si>
+    <t>m_hyg_8, m_hyg_3, m_hyg_2</t>
+  </si>
+  <si>
+    <t>회음부방석, 마이비데, 오버나이트 생리대 세트</t>
+  </si>
+  <si>
+    <t>조리원이용</t>
+  </si>
+  <si>
+    <t>m_feed_1, m_feed_2, m_feed_4, m_feed_6, m_feed_7, m_cloth_6, b_care_3, b_care_4</t>
+  </si>
+  <si>
+    <t>수유패드, 저장팩, 유두크림, 유축깔때기, 손목보호대, 아기로션/영양제</t>
+  </si>
+  <si>
+    <t>자택조리</t>
+  </si>
+  <si>
+    <t>m_feed_1, m_feed_4, b_care_3</t>
+  </si>
+  <si>
+    <t>기본 수유패드, 유두보호크림, 아기로션</t>
+  </si>
+  <si>
+    <t>공통산모</t>
+  </si>
+  <si>
+    <t>m_cloth_1, m_cloth_2, m_cloth_3, m_cloth_4, m_cloth_8, m_sk_1, m_sk_2, m_sk_3</t>
+  </si>
+  <si>
+    <t>수유브라, 산모팬티, 무압박양말, 슬리퍼, 세면/화장품 세트</t>
+  </si>
+  <si>
+    <t>공통신생아</t>
+  </si>
+  <si>
+    <t>b_cloth_1, b_cloth_2, b_cloth_3, b_care_1, b_safe_1</t>
+  </si>
+  <si>
+    <t>배냇저고리, 속싸개, 겉싸개, 손수건, 카시트</t>
+  </si>
+  <si>
+    <t>공통보호자</t>
+  </si>
+  <si>
+    <t>g_doc_1, g_doc_2, g_life_4</t>
+  </si>
+  <si>
+    <t>산모수첩/신분증, 결제수단, 충전기/멀티탭</t>
+  </si>
+  <si>
+    <t>기록일시</t>
+  </si>
+  <si>
+    <t>사용자구분</t>
+  </si>
+  <si>
+    <t>이벤트</t>
+  </si>
+  <si>
+    <t>분만법</t>
+  </si>
+  <si>
+    <t>조리원여부</t>
+  </si>
+  <si>
+    <t>아기성별</t>
+  </si>
+  <si>
+    <t>지역</t>
+  </si>
+  <si>
+    <t>출산예정일</t>
+  </si>
+  <si>
+    <t>담은_출산가방수</t>
+  </si>
+  <si>
+    <t>담은_출산가방_품목ID</t>
+  </si>
+  <si>
+    <t>담은_육아용품수</t>
+  </si>
+  <si>
+    <t>담은_육아용품_품목ID</t>
+  </si>
+  <si>
     <t>todo_b_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1. 출산 전 (준비기)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>#아빠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>집안 전체 대청소 실시</t>
-  </si>
-  <si>
-    <t>청소기로 바닥 및 침대 먼지 제거</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>청소기로 바닥 및 침대 먼지 제거, 소파·창틀 먼지 청소</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>필요없는 가전가구 숨기기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>동선 확보 및 아기 안전 대비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>커텐 먼지 털기 및 세탁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>아기 호흡기 보호를 위한 사전 청소</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>천장 및 벽 먼지 제거</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>상부 구역 먼지 제거</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>각종 가구위 쌓인 먼지 제거</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>손이 닿지 않는 상단 먼지 닦기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>창문 및 창틀 청소</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>창문, 베란다문, 현관중문 및 틀 청소</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>바닥 스팀 청소 및 매트 깔기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>위생 소독 및 층간소음/안전 대비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>자동차 실내외 세차</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>내부 스팀 손세차 실시</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>소파 및 침대 청소</t>
-  </si>
-  <si>
-    <t>매트리스/소파 딥클리닝</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>매트리스/소파 딥클리닝 (필요시 전문 업체 예약)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>유아차 세탁업체 예약</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>출산 전 미리 세탁 완료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>화장실 청소</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>유리, 변기, 줄눈, 세면대, 욕조 청소</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>아기비데 설치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>세면대 수전 교체 및 아기비데 설치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>샤워기 필터 교체</t>
-  </si>
-  <si>
-    <t>집안 전체 필터 새것으로 교체</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>집안 전체 샤워기/세면대 필터 새것으로 교체</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_14</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>워시타워, 식세기 통살균세척</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>내부 세척, 세제통 및 오수필터 세척</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>아기 용품 소독 세척</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>가습기, 분유 용품 등 사전 소독</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_16</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>에어컨 필터 청소</t>
-  </si>
-  <si>
-    <t>먼지 제거 및 곰팡이 방지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>먼지 제거 및 곰팡이 방지 세척</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_17</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>#부부</t>
-  </si>
-  <si>
-    <t>아기 옷, 턱받이 선세탁</t>
-  </si>
-  <si>
-    <t>아기 전용 세제로 세탁 후 지퍼백 보관</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아기 옷, 턱받이, 방수패드 선세탁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아기 옷, 턱받이, 방수패드, 인형 등을 아기 전용 세제로 세탁 후 지퍼백 보관</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_18</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>아기 손수건 선세탁</t>
-  </si>
-  <si>
-    <t>거즈/엠보 구분하여 세탁 및 건조</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>거즈/엠보 구분하여 아기 전용 세제로 세탁 및 자연건조 후 지퍼백 보관</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_19</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>실내 온도 세팅</t>
-  </si>
-  <si>
-    <t>22~24°C 유지 환경 조성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>실내 온도 22~24°C 유지 환경 조성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_20</t>
-  </si>
-  <si>
-    <t>실내 습도 세팅</t>
-  </si>
-  <si>
-    <t>40~60% 유지 (가습기 점검)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>실내 습도 환경 구축</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>습도 40~60% 항상 유지할 수 있도록 가습기 점검 및 가동 환경 준비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_21</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>트립트랩 뉴본 설치</t>
-  </si>
-  <si>
-    <t>식탁 옆 사전 세팅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>식탁 옆 사전 세팅 및 각도 조절</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_22</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>홈캠 설치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>카메라 각도 및 Wi-Fi 연결 점검</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_23</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>맘마존 설치</t>
-  </si>
-  <si>
-    <t>유팡, 젖병 열탕, 분유포트 세척 및 배치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>유팡 소독기, 젖병 열탕, 분유포트 세척 및 배치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_24</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>#엄마</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>출산 가방 최종 패킹</t>
-  </si>
-  <si>
-    <t>병원/조리원 서류 및 산모/아기 용품 챙기기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임신 37주차 전후로 병원/조리원 서류 및 산모/신생아 용품 준비 완료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>정부지원 산후도우미 바우처 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>출산 예정일 40일 전부터 보건소/복지로 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_26</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>분만 병원 동선 및 야간 주차 파악</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>야간/공휴일 응급실 진입 동선 미리 숙지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_27</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>비상 연락망 공유</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>양가, 병원, 조리원, 도우미 업체 연락처 저장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_b_28</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>산모 젤네일 제거 및 왁싱</t>
-  </si>
-  <si>
-    <t>수술 모니터링용 손발톱 정돈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수술 모니터링용 손발톱 정돈 및 산모 왁싱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_b_29</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>💉 [예방접종] 백일해(Tdap) 접종 (임신 27~36주 권장)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신생아 백일해 감염 예방을 위해 산모 및 남편, 양육자(조부모) 동시 접종 권장 (생후 2개월 전 항체 전달).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_b_30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>💉 [예방접종] 인플루엔자(독감) 접종 (임신 주수 무관)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임산부 국가 무료 예방접종 지원 사업 대상 (지정 의료기관 및 보건소에서 무료 접종 가능).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_b_31</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>태아보험 가입 (11주차 이전 권장)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 기형아 검사(11~13주) 전 가입 필수(검사 결과 이상 소견 발생 시 가입 거절 또는 승인 보완 요청 가능). 산모 특약 및 신생아 선천이상·저체중·인큐베이터 입원일당 등 필수 특약 비교 선택.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_b_32</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임산부 검진 복지포인트 신청 (공무원/교직원 등)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(공무원/교직원 등 해당 시) 공무원 맞춤형 복지포털에서 태아·산모 검진 복지포인트(10만 원) 사전 신청.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_h_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2. 병원 (입원 및 분만기)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>아기 이름 후보 결정</t>
-  </si>
-  <si>
-    <t>출생신고를 위한 이름 미리 결정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출생 후 4주 이내 출생신고를 위해 인명용 한자를 포함한 이름 후보군을 미리 확정.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_h_2</t>
-  </si>
-  <si>
-    <t>입원 수속 및 병실 배정</t>
-  </si>
-  <si>
-    <t>보호자 출입증 수령 및 입원 안내 숙지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>양가 부모님 출산 소식 전달 &amp; 면회 수칙 안내</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출산 직후 산모·아기 상태를 연락하고, 병원 면회 제한 수칙을 미리 알려 부모님 헛걸음 방지.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_h_3</t>
-  </si>
-  <si>
-    <t>출생 증명서 발급 신청</t>
-  </si>
-  <si>
-    <t>출생신고 및 행정처리를 위한 원본 2~3부 수령</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산후조리원 출산 알림</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>예약 업체에 출산 소식을 전하고, 정확한 조리원 입실 일정을 최종 픽스.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_h_4</t>
-  </si>
-  <si>
-    <t>신생아 청각/대사이상 선별검사 동의</t>
-  </si>
-  <si>
-    <t>검사 항목 및 비급여 선택사항 확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산후도우미 업체 출산 알림</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조리원 퇴소일 전달 및 도우미 시작 일정을 최종 픽스.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산모 압박스타킹 착용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>다리 부기 예방용 압박스타킹 착용 및 정맥 혈전 예방.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>항생제 발진 수시 체크</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>항생제 발진 체크(비판텐 도포) 및 피부 상태 확인.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>병원 모유 차 요청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>병원에 모유 차 요청 및 병원 수유 지원 서비스 확인.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신생아실 영양제 전달</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>준비해 간 신생아용 유산균, 비타민 D 등을 신생아실 간호사에게 전달.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출생증명서 발급</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출생증명서 원본 2~3부 발급(스마트폰 사진/PDF 저장 필수).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>병원비 내역서 출력</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>회사 제출 및 연말정산용 진료비 영수증·상세내역서 수령.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>퇴원 시 보험 청구용 필수 서류 발급 요청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>퇴원 전 원무과에 사전 요청: 진단서(질병분류코드 필수), 입퇴원확인서, 진료비 계산서·영수증, 진료비 세부내역서 원본 2부 수령 (보험금 청구 및 회사/연말정산 제출용).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산후 검진 예약</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>실밥 제거 및 산모 건강 체크 일정 확정.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>💉 [예방접종] 1차 B형간염 접종 확인 &amp; 캘린더 등록</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 B형간염(출생 직후) 접종 확인, 다음 예방접종일 및 산모/아기 외래 관찰 일정을 캘린더에 등록.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_14</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>병원 내 무료 바우처 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>병원 내 비치된 출산/육아 관련 무료 바우처 직접 신청.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수술부위/회음부 케어 연고 확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수간호사에게 소독 및 연고 사용법 숙지.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_16</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>선천성 대사이상 검사 동의서 작성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>병원 제출용 기본/확장 선천성 대사이상 선별검사 선택 및 동의서 작성.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_17</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>병원비/수술비 결제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지역화폐 가능 여부 확인 및 병원비 결제.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_18</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>분만실 촬영 및 탯줄 채취 확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>분만실 대기 시 탯줄 자르기 및 영상·사진 촬영 가능 여부를 의료진에게 사전 확인.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_19</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아기 첫 순간 영상/사진 기록</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>탄생 직후, 신생아실 이동, 간호사의 신체 특징 설명 시 카메라 초점을 아기에게 맞춰 영상 기록.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신생아 병원/국민 등록 &amp; 팔찌 확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산모 후처치 동안 아기와 동행하여 신생아 팔찌 착용을 확인하고 병원 및 국민 등록 진행.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_21</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산모 밀착 간호 (손발 되기 세팅)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출혈량·통증 수시 체크, 물·구부러지는 빨대·휴대폰·도넛방석(자연분만 회음부용)을 산모 옆에 세팅.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_22</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산모 신체 회복 &amp; 보행 부축</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자연분만 시 자궁 수축 배 마사지, 제왕절개 시(8시간 누워있기 후) 상체 일으키기 및 보행 동행(혈전 예방).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_23</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산모 감정 공감 &amp; 면회객 조율</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>해결책보다 감정 공감 위주로 대화하며, 외부 면회객을 적절히 제지·조율하여 산모 피로 방지.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_24</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>회사 연락 및 휴가 일정 조율</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>인사팀 및 상사에 소식 공유, 출산휴가/연차 사용 일정 협의 및 필요 제출 서류 확인.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구독 서비스 및 학원 일시 중단</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신문, 정기배송, 학원, 기타 구독 서비스에 연락하여 일시 중단/연기 요청.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_26</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>회진 및 퇴원약 복용법 이중 체크</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>의사 회진 시간 확인, 산모 퇴원약 복용법 및 젖몸살 대비 유축/수유 물품 함께 챙기기.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_27</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>바구니 카시트 미리 설치 &amp; 연습</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>퇴원 당일 당황하지 않도록 차량에 카시트를 미리 장착하고 안전벨트 체결 예행연습 실시.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_h_28</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>퇴원 시 신생아 용품 준비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신생아실 인계 시 필요한 배냇저고리, 속싸개, 겉싸개, 방한용품 등 미리 챙기기.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_c_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>3. 조리원 (회복 및 행정 처리기)</t>
-  </si>
-  <si>
-    <t>온라인/방문 출생신고 완료</t>
-  </si>
-  <si>
-    <t>대법원 전자가족관계등록시스템 또는 주민센터 방문</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출생신고 진행 (방문 권장)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>관할 행정복지센터 방문 신고 (준비물: 출생증명서 원본, 부모 신분증, 가족관계증명서, 통장계좌) 또는 대법원 온라인 신고.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_c_2</t>
-  </si>
-  <si>
-    <t>첫만남이용권, 부모급여, 아동수당 신청</t>
-  </si>
-  <si>
-    <t>행복출산 원스톱 서비스로 한 번에 통합 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫만남이용권 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫째아 200만 원, 둘째아 이상 300만 원 국민행복카드 포인트 (출생신고 시 함께 신청).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_c_3</t>
-  </si>
-  <si>
-    <t>한전 출산가구 전기요금 30% 감면 신청</t>
-  </si>
-  <si>
-    <t>한전 고객센터(123) 또는 한전ON 어플로 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아동수당 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>만 8세 미만 월 10만 원 계좌 입금 (행복출산 원스톱으로 함께 신청).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_c_4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부모급여 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>만 0세 월 100만 원 현금 계좌 입금 (행복출산 원스톱으로 함께 신청).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>todo_c_5</t>
-  </si>
-  <si>
-    <t>todo_f_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지자체 지원금/산후조리비/축하금 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지자체별 산후조리비 지원금 및 출산축하금 차등 신청 (수원페이, 서울형 등).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기요금 &amp; 가스·난방비 감면 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기요금 감면: 한전(123) 전화 신청 (3년간 30% 할인), 가스/난방비 감면 및 지자체 출산선물 함께 신청.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아파트 관리소 고지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기요금 감면 신청 내역을 관리사무소에 전달하여 관리비 고지서 반영 확인.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>태아보험 피보험자 등록 &amp; 성별(남아·여아) 보험료 정산</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출생신고(등본 발급) 후 아기 주민번호 등록 및 태아→영유아 피보험자 확정. 가입 시 남아 기준 보험료에서 여아 출생 시 기납입 보험료 차액 환급 및 출생 후 보험료/약관 재정산 확인.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_claim</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출산·신생아 보험금 청구 (수술·입원 특약 신청)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제왕절개 수술비, 신생아 입원/인큐베이터/치료비 등 특약 보험금 청구. 병원에서 발급받은 진단서(질병코드 기재), 입퇴원확인서, 진료비 영수증, 세부내역서 구비 후 각 보험사 모바일 앱으로 간편 접수.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동차 보험 자녀 특약 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자녀 등록(등본 제출) 시 자동차 보험료 3~15% 할인 및 환급 신청.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>건강보험 피부양자 등록 확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아기 피부양자 등록 여부 체크 (국민건강보험공단 1577-1000 전화 확인).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>어린이집 입소 대기 등록</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아기 주민번호 발급 즉시 '아이사랑' 앱에서 희망 어린이집 3곳에 대기 등록.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>영유아 건강검진(1차) &amp; 소아과 예약</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>생후 14~35일 사이 영유아검진 1차 및 BCG 접종 일정 사전 예약('똑닥' 앱 등 활용).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신생아 건강 모니터링 (황달·배꼽)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>황달 수치 수시 확인(10 이하 유지), 배꼽 탈락 및 소독 상태 간호사 확인.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_14</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>배꼽 탈락 및 소독 상태 확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조리원 간호사에게 배꼽 탈락 일자 및 소독 상태 최종 확인.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산모 개인 위생 관리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>양말 착용 및 수유 전 손 소독 철저, 젖몸살 관리.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_16</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조리원 퇴소 시간 확정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조리원 퇴소 오전 시간을 최종 확정하고 퇴소 동선 점검.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_17</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>차량 실내 세차 및 청결 점검</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>차량 실내 청결 상태 확인 및 아기 탑승 전 내부 청소.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_18</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>바구니 카시트 설치/안전 상태 재점검</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>차량 실내 바구니 카시트 장착 및 안전벨트 체결 상태 재점검.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_19</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아기 침대 및 잠자리 세팅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아기 침대 패드/이불 세팅, 흑백모빌 교체, 아기 잠자리 최종 정돈.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기저귀 갈이대 소모품 보충</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기저귀, 물티슈, 손소독제, 온습도계 보충 및 배치.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_21</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>홈캠 설치 및 작동 테스트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>홈캠 Wi-Fi 연동, 카메라 각도 및 스마트폰 모니터링 테스트.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_22</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수유 용품 세척 및 열탕/UV 소독</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>분유포트 식초 소독, 분유제조기 세척, 젖병·젖꼭지·유축기 깔때기 열탕/UV 소독.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_23</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[퇴소 당일] 분유포트 &amp; 제조기 세팅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>분유포트 물을 미리 끓여 보온 온도로 식혀두고, 분유제조기에 물과 분유 채워두기.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_24</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>젖병 및 젖꼭지 최종 소독</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아기가 집에 오자마자 바로 먹을 수 있도록 젖병 및 젖꼭지 소독 완료.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KTX/다자녀 할인 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 시 코레일/SRT 앱에 다자녀 및 임산부 할인 등록.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_26</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산후도우미 관리사님 사전 연락</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산후도우미 방문 날짜 및 시간 사전 조율, 특이사항 및 준비물 확인.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_27</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>탯줄 소독용 알코올 솜 구비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>퇴소 후 가정에서 사용할 멸균 알코올 솜 및 소독 물품 구비.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_28</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조리원 퇴소 교육 이수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>목욕법, 분유량, 아기 변 상태 확인법 등 필수 신생아 케어 교육 이수.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_29</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>회사 및 공공 기관 출산 혜택 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>회사에 출생증명서/등본 제출, 공무원/교직원 출산축하금(100만/10만) 및 복지포인트 가족점수 신청.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보건소 유축기 대여</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신분증과 가족관계증명서를 지참하여 관할 보건소 방문 후 유축기 무료 대여.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_31</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산모 머리 감겨주기 &amp; 수유 지원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조리원 생활 중 산모 머리 감겨주기, 젖몸살 관리 및 유축 깔때기 세척·수유 수발.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_32</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>집 대청소 및 쌓인 택배 정리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>집안 대청소, 쌓여있는 출산선물·육아용품 택배 박스 개봉 및 분리수거 정리.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_c_33</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[퇴소 당일] 실내 온·습도 미리 세팅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아기가 집에 오기 전 적정 온도 22~24°C, 습도 40~60%로 환경 미리 가동 세팅.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>4. 가정 (집 복귀 및 초기 육아기)</t>
-  </si>
-  <si>
-    <t>바구니 카시트 장착 및 안전 이동</t>
-  </si>
-  <si>
-    <t>조리원 퇴소 시 안전 수칙 준수</t>
-  </si>
-  <si>
-    <t>todo_f_2</t>
-  </si>
-  <si>
-    <t>산후도우미 맞이 및 신생아 루틴 공유</t>
-  </si>
-  <si>
-    <t>수유 텀, 수면 패턴 등 사전 협의</t>
-  </si>
-  <si>
-    <t>todo_f_3</t>
-  </si>
-  <si>
-    <t>생후 4~6주 영유아 건강검진 1차 예약</t>
-  </si>
-  <si>
-    <t>국민건강보험공단 건강iN 문진표 작성 후 소아과 방문</t>
-  </si>
-  <si>
-    <t>todo_b_29</t>
-  </si>
-  <si>
-    <t>todo_b_30</t>
-  </si>
-  <si>
-    <t>todo_h_5</t>
-  </si>
-  <si>
-    <t>todo_f_4</t>
-  </si>
-  <si>
-    <t>todo_f_5</t>
-  </si>
-  <si>
-    <t>todo_f_6</t>
-  </si>
-  <si>
-    <t>지역구분</t>
-  </si>
-  <si>
-    <t>혜택명</t>
-  </si>
-  <si>
-    <t>지원형태(바우처/현금)</t>
-  </si>
-  <si>
-    <t>지원금액 및 내용</t>
-  </si>
-  <si>
-    <t>신청자격</t>
-  </si>
-  <si>
-    <t>신청시기</t>
-  </si>
-  <si>
-    <t>신청처</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아기 탯줄 도장 제작</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>탯줄 탈락 후 기념 탯줄 도장 제작 (선택 사항).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아기 통장 개설 및 수당 계좌 변경</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출생신고 5일 후 가족관계증명서 발급 받아 아기 통장 개설 → '복지로' 앱에서 부모급여·아동수당 수령 계좌를 아기 통장으로 변경.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>금융 바우처 등록</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>은행별 아기 행복 바우처(1~2만 원) 혜택 신청.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>💉 [예방접종] BCG(결핵) 예방접종 실시</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>생후 4주 이내 소아과(경피용 도장주사) 또는 보건소(피내용 불주사 사전예약) 방문 접종.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>💉 [예방접종] B형 간염 2차 예방접종</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>생후 1개월 차 소아과 방문 접종 (1차 영유아 건강검진과 함께 방문 추천).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>접종 후 위생 &amp; 접종열 관리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>접종 당일 목욕/연고 금지, 38°C 이상 접종열 발생 시 챔프 등 해열제(1.5ml) 복용 및 열 관리.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>태열 발생 시 온도 하향 케어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>태열 발생 시 실내 온도 20~22°C로 하향 조정 및 시원한 보습 환경 유지.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>두피 각질 케어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>두피 각질은 베이비 오일로 30분 불린 후 전용 샴푸로 부드럽게 세정.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시기별 발달 놀이 제공</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>초점책, 흑백모빌, 아기체육관 등 시기별 교구 비치 및 발달 놀이 진행.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산모 산후 검진 (4~6주)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오로 상태 및 자궁/수술부위 초음파 회복 상태 확인.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>영유아 건강검진 1차 실시</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>생후 14~35일 사이 지정 소아과 방문하여 성장 발달 및 신체 계측 진행.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산후도우미 관리사님 맞이 및 루틴 공유</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>집안 물품 위치, 원하는 수유/수면 케어 방식 및 신생아 루틴 공유.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>💉 [예방접종] 5종 혼합백신(DTaP·IPV·Hib·PCV) 1차 (생후 2개월)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>디프테리아/파상풍/백일해/소아마비/뇌수막염/폐렴구균 국가 무료 접종 (접종열 대비 해열제 사전 준비).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_14</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>💉 [예방접종] 로타바이러스 1차 접종 (생후 2개월)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>국가 무료 지원 (먹는 약 형태). 로타릭스(2회 완료) vs 로타텍(3회 완료) 중 선택 후 전 차수 동일 백신 유지.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주택 우대금리 / 신생아 대출 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>은행 앱 또는 기금e든든에서 등본 첨부하여 주택담보/전세자금 대출 자녀 우대금리 또는 신생아 특례 대출 신청.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_16</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>육아휴직 급여 신청</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴직 30일 이후 고용24 앱/웹에서 신청 (6+6 부모육아휴직 특례 요건 확인).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo_home_17</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>연말정산 소득공제 세팅 (조리원비 결제 &amp; 세액공제)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조리원비는 소득이 더 낮은 배우자 명의(카드/현금영수증)로 결제하여 의료비 공제 문턱(소득의 3%) 조절, 연말정산 시 출산세액공제(30만 원) 및 인적공제 반영.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출생증명서 발급</t>
   </si>
   <si>
     <t>nat_1</t>
@@ -2090,145 +3207,763 @@
     <t>바우처</t>
   </si>
   <si>
-    <t>첫째아 200만 원, 둘째아 이상 300만 원 국민행복카드 바우처 포인트 지급</t>
+    <t>첫째아 200만 원, 둘째아 이상 300만 원 국민행복카드 바우처 포인트 지급. 육아용품, 마트, 병원 등 사용 가능 (단, 산후조리원비 결제 시 연말정산 의료비 세액공제 대상 제외 주의).</t>
   </si>
   <si>
     <t>대한민국 모든 출생아 (출생 후 1년 이내 신청)</t>
   </si>
   <si>
+    <t>출산 후 (출생일 기준 1년 이내)</t>
+  </si>
+  <si>
+    <t>관할 행정복지센터 / 복지로 / 정부24</t>
+  </si>
+  <si>
+    <t>nat_2</t>
+  </si>
+  <si>
+    <t>부모급여 (만 0세 100만 원 / 만 1세 50만 원)</t>
+  </si>
+  <si>
+    <t>현금 지원</t>
+  </si>
+  <si>
+    <t>만 0세(0~11개월) 월 100만 원, 만 1세(12~23개월) 월 50만 원 매월 25일 현금 지급. 어린이집 이용 시 보육료 바우처 차감 후 차액 지급 (아기 명의 통장 지정 수령 시 국세청 비과세 증여 자산 형성 유용).</t>
+  </si>
+  <si>
+    <t>만 0~1세 영아 양육 부모 (소득 무관 전 가구)</t>
+  </si>
+  <si>
+    <t>출생 후 60일 이내 신청 (소급 적용)</t>
+  </si>
+  <si>
+    <t>행정복지센터 / 복지로 / 정부24</t>
+  </si>
+  <si>
+    <t>nat_3</t>
+  </si>
+  <si>
+    <t>아동수당 (월 10만 원)</t>
+  </si>
+  <si>
+    <t>만 8세 미만(0~95개월) 모든 아동 매월 10만 원 현금 지급. 부모급여와 전액 중복 수령 가능하며, 아이 명의 계좌로 직접 수령 시 비과세 자산 형성 가능.</t>
+  </si>
+  <si>
+    <t>만 8세 미만 모든 아동 (소득 무관)</t>
+  </si>
+  <si>
+    <t>출생 후 60일 이내 신청 권장</t>
+  </si>
+  <si>
+    <t>nat_4</t>
+  </si>
+  <si>
+    <t>출생신고 및 건강보험 피보험자 등록</t>
+  </si>
+  <si>
+    <t>행정 수속</t>
+  </si>
+  <si>
+    <t>출생 후 법적 신분 등록 및 건강보험 피보험자/피부양자 자동 연동. (미신고 시 과태료 발생, 출생 30일 이내 필수).</t>
+  </si>
+  <si>
+    <t>모든 출생아 가구</t>
+  </si>
+  <si>
+    <t>출생 후 30일 이내</t>
+  </si>
+  <si>
+    <t>관할 행정복지센터 / 대법원 전자가족관계등록</t>
+  </si>
+  <si>
+    <t>nat_5</t>
+  </si>
+  <si>
+    <t>서류 수속</t>
+  </si>
+  <si>
+    <t>출생신고, 태아보험 청구 및 회사 제출용 출생증명서 원본 2~3부 수령 (병원 퇴원 시 발급, 스마트폰 사진/PDF 보관 필수).</t>
+  </si>
+  <si>
+    <t>모든 출산 산모 가구</t>
+  </si>
+  <si>
+    <t>출생 즉시 (병원 퇴원 전)</t>
+  </si>
+  <si>
+    <t>분만 산부인과 병원 원무과</t>
+  </si>
+  <si>
+    <t>nat_6</t>
+  </si>
+  <si>
+    <t>전기요금 출산가구 30% 감면</t>
+  </si>
+  <si>
+    <t>요금 감면</t>
+  </si>
+  <si>
+    <t>출생일로부터 3년 미만(36개월 이하) 영아 거주 가구 월 전기요금 30% 감면 (월 최대 16,000원 한도, 36개월간 적용). 주거지 이전(이사) 시 한전에 재신청 필수.</t>
+  </si>
+  <si>
+    <t>출생일 3년 미만 영아 주민등록상 가구</t>
+  </si>
+  <si>
+    <t>출생 직후 신청 (신청월부터 적용, 소급 불가)</t>
+  </si>
+  <si>
+    <t>한국전력(123) / 한전ON / 행정복지센터 / 관리사무소</t>
+  </si>
+  <si>
+    <t>nat_7</t>
+  </si>
+  <si>
+    <t>어린이집 입소 대기 신청</t>
+  </si>
+  <si>
+    <t>보육 수속</t>
+  </si>
+  <si>
+    <t>출생 직후 임신육아종합포털 아이사랑에서 원하는 어린이집 최대 3곳에 입소 대기 등록.</t>
+  </si>
+  <si>
+    <t>모든 영유아 가구</t>
+  </si>
+  <si>
+    <t>출생신고(주민번호 발급) 직후 즉시</t>
+  </si>
+  <si>
+    <t>임신육아종합포털 아이사랑 (앱/웹)</t>
+  </si>
+  <si>
+    <t>nat_8</t>
+  </si>
+  <si>
+    <t>맘편한 KTX &amp; SRT 임산부·다자녀 기차요금 할인</t>
+  </si>
+  <si>
+    <t>교통 할인</t>
+  </si>
+  <si>
+    <t>맘편한 KTX(특실/우등실을 일반실 가격으로 이용, 일반실 40% 할인), SRT 맘편한 30% 할인 적용 (임산부 및 동행 보호자 1인 포함 총 2인 혜택).</t>
+  </si>
+  <si>
+    <t>임산부 및 출산 후 일정 기간 산모 (동행 보호자 1인 포함)</t>
+  </si>
+  <si>
+    <t>임신 확인 후 ~ 출산 후 일정 기간</t>
+  </si>
+  <si>
+    <t>코레일 / SRT 웹·앱 / 정부24('맘편한 임신')</t>
+  </si>
+  <si>
+    <t>nat_9</t>
+  </si>
+  <si>
+    <t>신생아 무료 예방접종 (BCG, B형간염 등 국가필수 18종)</t>
+  </si>
+  <si>
+    <t>의료 지원</t>
+  </si>
+  <si>
+    <t>BCG(피내용), B형간염 1~3차 등 국가 필수 예방접종 18종 전액 무료 지원 (지정 의료기관 및 보건소).</t>
+  </si>
+  <si>
+    <t>모든 신생아 및 영유아</t>
+  </si>
+  <si>
+    <t>출생 직후 ~ 만 12세까지</t>
+  </si>
+  <si>
+    <t>분만 병원 / 관할 보건소 / 지정 소아청소년과</t>
+  </si>
+  <si>
+    <t>nat_10</t>
+  </si>
+  <si>
+    <t>영유아 건강검진 (총 8회 무료)</t>
+  </si>
+  <si>
+    <t>의료 검진</t>
+  </si>
+  <si>
+    <t>생후 14일부터 71개월까지 성장·발달 단계별 무료 검진 및 구강검진 (건강iN 문진표 사전 작성 후 방문).</t>
+  </si>
+  <si>
+    <t>생후 14일 ~ 71개월 모든 영유아</t>
+  </si>
+  <si>
+    <t>생후 14일~71개월 (단계별)</t>
+  </si>
+  <si>
+    <t>지정 소아청소년과 병의원</t>
+  </si>
+  <si>
+    <t>nat_11</t>
+  </si>
+  <si>
+    <t>국민행복카드 임신·출산 진료비 바우처 (100만~140만 원)</t>
+  </si>
+  <si>
+    <t>의료 바우처</t>
+  </si>
+  <si>
+    <t>단태아 100만 원, 다태아 태아당 100만 원 바우처 지급 (분만취약지 20만 원 추가). 임신 확인 즉시부터 출생일 기준 2년까지 산모 및 2세 미만 아동 병원비·약제비 사용 가능.</t>
+  </si>
+  <si>
+    <t>대한민국 모든 임산부 (임신확인서 발급자)</t>
+  </si>
+  <si>
+    <t>임신 확인 즉시 ~ 출생일 기준 2년</t>
+  </si>
+  <si>
+    <t>카드사 / 정부24('맘편한 임신') / 관할 보건소</t>
+  </si>
+  <si>
+    <t>nat_12</t>
+  </si>
+  <si>
+    <t>산모·신생아 건강관리 지원 (정부지원 산후도우미 바우처)</t>
+  </si>
+  <si>
+    <t>돌봄 바우처</t>
+  </si>
+  <si>
+    <t>전문 산후관리사가 가정 방문하여 산모 조리, 신생아 케어, 수유 지원 (소득 수준별 차등 정부지원금 지원, 자기부담금만 결제, 3주 이용 권장).</t>
+  </si>
+  <si>
+    <t>모든 출산가구 (소득별 정부지원금 차등 지원)</t>
+  </si>
+  <si>
+    <t>출산 예정일 40일 전 ~ 출산 후 60일 이내</t>
+  </si>
+  <si>
+    <t>관할 보건소 방문 또는 복지로 온라인 신청</t>
+  </si>
+  <si>
+    <t>nat_13</t>
+  </si>
+  <si>
+    <t>제왕절개 / 분만 본인부담금 0원 (법정 본인부담금 전액 면제)</t>
+  </si>
+  <si>
+    <t>의료비 면제</t>
+  </si>
+  <si>
+    <t>자연분만 및 제왕절개 수술 시 법정 본인부담 수술·입원비 0원 전액 면제 (단, 1인실 상급병실료, 무통주사 등 일부 선택 비급여 항목 제외).</t>
+  </si>
+  <si>
+    <t>대한민국 모든 출산 산모</t>
+  </si>
+  <si>
+    <t>출산 시 병원 진료비 정산 단계</t>
+  </si>
+  <si>
+    <t>해당 분만 산부인과 병원 (자동 적용)</t>
+  </si>
+  <si>
+    <t>nat_14</t>
+  </si>
+  <si>
+    <t>조산아·저체중아 외래진료비 경감 (본인부담률 5~10%)</t>
+  </si>
+  <si>
+    <t>의료비 감면</t>
+  </si>
+  <si>
+    <t>재태기간 37주 미만 조산아 또는 2.5kg 이하 저체중아 대상 외래진료 시 본인부담률을 5~10% 수준으로 대폭 경감하여 대학병원 등 중증 외래 의료비 부담 완화.</t>
+  </si>
+  <si>
+    <t>37주 미만 조산아 또는 2.5kg 이하 저체중아</t>
+  </si>
+  <si>
+    <t>출생일로부터 5세(45개월/5년)까지</t>
+  </si>
+  <si>
+    <t>국민건강보험공단 등록 후 병원 외래 이용 시</t>
+  </si>
+  <si>
+    <t>nat_15</t>
+  </si>
+  <si>
+    <t>보건소 임산부 무료 지원 (영양제·검사·주차증)</t>
+  </si>
+  <si>
+    <t>보건소 혜택</t>
+  </si>
+  <si>
+    <t>임신 초기~후기 엽산제·철분제 무료 지급, 임산부 배지 및 차량 주차증 발급, 산전 초기 무료 혈액·소변검사 지원.</t>
+  </si>
+  <si>
+    <t>모든 임산부 (주소지 관할 보건소 등록)</t>
+  </si>
+  <si>
+    <t>임신 확인 즉시 ~ 출산 후</t>
+  </si>
+  <si>
+    <t>관할 보건소 방문 또는 정부24 온라인</t>
+  </si>
+  <si>
+    <t>per_1</t>
+  </si>
+  <si>
+    <t>개인 맞춤</t>
+  </si>
+  <si>
+    <t>공무원연금공단 출산축하금 (100만 원)</t>
+  </si>
+  <si>
+    <t>공무원 혜택</t>
+  </si>
+  <si>
+    <t>공무원 맞춤형 복지 / 공무원연금공단 출산축하금 첫째 100만 원 지급 및 수술비/누적 병원 진료비 신청 (출생증명서 첨부).</t>
+  </si>
+  <si>
+    <t>공무원 가구</t>
+  </si>
+  <si>
     <t>출산 후</t>
   </si>
   <si>
-    <t>행정복지센터 / 복지로</t>
-  </si>
-  <si>
-    <t>nat_2</t>
-  </si>
-  <si>
-    <t>부모급여 (만 0세 100만 원 / 만 1세 50만 원)</t>
-  </si>
-  <si>
-    <t>현금 지원</t>
-  </si>
-  <si>
-    <t>만 0세 월 100만 원, 만 1세 월 50만 원 매월 25일 현금 지급</t>
-  </si>
-  <si>
-    <t>만 0~1세 영아 양육 가정</t>
-  </si>
-  <si>
-    <t>출산 후 매월</t>
-  </si>
-  <si>
-    <t>nat_3</t>
-  </si>
-  <si>
-    <t>아동수당 (월 10만 원)</t>
-  </si>
-  <si>
-    <t>만 8세 미만(0~95개월) 모든 아동 매월 10만 원 현금 지급</t>
-  </si>
-  <si>
-    <t>만 8세 미만 모든 아동</t>
-  </si>
-  <si>
-    <t>60일 이내 신청</t>
-  </si>
-  <si>
-    <t>nat_4</t>
-  </si>
-  <si>
-    <t>출산가구 전기요금 30% 감면</t>
-  </si>
-  <si>
-    <t>요금 감면</t>
-  </si>
-  <si>
-    <t>출생일로부터 3년 미만 영아 거주 가구 매월 전기요금 30% 감면 (월 최대 1.6만원)</t>
-  </si>
-  <si>
-    <t>만 3세 미만 영아 주민등록상 가구</t>
-  </si>
-  <si>
-    <t>출생신고 후 즉시</t>
-  </si>
-  <si>
-    <t>한전(123) / 한전ON / 주민센터</t>
-  </si>
-  <si>
-    <t>nat_5</t>
-  </si>
-  <si>
-    <t>산모·신생아 건강관리 지원 (산후도우미 바우처)</t>
-  </si>
-  <si>
-    <t>전문 산후관리사 가정 방문 건강관리 서비스 정부 지원 바우처</t>
-  </si>
-  <si>
-    <t>기준중위소득 150% 이하 가구 (지자체별 예외지원 확대)</t>
-  </si>
-  <si>
-    <t>출산 예정 40일 전~출산 후 30일</t>
-  </si>
-  <si>
-    <t>주소지 보건소 / 복지로</t>
-  </si>
-  <si>
-    <t>nat_6</t>
-  </si>
-  <si>
-    <t>신생아 취득세 감면</t>
-  </si>
-  <si>
-    <t>세제 감면</t>
-  </si>
-  <si>
-    <t>신생아 출산일 기준 전후 1년 이내 취득한 주택 취득세 500만원 한도 100% 감면</t>
-  </si>
-  <si>
-    <t>출산 무주택 또는 1주택 가구 (12억원 이하 주택)</t>
-  </si>
-  <si>
-    <t>취득 후 출산 시 소급</t>
+    <t>공무원연금공단 홈페이지 / 소속 기관 복지팀</t>
+  </si>
+  <si>
+    <t>per_2</t>
+  </si>
+  <si>
+    <t>교직원공제회 출산축하금 (10만 원 + 축하선물)</t>
+  </si>
+  <si>
+    <t>교직원 혜택</t>
+  </si>
+  <si>
+    <t>한국교직원공제회 회원 출산축하금 10만 원 및 신생아 축하용품 선물 지급.</t>
+  </si>
+  <si>
+    <t>교직원 가구 (한국교직원공제회 회원)</t>
+  </si>
+  <si>
+    <t>교직원공제회 홈페이지</t>
+  </si>
+  <si>
+    <t>per_3</t>
+  </si>
+  <si>
+    <t>맞춤형 복지포털 복지포인트 (검진 10만 + 가족점수)</t>
+  </si>
+  <si>
+    <t>복지포인트</t>
+  </si>
+  <si>
+    <t>태아·산모 검진 복지포인트 10만 원(출산 전) + 출산 가족점수 복지포인트 10만 원x2(배우자·자녀, 출산 후) 추가 배정.</t>
+  </si>
+  <si>
+    <t>공무원 및 교직원 (맞춤형 복지 적용 대상자)</t>
+  </si>
+  <si>
+    <t>출산 전(검진) 및 출산 후</t>
+  </si>
+  <si>
+    <t>맞춤형 복지포털 시스템</t>
+  </si>
+  <si>
+    <t>per_4</t>
+  </si>
+  <si>
+    <t>공무원/직장 가족수당 신청 (월 3만~11만 원)</t>
+  </si>
+  <si>
+    <t>가족수당</t>
+  </si>
+  <si>
+    <t>매월 가족수당 급여 지급 (첫째 자녀 월 3만 원, 둘째 월 7만 원, 셋째 이상 월 11만 원).</t>
+  </si>
+  <si>
+    <t>공무원, 교직원 및 해당 직장인</t>
+  </si>
+  <si>
+    <t>출산 후 급여 반영</t>
+  </si>
+  <si>
+    <t>소속 학교/기관 행정실 또는 회사 인사팀</t>
+  </si>
+  <si>
+    <t>per_5</t>
+  </si>
+  <si>
+    <t>출산전후휴가 (90일) &amp; 배우자 출산휴가 (20일 유급)</t>
+  </si>
+  <si>
+    <t>휴가 혜택</t>
+  </si>
+  <si>
+    <t>산모 출산전후휴가 90일(다태아 120일, 최초 60일 회사 유급 보장). 배우자(남편) 출산휴가 20일 전체 유급 보장 (출산 후 120일 이내 3회 분할 사용 가능).</t>
+  </si>
+  <si>
+    <t>근로자 산모 및 배우자 (고용보험 피보험자)</t>
+  </si>
+  <si>
+    <t>출산 전후 ~ 출산 후 120일 이내</t>
+  </si>
+  <si>
+    <t>소속 회사 신청 및 고용24 (급여 신청)</t>
+  </si>
+  <si>
+    <t>per_6</t>
+  </si>
+  <si>
+    <t>태아보험 수급 및 계약 조정 (입원·수술비 청구)</t>
+  </si>
+  <si>
+    <t>보험 혜택</t>
+  </si>
+  <si>
+    <t>제왕절개 수술비, 신생아 입원 일당 청구 + 출생 후 피보험자 명의 변경 및 남아/여아 선납료 환급 정산.</t>
+  </si>
+  <si>
+    <t>태아보험 가입자</t>
+  </si>
+  <si>
+    <t>수술/출생 후</t>
+  </si>
+  <si>
+    <t>가입 보험사 (모바일 앱 / 콜센터)</t>
+  </si>
+  <si>
+    <t>per_7</t>
+  </si>
+  <si>
+    <t>자동차보험 태아/자녀 할인 환급 (5~20% 할인)</t>
+  </si>
+  <si>
+    <t>보험 환급</t>
+  </si>
+  <si>
+    <t>임신 확인서 또는 등본 제출 시 자동차 보험료 5~20% 할인/환급. 출산 후 특약 해지 및 미신청분 소급 환급 신청 가능.</t>
+  </si>
+  <si>
+    <t>임산부 또는 만 6세 이하 자녀가 있는 피보험자</t>
+  </si>
+  <si>
+    <t>임신 확인 즉시 또는 출산 후 (소급 가능)</t>
+  </si>
+  <si>
+    <t>가입 자동차보험사 (고객센터 / 앱)</t>
+  </si>
+  <si>
+    <t>per_8</t>
+  </si>
+  <si>
+    <t>공무원 단체보험 / 실손보험 병원 진료비 신청</t>
+  </si>
+  <si>
+    <t>보험 청구</t>
+  </si>
+  <si>
+    <t>임신·출산 관련 입원비, 수술비, 누적 병원 진료비 실손보험 및 단체보험 보장 특약 청구.</t>
+  </si>
+  <si>
+    <t>공무원 단체보험 / 개인 실손 가입자</t>
+  </si>
+  <si>
+    <t>수술/출산 후</t>
+  </si>
+  <si>
+    <t>공무원연금공단 / 가입 보험사</t>
+  </si>
+  <si>
+    <t>per_9</t>
+  </si>
+  <si>
+    <t>연말정산 - 출산·입양 세액공제 (30만~70만 원)</t>
+  </si>
+  <si>
+    <t>세액공제</t>
+  </si>
+  <si>
+    <t>해당 연도 출생아 첫째 30만 원, 둘째 50만 원, 셋째 이상 70만 원 세액공제 반영.</t>
+  </si>
+  <si>
+    <t>근로소득자 및 종합소득자 부부</t>
+  </si>
+  <si>
+    <t>연말정산 시기</t>
+  </si>
+  <si>
+    <t>국세청 홈택스 (연말정산 간소화)</t>
+  </si>
+  <si>
+    <t>per_10</t>
+  </si>
+  <si>
+    <t>연말정산 - 산후조리원비 의료비 세액공제 (최대 200만 원)</t>
+  </si>
+  <si>
+    <t>의료비 공제</t>
+  </si>
+  <si>
+    <t>출산 1회당 산후조리원 결제금액 200만 원 한도 의료비 세액공제. (총급여 3% 문턱을 넘기기 위해 소득이 낮은 배우자 명의 카드/현금영수증 결제 유용 / 첫만남이용권 바우처 결제분은 제외 주의).</t>
+  </si>
+  <si>
+    <t>근로소득자 부부 (총급여 7,000만 원 이하 기준 등)</t>
+  </si>
+  <si>
+    <t>연말정산 시기 (결제 명의 사전 관리)</t>
+  </si>
+  <si>
+    <t>국세청 홈택스 / 조리원 영수증</t>
+  </si>
+  <si>
+    <t>per_11</t>
+  </si>
+  <si>
+    <t>연말정산 - 신생아 기본 인적공제 (부양가족 150만 원)</t>
+  </si>
+  <si>
+    <t>인적공제</t>
+  </si>
+  <si>
+    <t>출생아를 부양가족 기본공제 대상자로 등록하여 소득공제 1인당 150만 원 공제 반영.</t>
+  </si>
+  <si>
+    <t>근로소득자 부부</t>
+  </si>
+  <si>
+    <t>국세청 홈택스</t>
+  </si>
+  <si>
+    <t>per_12</t>
+  </si>
+  <si>
+    <t>임신기 근로시간 단축 &amp; 유급 태아검진 시간</t>
+  </si>
+  <si>
+    <t>근로 단축</t>
+  </si>
+  <si>
+    <t>임금 삭감 없이 하루 2시간 단축 근무(출퇴근 조정). 임신 주수별 유급 태아검진 시간 법적 보장.</t>
+  </si>
+  <si>
+    <t>임신 중 여성 근로자 (12주 이내, 32주 이후)</t>
+  </si>
+  <si>
+    <t>단축 개시 3일 전까지 회사 신청</t>
+  </si>
+  <si>
+    <t>의사 진단서 첨부하여 회사(사업주) 제출</t>
+  </si>
+  <si>
+    <t>per_13</t>
+  </si>
+  <si>
+    <t>육아휴직 급여 인상 (월 250만) &amp; 6+6 부모육아휴직 특례</t>
+  </si>
+  <si>
+    <t>육아휴직</t>
+  </si>
+  <si>
+    <t>일반 육아휴직 급여 상한액 월 최대 250만 원 개편. 생후 18개월 이내 부모가 순차/동시 육아휴직 시 첫 6개월간 통상임금 100%(최대 월 450만 원) 지급.</t>
+  </si>
+  <si>
+    <t>만 8세/초2 이하 자녀 부모 (고용보험 피보험 180일 이상)</t>
+  </si>
+  <si>
+    <t>생후 18개월 이내 부모 사용 시 특례</t>
+  </si>
+  <si>
+    <t>소속 회사 신청 및 고용24 (앱/웹)</t>
+  </si>
+  <si>
+    <t>per_14</t>
+  </si>
+  <si>
+    <t>육아기 근로시간 단축 (주 15~35시간 &amp; 단축급여 지원)</t>
+  </si>
+  <si>
+    <t>육아휴직 대신 또는 복직 후 주 15~35시간으로 근로시간 축소, 줄어든 시간에 대해 고용보험 단축 급여 추가 지원 (최대 3년 사용 가능).</t>
+  </si>
+  <si>
+    <t>만 12세/초6 이하 자녀 부모 근로자</t>
+  </si>
+  <si>
+    <t>육아휴직 후 복직 시 또는 대체 사용</t>
+  </si>
+  <si>
+    <t>소속 회사 신청 및 고용24 (단축 급여)</t>
+  </si>
+  <si>
+    <t>per_15</t>
+  </si>
+  <si>
+    <t>우체국 대한민국 엄마보험 (보험료 0원 전액 무료)</t>
+  </si>
+  <si>
+    <t>무료 보험</t>
+  </si>
+  <si>
+    <t>전액 무료(보험료 0원!). 태아 희귀질환(100만 원) 및 산모 임신중독증·고혈압·당뇨 진단금 보장 (임신 22주 이내 신청 필수).</t>
+  </si>
+  <si>
+    <t>17~45세 임산부 (임신 22주 이내)</t>
+  </si>
+  <si>
+    <t>임신 22주 이내 신청 필수</t>
+  </si>
+  <si>
+    <t>우체국 창구 방문 또는 우체국보험 웹</t>
+  </si>
+  <si>
+    <t>per_16</t>
+  </si>
+  <si>
+    <t>신생아 특례 디딤돌 / 버팀목 저금리 대출</t>
+  </si>
+  <si>
+    <t>주택 대출</t>
+  </si>
+  <si>
+    <t>저금리(1~4%대) 주택구입 디딤돌 대출(최대 4억 원) 및 전세자금 버팀목 대출(최대 2.4억 원) 지원 (부부합산 소득 요건 대폭 완화).</t>
+  </si>
+  <si>
+    <t>출산 2년 이내 무주택 세대주</t>
+  </si>
+  <si>
+    <t>대출 접수일 기준 출산 2년 이내</t>
+  </si>
+  <si>
+    <t>주택도시기금(기금e든든) 또는 시중 은행</t>
+  </si>
+  <si>
+    <t>per_17</t>
+  </si>
+  <si>
+    <t>출산가구 주택 취득세 감면 (최대 500만 원 면제)</t>
+  </si>
+  <si>
+    <t>세금 감면</t>
+  </si>
+  <si>
+    <t>출산 전 1년 ~ 출산 후 5년 12억 원 이하 1주택 취득 가구 대상 취득세 최대 500만 원 감면 (이미 낸 세금도 경정청구로 소급 환급 가능).</t>
+  </si>
+  <si>
+    <t>출산 전 1년 ~ 출산 후 5년 12억 이하 1주택 취득 가구</t>
+  </si>
+  <si>
+    <t>주택 취득 시 또는 출산 후 (경정청구 가능)</t>
   </si>
   <si>
     <t>관할 시·군·구청 세무과</t>
   </si>
   <si>
+    <t>per_18</t>
+  </si>
+  <si>
+    <t>혼인·출산 증여세 추가 공제 (부부 합산 최대 3억 비과세)</t>
+  </si>
+  <si>
+    <t>증여세 감면</t>
+  </si>
+  <si>
+    <t>기본 증여 공제 5,000만 원에 출산 추가 공제 1억 원을 합산해 총 1억 5,000만 원까지 증여세 비과세 (신랑·신부 부부 합산 최대 3억 원).</t>
+  </si>
+  <si>
+    <t>출산일 기준 2년 이내 부모로부터 증여받는 가구</t>
+  </si>
+  <si>
+    <t>출산일 기준 2년 이내</t>
+  </si>
+  <si>
+    <t>국세청 홈택스 증여세 신고</t>
+  </si>
+  <si>
+    <t>reg_sj_1</t>
+  </si>
+  <si>
+    <t>세종</t>
+  </si>
+  <si>
+    <t>세종시 출생축하금 (120만 원)</t>
+  </si>
+  <si>
+    <t>세종시 특화</t>
+  </si>
+  <si>
+    <t>세종특별자치시 출생아 1인당 120만 원 지역화폐/현금 지급</t>
+  </si>
+  <si>
+    <t>세종시 거주 출산 가정 (출생 후 6개월 이내 신청)</t>
+  </si>
+  <si>
+    <t>6개월 이내</t>
+  </si>
+  <si>
+    <t>세종시 읍·면·동 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_sj_2</t>
+  </si>
+  <si>
+    <t>세종시 산모·신생아 건강관리사 지원금 &amp; 농산물</t>
+  </si>
+  <si>
+    <t>세종시 지원</t>
+  </si>
+  <si>
+    <t>산후조도우미 본인부담금 추가 지원 및 48만 원 상당 친환경 농산물 꾸러미</t>
+  </si>
+  <si>
+    <t>세종시 거주 산모</t>
+  </si>
+  <si>
+    <t>출산 전 40일 ~ 출산 후 30일</t>
+  </si>
+  <si>
+    <t>세종시 보건소</t>
+  </si>
+  <si>
     <t>reg_seoul_1</t>
   </si>
   <si>
     <t>서울</t>
   </si>
   <si>
-    <t>서울형 산후조리경비 (100만 원 바우처)</t>
-  </si>
-  <si>
-    <t>산모 1인당 100만 원 상당 바우처 (산후도우미 본인부담금 50만원, 한약·마사지 50만원)</t>
-  </si>
-  <si>
-    <t>서울시 6개월 이상 거주 산모</t>
+    <t>서울형 산후조리경비 지원 (100만 원)</t>
+  </si>
+  <si>
+    <t>서울시 특화</t>
+  </si>
+  <si>
+    <t>출생아 1인당 100만 원 바우처 (산후조리원, 의약품, 운동 등 이용 가능)</t>
+  </si>
+  <si>
+    <t>서울시 90일 이상 거주 출산 가정</t>
   </si>
   <si>
     <t>출산 후 60일 이내</t>
   </si>
   <si>
-    <t>서울맘케어 웹사이트</t>
+    <t>서울엄마아빠택시 / 몽땅정보만능키</t>
   </si>
   <si>
     <t>reg_seoul_2</t>
   </si>
   <si>
-    <t>서울시 임산부 교통비 지원 (70만 원)</t>
-  </si>
-  <si>
-    <t>임산부 1인당 70만 원 교통비 포인트 (지하철, 버스, 택시, 자가용 유류비)</t>
-  </si>
-  <si>
-    <t>임신 3개월(12주)~출산 후 3개월</t>
-  </si>
-  <si>
-    <t>임신 중 신청 권장</t>
+    <t>서울 엄마아빠 택시 &amp; 임산부 교통비 (70만 원)</t>
+  </si>
+  <si>
+    <t>교통 지원</t>
+  </si>
+  <si>
+    <t>영아 1인당 10만 원 택시 포인트 + 임산부 교통비 70만 원 지원</t>
+  </si>
+  <si>
+    <t>서울시 거주 임산부 및 영아 가구</t>
+  </si>
+  <si>
+    <t>임신 중 ~ 출산 후</t>
+  </si>
+  <si>
+    <t>정부24 / 몽땅정보만능키</t>
   </si>
   <si>
     <t>reg_gg_1</t>
@@ -2237,322 +3972,412 @@
     <t>경기</t>
   </si>
   <si>
-    <t>경기도 산후조리비 지원 (50만 원 지역화폐)</t>
-  </si>
-  <si>
-    <t>지역화폐</t>
-  </si>
-  <si>
-    <t>출생아 1인당 50만 원 지역화폐 지급 (조리원 및 지역 가맹점 사용)</t>
-  </si>
-  <si>
-    <t>출생일 및 신청일 현재 경기도 거주 부모</t>
-  </si>
-  <si>
-    <t>출생 후 12개월 이내</t>
-  </si>
-  <si>
-    <t>행정복지센터 / 경기민원24</t>
-  </si>
-  <si>
-    <t>reg_incheon_1</t>
+    <t>경기도 산후조리비 지원 (50만 원)</t>
+  </si>
+  <si>
+    <t>경기도 지원</t>
+  </si>
+  <si>
+    <t>출생아 1인당 50만 원 경기지역화폐 지급</t>
+  </si>
+  <si>
+    <t>경기도 거주 출산 가정</t>
+  </si>
+  <si>
+    <t>경기도 시·군 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_gg_2</t>
+  </si>
+  <si>
+    <t>경기도 임산부 친환경 농산물 꾸러미 (48만 원)</t>
+  </si>
+  <si>
+    <t>농산물 지원</t>
+  </si>
+  <si>
+    <t>연간 48만 원 상당 친환경 농산물 자부담 20% 지원</t>
+  </si>
+  <si>
+    <t>경기도 거주 임산부/산모</t>
+  </si>
+  <si>
+    <t>임신 중 ~ 출산 후 1년</t>
+  </si>
+  <si>
+    <t>임산부 친환경농산물 쇼핑몰</t>
+  </si>
+  <si>
+    <t>reg_ic_1</t>
   </si>
   <si>
     <t>인천</t>
   </si>
   <si>
-    <t>인천 1억 플러스 아이드림 (100만 원 천사지원금)</t>
-  </si>
-  <si>
-    <t>1세부터 7세까지 매년 120만 원 지급 (인천e음 포인트)</t>
-  </si>
-  <si>
-    <t>인천시 거주 부모 및 아동</t>
-  </si>
-  <si>
-    <t>매년 생일 기준</t>
-  </si>
-  <si>
-    <t>정부24 / 행정복지센터</t>
-  </si>
-  <si>
-    <t>reg_busan_1</t>
+    <t>인천 1억 플러스 아이드림 지원</t>
+  </si>
+  <si>
+    <t>인천시 특화</t>
+  </si>
+  <si>
+    <t>천사지원금(1~7세 연 120만 원) 및 아이 꿈 수당 등 인천시 양육 패키지 지원</t>
+  </si>
+  <si>
+    <t>인천시 거주 출산 가정</t>
+  </si>
+  <si>
+    <t>인천시 / 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_ic_2</t>
+  </si>
+  <si>
+    <t>인천시 산후조리비 &amp; 임산부 교통비 지원 (50만 원)</t>
+  </si>
+  <si>
+    <t>인천시 지원</t>
+  </si>
+  <si>
+    <t>산후조리 비용 및 이동 교통비 50만 원 바우처 지급</t>
+  </si>
+  <si>
+    <t>인천시 거주 임산부</t>
+  </si>
+  <si>
+    <t>출산 전후</t>
+  </si>
+  <si>
+    <t>인천시 보건소</t>
+  </si>
+  <si>
+    <t>reg_bs_1</t>
   </si>
   <si>
     <t>부산</t>
   </si>
   <si>
-    <t>부산시 출산축하금 (둘째 이상 100만 원)</t>
-  </si>
-  <si>
-    <t>둘째아 이상 출산 시 100만 원 일시금 지급</t>
-  </si>
-  <si>
-    <t>부산시 거주 부모</t>
+    <t>부산시 출산축하금 (첫째 20만 / 둘째 이상 100만 원)</t>
+  </si>
+  <si>
+    <t>부산시 지원</t>
+  </si>
+  <si>
+    <t>부산광역시 출산축하금 + 구·군별 추가 축하금 지원</t>
+  </si>
+  <si>
+    <t>부산시 거주 출산 가정</t>
   </si>
   <si>
     <t>출생 후 1년 이내</t>
   </si>
   <si>
-    <t>행정복지센터</t>
-  </si>
-  <si>
-    <t>reg_daegu_1</t>
+    <t>부산시 읍·면·동 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_bs_2</t>
+  </si>
+  <si>
+    <t>부산시 산후조리비 지원 (50만 원)</t>
+  </si>
+  <si>
+    <t>부산시 특화</t>
+  </si>
+  <si>
+    <t>동백전 지역화폐 50만 원 상당 산후조리비 지원</t>
+  </si>
+  <si>
+    <t>부산시 거주 산모</t>
+  </si>
+  <si>
+    <t>부산시 보건소 / 읍면동</t>
+  </si>
+  <si>
+    <t>reg_dg_1</t>
   </si>
   <si>
     <t>대구</t>
   </si>
   <si>
-    <t>대구시 출산축하금 (첫째 50만, 둘째 100만, 셋째 200만)</t>
-  </si>
-  <si>
-    <t>자녀 순위에 따른 차등 축하금 지급</t>
-  </si>
-  <si>
-    <t>대구시 거주 부모</t>
-  </si>
-  <si>
-    <t>reg_sejong_1</t>
-  </si>
-  <si>
-    <t>세종</t>
-  </si>
-  <si>
-    <t>세종시 출산축하금 (120만 원 여민전)</t>
-  </si>
-  <si>
-    <t>출생아 1인당 120만 원 지역화폐 여민전 포인트 분할 지급</t>
-  </si>
-  <si>
-    <t>세종시 거주 부모</t>
+    <t>대구시 출생축하금 (둘째 100만 / 셋째 이상 200만 원)</t>
+  </si>
+  <si>
+    <t>대구시 지원</t>
+  </si>
+  <si>
+    <t>다자녀 출생아 대상 현금 출생축하금 지원</t>
+  </si>
+  <si>
+    <t>대구시 거주 출산 가정</t>
+  </si>
+  <si>
+    <t>대구시 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_dj_1</t>
+  </si>
+  <si>
+    <t>대전</t>
+  </si>
+  <si>
+    <t>대전 대전맘 출산장려금 (30만~80만 원)</t>
+  </si>
+  <si>
+    <t>대전시 지원</t>
+  </si>
+  <si>
+    <t>대전시 기본 30만 원 + 구별 추가 축하금 (30~50만 원 추가)</t>
+  </si>
+  <si>
+    <t>대전시 거주 출산 가정</t>
+  </si>
+  <si>
+    <t>출생 후 6개월 이내</t>
+  </si>
+  <si>
+    <t>대전시 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_gj_1</t>
+  </si>
+  <si>
+    <t>광주</t>
+  </si>
+  <si>
+    <t>광주형 출생축하금 (100만 원)</t>
+  </si>
+  <si>
+    <t>광주시 지원</t>
+  </si>
+  <si>
+    <t>광주광역시 출생아 1인당 100만 원 현금 지급</t>
+  </si>
+  <si>
+    <t>광주시 거주 출산 가정</t>
   </si>
   <si>
     <t>출생 후 3개월 이내</t>
   </si>
   <si>
-    <t>구분</t>
-  </si>
-  <si>
-    <t>추천품목ID1</t>
-  </si>
-  <si>
-    <t>품목명1</t>
-  </si>
-  <si>
-    <t>추천품목ID2</t>
-  </si>
-  <si>
-    <t>품목명2</t>
-  </si>
-  <si>
-    <t>추천품목ID3</t>
-  </si>
-  <si>
-    <t>품목명3</t>
-  </si>
-  <si>
-    <t>추천품목ID4</t>
-  </si>
-  <si>
-    <t>품목명4</t>
-  </si>
-  <si>
-    <t>추천품목ID5</t>
-  </si>
-  <si>
-    <t>품목명5</t>
-  </si>
-  <si>
-    <t>추천품목ID6</t>
-  </si>
-  <si>
-    <t>품목명6</t>
-  </si>
-  <si>
-    <t>추천품목ID7</t>
-  </si>
-  <si>
-    <t>품목명7</t>
-  </si>
-  <si>
-    <t>추천품목ID8</t>
-  </si>
-  <si>
-    <t>품목명8</t>
-  </si>
-  <si>
-    <t>제왕절개</t>
-  </si>
-  <si>
-    <t>m_cloth_7, m_hyg_7, m_hyg_1, m_cloth_5, g_life_1</t>
-  </si>
-  <si>
-    <t>산후복대, 흉터시트, 맘스안심팬티, 압박스타킹, 꺾인빨대 텀블러</t>
-  </si>
-  <si>
-    <t>자연분만</t>
-  </si>
-  <si>
-    <t>m_hyg_8, m_hyg_3, m_hyg_2</t>
-  </si>
-  <si>
-    <t>회음부방석, 마이비데, 오버나이트 생리대 세트</t>
-  </si>
-  <si>
-    <t>조리원이용</t>
-  </si>
-  <si>
-    <t>m_feed_1, m_feed_2, m_feed_4, m_feed_6, m_feed_7, m_cloth_6, b_care_3, b_care_4</t>
-  </si>
-  <si>
-    <t>수유패드, 저장팩, 유두크림, 유축깔때기, 손목보호대, 아기로션/영양제</t>
-  </si>
-  <si>
-    <t>자택조리</t>
-  </si>
-  <si>
-    <t>m_feed_1, m_feed_4, b_care_3</t>
-  </si>
-  <si>
-    <t>기본 수유패드, 유두보호크림, 아기로션</t>
-  </si>
-  <si>
-    <t>공통산모</t>
-  </si>
-  <si>
-    <t>m_cloth_1, m_cloth_2, m_cloth_3, m_cloth_4, m_cloth_8, m_sk_1, m_sk_2, m_sk_3</t>
-  </si>
-  <si>
-    <t>수유브라, 산모팬티, 무압박양말, 슬리퍼, 세면/화장품 세트</t>
-  </si>
-  <si>
-    <t>공통신생아</t>
-  </si>
-  <si>
-    <t>b_cloth_1, b_cloth_2, b_cloth_3, b_care_1, b_safe_1</t>
-  </si>
-  <si>
-    <t>배냇저고리, 속싸개, 겉싸개, 손수건, 카시트</t>
-  </si>
-  <si>
-    <t>공통보호자</t>
-  </si>
-  <si>
-    <t>g_doc_1, g_doc_2, g_life_4</t>
-  </si>
-  <si>
-    <t>산모수첩/신분증, 결제수단, 충전기/멀티탭</t>
-  </si>
-  <si>
-    <t>기록일시</t>
-  </si>
-  <si>
-    <t>사용자구분</t>
-  </si>
-  <si>
-    <t>이벤트</t>
-  </si>
-  <si>
-    <t>분만법</t>
-  </si>
-  <si>
-    <t>조리원여부</t>
-  </si>
-  <si>
-    <t>아기성별</t>
-  </si>
-  <si>
-    <t>지역</t>
-  </si>
-  <si>
-    <t>출산예정일</t>
-  </si>
-  <si>
-    <t>담은_출산가방수</t>
-  </si>
-  <si>
-    <t>담은_출산가방_품목ID</t>
-  </si>
-  <si>
-    <t>담은_육아용품수</t>
-  </si>
-  <si>
-    <t>담은_육아용품_품목ID</t>
-  </si>
-  <si>
-    <t>💉 [예방접종] 백일해(Tdap) 접종 (임신 27~36주 권장)</t>
-  </si>
-  <si>
-    <t>신생아 백일해 감염 예방을 위해 산모 및 남편, 양육자(조부모) 동시 접종 권장 (생후 2개월 전 항체 전달).</t>
-  </si>
-  <si>
-    <t>💉 [예방접종] 인플루엔자(독감) 접종 (임신 주수 무관)</t>
-  </si>
-  <si>
-    <t>임산부 국가 무료 예방접종 지원 사업 대상 (지정 의료기관 및 보건소에서 무료 접종 가능).</t>
-  </si>
-  <si>
-    <t>todo_b_31</t>
-  </si>
-  <si>
-    <t>태아보험 가입 (11주차 이전 권장)</t>
-  </si>
-  <si>
-    <t>1차 기형아 검사(11~13주) 전 가입 필수(검사 결과 이상 소견 발생 시 가입 거절 또는 승인 보완 요청 가능). 산모 특약 및 신생아 선천이상·저체중·인큐베이터 입원일당 등 필수 특약 비교 선택.</t>
-  </si>
-  <si>
-    <t>💉 [예방접종] 신생아 B형 간염 1차 접종 확인 (출생 직후)</t>
-  </si>
-  <si>
-    <t>출생 후 24시간 이내 분만 병원에서 기본 접종 진행 (아기수첩 접종 기록 확인).</t>
-  </si>
-  <si>
-    <t>todo_h_6</t>
-  </si>
-  <si>
-    <t>퇴원 시 보험 청구용 필수 서류 발급 요청</t>
-  </si>
-  <si>
-    <t>퇴원 전 원무과에 사전 요청: 진단서(질병분류코드 필수), 입퇴원확인서, 진료비 계산서·영수증, 진료비 세부내역서 원본 2부 수령 (보험금 청구 및 회사/연말정산 제출용).</t>
-  </si>
-  <si>
-    <t>💉 [예방접종] BCG(결핵) 접종 예약 및 접종 (생후 4주 이내)</t>
-  </si>
-  <si>
-    <t>피내용(보건소 무료, 주사형) vs 경피용(유료, 도장형) 사전 선택 및 관할 보건소/소아과 사전 예약.</t>
-  </si>
-  <si>
-    <t>태아보험 피보험자 등록 &amp; 성별(남아·여아) 보험료 정산</t>
-  </si>
-  <si>
-    <t>출생신고(등본 발급) 후 아기 주민번호 등록 및 태아→영유아 피보험자 확정. 가입 시 남아 기준 보험료에서 여아 출생 시 기납입 보험료 차액 환급 및 출생 후 보험료/약관 재정산 확인.</t>
-  </si>
-  <si>
-    <t>todo_c_6</t>
-  </si>
-  <si>
-    <t>출산·신생아 보험금 청구 (수술·입원 특약 신청)</t>
-  </si>
-  <si>
-    <t>제왕절개 수술비, 신생아 입원/인큐베이터/치료비 등 특약 보험금 청구. 병원에서 발급받은 진단서(질병코드 기재), 입퇴원확인서, 진료비 영수증, 세부내역서 구비 후 각 보험사 모바일 앱으로 간편 접수.</t>
-  </si>
-  <si>
-    <t>💉 [예방접종] B형 간염 2차 접종 (생후 1개월)</t>
-  </si>
-  <si>
-    <t>생후 1개월 소아과 방문 접종 (생후 4~6주 1차 영유아 건강검진과 함께 방문 추천).</t>
-  </si>
-  <si>
-    <t>💉 [예방접종] 5종 혼합백신(DTaP·IPV·Hib·PCV) 1차 (생후 2개월)</t>
-  </si>
-  <si>
-    <t>디프테리아/파상풍/백일해/소아마비/뇌수막염/폐렴구균 국가 무료 접종 (접종열 대비 해열제 사전 준비).</t>
-  </si>
-  <si>
-    <t>💉 [예방접종] 로타바이러스 1차 접종 (생후 2개월)</t>
-  </si>
-  <si>
-    <t>국가 무료 지원 (먹는 약 형태). 로타릭스(2회 완료) vs 로타텍(3회 완료) 중 선택 후 전 차수 동일 백신 유지.</t>
+    <t>광주시 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_us_1</t>
+  </si>
+  <si>
+    <t>울산</t>
+  </si>
+  <si>
+    <t>울산시 출산축하금 (첫째 50만 / 둘째 100만 / 셋째 200만 원)</t>
+  </si>
+  <si>
+    <t>울산시 지원</t>
+  </si>
+  <si>
+    <t>자녀 순위별 차등 출산축하금 현금 지급</t>
+  </si>
+  <si>
+    <t>울산시 거주 출산 가정</t>
+  </si>
+  <si>
+    <t>울산시 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_cb_1</t>
+  </si>
+  <si>
+    <t>충북</t>
+  </si>
+  <si>
+    <t>충북 출산육아수당 (5년간 총 1,000만 원)</t>
+  </si>
+  <si>
+    <t>충북 특화</t>
+  </si>
+  <si>
+    <t>1세 300만, 2세 200만, 3~5세 각 170만 원 총 1천만 원 분할 지급</t>
+  </si>
+  <si>
+    <t>충청북도 거주 출산 가구</t>
+  </si>
+  <si>
+    <t>출생 후 5년간</t>
+  </si>
+  <si>
+    <t>충북 시·군 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_cn_1</t>
+  </si>
+  <si>
+    <t>충남</t>
+  </si>
+  <si>
+    <t>충남 행복키움수당 (월 10만 원)</t>
+  </si>
+  <si>
+    <t>충남 지원</t>
+  </si>
+  <si>
+    <t>12~36개월 아동 대상 매월 10만 원 현금 추가 지원</t>
+  </si>
+  <si>
+    <t>충청남도 거주 영유아</t>
+  </si>
+  <si>
+    <t>매월 25일</t>
+  </si>
+  <si>
+    <t>충남 시·군 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_jb_1</t>
+  </si>
+  <si>
+    <t>전북</t>
+  </si>
+  <si>
+    <t>전북 출산축하금 (첫째 30~100만 / 셋째 이상 500만 원)</t>
+  </si>
+  <si>
+    <t>전북 지원</t>
+  </si>
+  <si>
+    <t>시·군별 차등 지급되는 대형 출생축하금 지원</t>
+  </si>
+  <si>
+    <t>전북 거주 출산 가정</t>
+  </si>
+  <si>
+    <t>전북 시·군 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_jn_1</t>
+  </si>
+  <si>
+    <t>전남</t>
+  </si>
+  <si>
+    <t>전남 출생기본수당 (1~18세 매월 20만 원)</t>
+  </si>
+  <si>
+    <t>전남 파격지원</t>
+  </si>
+  <si>
+    <t>18세까지 매월 20만 원 총 4,320만 원 장기 육아수당 지급</t>
+  </si>
+  <si>
+    <t>전라남도 거주 아동</t>
+  </si>
+  <si>
+    <t>매월 지급</t>
+  </si>
+  <si>
+    <t>전남 시·군 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_gb_1</t>
+  </si>
+  <si>
+    <t>경북</t>
+  </si>
+  <si>
+    <t>경북 저출생 극복 출산축하금 (100만~500만 원)</t>
+  </si>
+  <si>
+    <t>경북 지원</t>
+  </si>
+  <si>
+    <t>시·군별 첫째 100만 원부터 셋째 이상 500만 원 이상 지원</t>
+  </si>
+  <si>
+    <t>경상북도 거주 출산 가정</t>
+  </si>
+  <si>
+    <t>경북 시·군 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_gn_1</t>
+  </si>
+  <si>
+    <t>경남</t>
+  </si>
+  <si>
+    <t>경남 출산축하금 &amp; 산후조리비 (50만~300만 원)</t>
+  </si>
+  <si>
+    <t>경남 지원</t>
+  </si>
+  <si>
+    <t>시·군별 출산축하금 및 산후조리비 지원금 파격 혜택</t>
+  </si>
+  <si>
+    <t>경상남도 거주 출산 가정</t>
+  </si>
+  <si>
+    <t>경남 시·군 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_gw_1</t>
+  </si>
+  <si>
+    <t>강원</t>
+  </si>
+  <si>
+    <t>강원 육아기본수당 (만 0~5세 월 30만~50만 원)</t>
+  </si>
+  <si>
+    <t>강원 특화</t>
+  </si>
+  <si>
+    <t>정부 부모급여와 연계하여 만 5세까지 매월 육아수당 현금 지급</t>
+  </si>
+  <si>
+    <t>강원특별자치도 거주 가구</t>
+  </si>
+  <si>
+    <t>강원 시·군 행정복지센터</t>
+  </si>
+  <si>
+    <t>reg_jj_1</t>
+  </si>
+  <si>
+    <t>제주</t>
+  </si>
+  <si>
+    <t>제주 출산복지수당 (첫째 50만 / 둘째 이상 200만 원)</t>
+  </si>
+  <si>
+    <t>제주 특화</t>
+  </si>
+  <si>
+    <t>둘째 이상 연 50만 원씩 4년간 총 200만 원 분할 지급</t>
+  </si>
+  <si>
+    <t>제주특별자치도 거주 가정</t>
+  </si>
+  <si>
+    <t>출생 후 4년간</t>
+  </si>
+  <si>
+    <t>제주 읍·면·동 주민센터</t>
+  </si>
+  <si>
+    <t>reg_jj_2</t>
+  </si>
+  <si>
+    <t>제주 임산부 행복택시 지원 (연 12만 원)</t>
+  </si>
+  <si>
+    <t>임산부 병원 진료 및 이동용 행복택시 12만 원 이용권 지원</t>
+  </si>
+  <si>
+    <t>제주 거주 임산부</t>
+  </si>
+  <si>
+    <t>임신 중</t>
+  </si>
+  <si>
+    <t>제주도 보건소</t>
   </si>
 </sst>
 </file>
@@ -5824,7 +7649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2190E7C4-5255-4C66-A5B8-E31D4B2E5FBA}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.125" bestFit="1" customWidth="1"/>
@@ -5853,835 +7678,1889 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>542</v>
+        <v>599</v>
       </c>
       <c r="B2" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C2" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D2" t="s">
-        <v>545</v>
+        <v>602</v>
       </c>
       <c r="E2" t="s">
-        <v>546</v>
+        <v>603</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>547</v>
+        <v>604</v>
       </c>
       <c r="B3" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C3" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D3" t="s">
-        <v>548</v>
+        <v>605</v>
       </c>
       <c r="E3" t="s">
-        <v>549</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>550</v>
+        <v>607</v>
       </c>
       <c r="B4" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C4" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D4" t="s">
-        <v>551</v>
+        <v>608</v>
       </c>
       <c r="E4" t="s">
-        <v>552</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>553</v>
+        <v>610</v>
       </c>
       <c r="B5" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C5" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D5" t="s">
-        <v>554</v>
+        <v>611</v>
       </c>
       <c r="E5" t="s">
-        <v>555</v>
+        <v>612</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>556</v>
+        <v>613</v>
       </c>
       <c r="B6" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C6" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D6" t="s">
-        <v>557</v>
+        <v>614</v>
       </c>
       <c r="E6" t="s">
-        <v>558</v>
+        <v>615</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>559</v>
+        <v>616</v>
       </c>
       <c r="B7" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C7" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D7" t="s">
-        <v>560</v>
+        <v>617</v>
       </c>
       <c r="E7" t="s">
-        <v>561</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>562</v>
+        <v>619</v>
       </c>
       <c r="B8" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C8" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D8" t="s">
-        <v>563</v>
+        <v>620</v>
       </c>
       <c r="E8" t="s">
-        <v>564</v>
+        <v>621</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>565</v>
+        <v>622</v>
       </c>
       <c r="B9" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C9" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D9" t="s">
-        <v>566</v>
+        <v>623</v>
       </c>
       <c r="E9" t="s">
-        <v>567</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>568</v>
+        <v>625</v>
       </c>
       <c r="B10" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C10" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D10" t="s">
-        <v>569</v>
+        <v>626</v>
       </c>
       <c r="E10" t="s">
-        <v>570</v>
+        <v>627</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>571</v>
+        <v>628</v>
       </c>
       <c r="B11" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C11" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D11" t="s">
-        <v>572</v>
+        <v>629</v>
       </c>
       <c r="E11" t="s">
-        <v>573</v>
+        <v>630</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>574</v>
+        <v>631</v>
       </c>
       <c r="B12" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C12" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D12" t="s">
-        <v>575</v>
+        <v>632</v>
       </c>
       <c r="E12" t="s">
-        <v>576</v>
+        <v>633</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>577</v>
+        <v>634</v>
       </c>
       <c r="B13" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C13" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D13" t="s">
-        <v>578</v>
+        <v>635</v>
       </c>
       <c r="E13" t="s">
-        <v>579</v>
+        <v>636</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>580</v>
+        <v>637</v>
       </c>
       <c r="B14" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C14" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D14" t="s">
-        <v>581</v>
+        <v>638</v>
       </c>
       <c r="E14" t="s">
-        <v>582</v>
+        <v>639</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>583</v>
+        <v>640</v>
       </c>
       <c r="B15" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C15" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D15" t="s">
-        <v>584</v>
+        <v>641</v>
       </c>
       <c r="E15" t="s">
-        <v>585</v>
+        <v>642</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>586</v>
+        <v>643</v>
       </c>
       <c r="B16" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C16" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D16" t="s">
-        <v>587</v>
+        <v>644</v>
       </c>
       <c r="E16" t="s">
-        <v>588</v>
+        <v>645</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>589</v>
+        <v>646</v>
       </c>
       <c r="B17" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C17" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D17" t="s">
-        <v>590</v>
+        <v>647</v>
       </c>
       <c r="E17" t="s">
-        <v>591</v>
+        <v>648</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>592</v>
+        <v>649</v>
       </c>
       <c r="B18" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C18" t="s">
-        <v>593</v>
+        <v>650</v>
       </c>
       <c r="D18" t="s">
-        <v>594</v>
+        <v>651</v>
       </c>
       <c r="E18" t="s">
-        <v>595</v>
+        <v>652</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>596</v>
+        <v>653</v>
       </c>
       <c r="B19" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C19" t="s">
-        <v>593</v>
+        <v>650</v>
       </c>
       <c r="D19" t="s">
-        <v>597</v>
+        <v>654</v>
       </c>
       <c r="E19" t="s">
-        <v>598</v>
+        <v>655</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>599</v>
+        <v>656</v>
       </c>
       <c r="B20" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C20" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D20" t="s">
-        <v>600</v>
+        <v>657</v>
       </c>
       <c r="E20" t="s">
-        <v>601</v>
+        <v>658</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>602</v>
+        <v>659</v>
       </c>
       <c r="B21" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C21" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D21" t="s">
-        <v>603</v>
+        <v>660</v>
       </c>
       <c r="E21" t="s">
-        <v>604</v>
+        <v>661</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>605</v>
+        <v>662</v>
       </c>
       <c r="B22" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C22" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D22" t="s">
-        <v>606</v>
+        <v>663</v>
       </c>
       <c r="E22" t="s">
-        <v>607</v>
+        <v>664</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>608</v>
+        <v>665</v>
       </c>
       <c r="B23" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C23" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D23" t="s">
-        <v>609</v>
+        <v>666</v>
       </c>
       <c r="E23" t="s">
-        <v>610</v>
+        <v>667</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>611</v>
+        <v>668</v>
       </c>
       <c r="B24" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C24" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D24" t="s">
-        <v>612</v>
+        <v>669</v>
       </c>
       <c r="E24" t="s">
-        <v>613</v>
+        <v>670</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>614</v>
+        <v>671</v>
       </c>
       <c r="B25" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C25" t="s">
-        <v>615</v>
+        <v>672</v>
       </c>
       <c r="D25" t="s">
-        <v>616</v>
+        <v>673</v>
       </c>
       <c r="E25" t="s">
-        <v>617</v>
+        <v>674</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>618</v>
+        <v>675</v>
       </c>
       <c r="B26" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C26" t="s">
-        <v>593</v>
+        <v>650</v>
       </c>
       <c r="D26" t="s">
-        <v>619</v>
+        <v>676</v>
       </c>
       <c r="E26" t="s">
-        <v>620</v>
+        <v>677</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>621</v>
+        <v>678</v>
       </c>
       <c r="B27" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C27" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D27" t="s">
-        <v>622</v>
+        <v>679</v>
       </c>
       <c r="E27" t="s">
-        <v>623</v>
+        <v>680</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>624</v>
+        <v>681</v>
       </c>
       <c r="B28" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C28" t="s">
-        <v>593</v>
+        <v>650</v>
       </c>
       <c r="D28" t="s">
-        <v>625</v>
+        <v>682</v>
       </c>
       <c r="E28" t="s">
-        <v>626</v>
+        <v>683</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>627</v>
+        <v>684</v>
       </c>
       <c r="B29" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C29" t="s">
-        <v>615</v>
+        <v>672</v>
       </c>
       <c r="D29" t="s">
-        <v>628</v>
+        <v>685</v>
       </c>
       <c r="E29" t="s">
-        <v>629</v>
+        <v>686</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>665</v>
+        <v>687</v>
       </c>
       <c r="B30" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C30" t="s">
-        <v>593</v>
+        <v>650</v>
       </c>
       <c r="D30" t="s">
-        <v>812</v>
+        <v>688</v>
       </c>
       <c r="E30" t="s">
-        <v>813</v>
+        <v>689</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>666</v>
+        <v>690</v>
       </c>
       <c r="B31" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C31" t="s">
-        <v>615</v>
+        <v>672</v>
       </c>
       <c r="D31" t="s">
-        <v>814</v>
+        <v>691</v>
       </c>
       <c r="E31" t="s">
-        <v>815</v>
+        <v>692</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>816</v>
+        <v>693</v>
       </c>
       <c r="B32" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="C32" t="s">
-        <v>593</v>
+        <v>650</v>
       </c>
       <c r="D32" t="s">
-        <v>817</v>
+        <v>694</v>
       </c>
       <c r="E32" t="s">
-        <v>818</v>
+        <v>695</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>630</v>
+        <v>696</v>
       </c>
       <c r="B33" t="s">
-        <v>631</v>
+        <v>600</v>
       </c>
       <c r="C33" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="D33" t="s">
-        <v>632</v>
+        <v>697</v>
       </c>
       <c r="E33" t="s">
-        <v>633</v>
+        <v>698</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>634</v>
+        <v>699</v>
       </c>
       <c r="B34" t="s">
-        <v>631</v>
+        <v>700</v>
       </c>
       <c r="C34" t="s">
-        <v>544</v>
+        <v>650</v>
       </c>
       <c r="D34" t="s">
-        <v>635</v>
+        <v>701</v>
       </c>
       <c r="E34" t="s">
-        <v>636</v>
+        <v>702</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>637</v>
+        <v>703</v>
       </c>
       <c r="B35" t="s">
-        <v>631</v>
+        <v>700</v>
       </c>
       <c r="C35" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="D35" t="s">
-        <v>638</v>
+        <v>704</v>
       </c>
       <c r="E35" t="s">
-        <v>639</v>
+        <v>705</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>640</v>
+        <v>706</v>
       </c>
       <c r="B36" t="s">
-        <v>631</v>
+        <v>700</v>
       </c>
       <c r="C36" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D36" t="s">
-        <v>641</v>
+        <v>707</v>
       </c>
       <c r="E36" t="s">
-        <v>642</v>
+        <v>708</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>667</v>
+        <v>709</v>
       </c>
       <c r="B37" t="s">
-        <v>631</v>
+        <v>700</v>
       </c>
       <c r="C37" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="D37" t="s">
-        <v>819</v>
+        <v>710</v>
       </c>
       <c r="E37" t="s">
-        <v>820</v>
+        <v>711</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>821</v>
+        <v>712</v>
       </c>
       <c r="B38" t="s">
-        <v>631</v>
+        <v>700</v>
       </c>
       <c r="C38" t="s">
-        <v>544</v>
+        <v>672</v>
       </c>
       <c r="D38" t="s">
-        <v>822</v>
+        <v>713</v>
       </c>
       <c r="E38" t="s">
-        <v>823</v>
+        <v>714</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>643</v>
+        <v>715</v>
       </c>
       <c r="B39" t="s">
-        <v>644</v>
+        <v>700</v>
       </c>
       <c r="C39" t="s">
-        <v>544</v>
+        <v>672</v>
       </c>
       <c r="D39" t="s">
-        <v>645</v>
+        <v>716</v>
       </c>
       <c r="E39" t="s">
-        <v>646</v>
+        <v>717</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>647</v>
+        <v>718</v>
       </c>
       <c r="B40" t="s">
-        <v>644</v>
+        <v>700</v>
       </c>
       <c r="C40" t="s">
-        <v>544</v>
+        <v>672</v>
       </c>
       <c r="D40" t="s">
-        <v>648</v>
+        <v>719</v>
       </c>
       <c r="E40" t="s">
-        <v>649</v>
+        <v>720</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>650</v>
+        <v>721</v>
       </c>
       <c r="B41" t="s">
-        <v>644</v>
+        <v>700</v>
       </c>
       <c r="C41" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D41" t="s">
-        <v>651</v>
+        <v>722</v>
       </c>
       <c r="E41" t="s">
-        <v>652</v>
+        <v>723</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>653</v>
+        <v>724</v>
       </c>
       <c r="B42" t="s">
-        <v>644</v>
+        <v>700</v>
       </c>
       <c r="C42" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="D42" t="s">
-        <v>824</v>
+        <v>725</v>
       </c>
       <c r="E42" t="s">
-        <v>825</v>
+        <v>726</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>654</v>
+        <v>727</v>
       </c>
       <c r="B43" t="s">
-        <v>644</v>
+        <v>700</v>
       </c>
       <c r="C43" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="D43" t="s">
-        <v>826</v>
+        <v>728</v>
       </c>
       <c r="E43" t="s">
-        <v>827</v>
+        <v>729</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>828</v>
+        <v>730</v>
       </c>
       <c r="B44" t="s">
-        <v>644</v>
+        <v>700</v>
       </c>
       <c r="C44" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="D44" t="s">
-        <v>829</v>
+        <v>731</v>
       </c>
       <c r="E44" t="s">
-        <v>830</v>
+        <v>732</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>655</v>
+        <v>733</v>
       </c>
       <c r="B45" t="s">
-        <v>656</v>
+        <v>700</v>
       </c>
       <c r="C45" t="s">
-        <v>544</v>
+        <v>672</v>
       </c>
       <c r="D45" t="s">
-        <v>657</v>
+        <v>734</v>
       </c>
       <c r="E45" t="s">
-        <v>658</v>
+        <v>735</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>659</v>
+        <v>736</v>
       </c>
       <c r="B46" t="s">
-        <v>656</v>
+        <v>700</v>
       </c>
       <c r="C46" t="s">
-        <v>593</v>
+        <v>650</v>
       </c>
       <c r="D46" t="s">
-        <v>660</v>
+        <v>737</v>
       </c>
       <c r="E46" t="s">
-        <v>661</v>
+        <v>738</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>662</v>
+        <v>739</v>
       </c>
       <c r="B47" t="s">
-        <v>656</v>
+        <v>700</v>
       </c>
       <c r="C47" t="s">
-        <v>593</v>
+        <v>672</v>
       </c>
       <c r="D47" t="s">
-        <v>663</v>
+        <v>740</v>
       </c>
       <c r="E47" t="s">
-        <v>664</v>
+        <v>741</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>668</v>
+        <v>742</v>
       </c>
       <c r="B48" t="s">
-        <v>656</v>
+        <v>700</v>
       </c>
       <c r="C48" t="s">
-        <v>593</v>
+        <v>672</v>
       </c>
       <c r="D48" t="s">
-        <v>831</v>
+        <v>743</v>
       </c>
       <c r="E48" t="s">
-        <v>832</v>
+        <v>744</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>669</v>
+        <v>745</v>
       </c>
       <c r="B49" t="s">
-        <v>656</v>
+        <v>700</v>
       </c>
       <c r="C49" t="s">
-        <v>593</v>
+        <v>650</v>
       </c>
       <c r="D49" t="s">
-        <v>833</v>
+        <v>746</v>
       </c>
       <c r="E49" t="s">
-        <v>834</v>
+        <v>747</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>670</v>
+        <v>748</v>
       </c>
       <c r="B50" t="s">
-        <v>656</v>
+        <v>700</v>
       </c>
       <c r="C50" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="D50" t="s">
+        <v>749</v>
+      </c>
+      <c r="E50" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>751</v>
+      </c>
+      <c r="B51" t="s">
+        <v>700</v>
+      </c>
+      <c r="C51" t="s">
+        <v>601</v>
+      </c>
+      <c r="D51" t="s">
+        <v>752</v>
+      </c>
+      <c r="E51" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>754</v>
+      </c>
+      <c r="B52" t="s">
+        <v>700</v>
+      </c>
+      <c r="C52" t="s">
+        <v>601</v>
+      </c>
+      <c r="D52" t="s">
+        <v>755</v>
+      </c>
+      <c r="E52" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>757</v>
+      </c>
+      <c r="B53" t="s">
+        <v>700</v>
+      </c>
+      <c r="C53" t="s">
+        <v>601</v>
+      </c>
+      <c r="D53" t="s">
+        <v>758</v>
+      </c>
+      <c r="E53" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>760</v>
+      </c>
+      <c r="B54" t="s">
+        <v>700</v>
+      </c>
+      <c r="C54" t="s">
+        <v>601</v>
+      </c>
+      <c r="D54" t="s">
+        <v>761</v>
+      </c>
+      <c r="E54" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>763</v>
+      </c>
+      <c r="B55" t="s">
+        <v>700</v>
+      </c>
+      <c r="C55" t="s">
+        <v>601</v>
+      </c>
+      <c r="D55" t="s">
+        <v>764</v>
+      </c>
+      <c r="E55" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>766</v>
+      </c>
+      <c r="B56" t="s">
+        <v>700</v>
+      </c>
+      <c r="C56" t="s">
+        <v>601</v>
+      </c>
+      <c r="D56" t="s">
+        <v>767</v>
+      </c>
+      <c r="E56" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>769</v>
+      </c>
+      <c r="B57" t="s">
+        <v>700</v>
+      </c>
+      <c r="C57" t="s">
+        <v>601</v>
+      </c>
+      <c r="D57" t="s">
+        <v>770</v>
+      </c>
+      <c r="E57" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>772</v>
+      </c>
+      <c r="B58" t="s">
+        <v>700</v>
+      </c>
+      <c r="C58" t="s">
+        <v>601</v>
+      </c>
+      <c r="D58" t="s">
+        <v>773</v>
+      </c>
+      <c r="E58" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>775</v>
+      </c>
+      <c r="B59" t="s">
+        <v>700</v>
+      </c>
+      <c r="C59" t="s">
+        <v>650</v>
+      </c>
+      <c r="D59" t="s">
+        <v>776</v>
+      </c>
+      <c r="E59" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>778</v>
+      </c>
+      <c r="B60" t="s">
+        <v>700</v>
+      </c>
+      <c r="C60" t="s">
+        <v>601</v>
+      </c>
+      <c r="D60" t="s">
+        <v>779</v>
+      </c>
+      <c r="E60" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>781</v>
+      </c>
+      <c r="B61" t="s">
+        <v>700</v>
+      </c>
+      <c r="C61" t="s">
+        <v>601</v>
+      </c>
+      <c r="D61" t="s">
+        <v>782</v>
+      </c>
+      <c r="E61" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>784</v>
+      </c>
+      <c r="B62" t="s">
+        <v>785</v>
+      </c>
+      <c r="C62" t="s">
+        <v>601</v>
+      </c>
+      <c r="D62" t="s">
+        <v>786</v>
+      </c>
+      <c r="E62" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>788</v>
+      </c>
+      <c r="B63" t="s">
+        <v>785</v>
+      </c>
+      <c r="C63" t="s">
+        <v>601</v>
+      </c>
+      <c r="D63" t="s">
+        <v>789</v>
+      </c>
+      <c r="E63" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>791</v>
+      </c>
+      <c r="B64" t="s">
+        <v>785</v>
+      </c>
+      <c r="C64" t="s">
+        <v>601</v>
+      </c>
+      <c r="D64" t="s">
+        <v>792</v>
+      </c>
+      <c r="E64" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>794</v>
+      </c>
+      <c r="B65" t="s">
+        <v>785</v>
+      </c>
+      <c r="C65" t="s">
+        <v>601</v>
+      </c>
+      <c r="D65" t="s">
+        <v>795</v>
+      </c>
+      <c r="E65" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>797</v>
+      </c>
+      <c r="B66" t="s">
+        <v>785</v>
+      </c>
+      <c r="C66" t="s">
+        <v>601</v>
+      </c>
+      <c r="D66" t="s">
+        <v>798</v>
+      </c>
+      <c r="E66" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>800</v>
+      </c>
+      <c r="B67" t="s">
+        <v>785</v>
+      </c>
+      <c r="C67" t="s">
+        <v>601</v>
+      </c>
+      <c r="D67" t="s">
+        <v>801</v>
+      </c>
+      <c r="E67" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>803</v>
+      </c>
+      <c r="B68" t="s">
+        <v>785</v>
+      </c>
+      <c r="C68" t="s">
+        <v>601</v>
+      </c>
+      <c r="D68" t="s">
+        <v>804</v>
+      </c>
+      <c r="E68" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>806</v>
+      </c>
+      <c r="B69" t="s">
+        <v>785</v>
+      </c>
+      <c r="C69" t="s">
+        <v>601</v>
+      </c>
+      <c r="D69" t="s">
+        <v>807</v>
+      </c>
+      <c r="E69" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>809</v>
+      </c>
+      <c r="B70" t="s">
+        <v>785</v>
+      </c>
+      <c r="C70" t="s">
+        <v>650</v>
+      </c>
+      <c r="D70" t="s">
+        <v>810</v>
+      </c>
+      <c r="E70" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>812</v>
+      </c>
+      <c r="B71" t="s">
+        <v>785</v>
+      </c>
+      <c r="C71" t="s">
+        <v>601</v>
+      </c>
+      <c r="D71" t="s">
+        <v>813</v>
+      </c>
+      <c r="E71" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>815</v>
+      </c>
+      <c r="B72" t="s">
+        <v>785</v>
+      </c>
+      <c r="C72" t="s">
+        <v>601</v>
+      </c>
+      <c r="D72" t="s">
+        <v>816</v>
+      </c>
+      <c r="E72" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>818</v>
+      </c>
+      <c r="B73" t="s">
+        <v>785</v>
+      </c>
+      <c r="C73" t="s">
+        <v>650</v>
+      </c>
+      <c r="D73" t="s">
+        <v>819</v>
+      </c>
+      <c r="E73" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>821</v>
+      </c>
+      <c r="B74" t="s">
+        <v>785</v>
+      </c>
+      <c r="C74" t="s">
+        <v>650</v>
+      </c>
+      <c r="D74" t="s">
+        <v>822</v>
+      </c>
+      <c r="E74" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>824</v>
+      </c>
+      <c r="B75" t="s">
+        <v>785</v>
+      </c>
+      <c r="C75" t="s">
+        <v>672</v>
+      </c>
+      <c r="D75" t="s">
+        <v>825</v>
+      </c>
+      <c r="E75" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>827</v>
+      </c>
+      <c r="B76" t="s">
+        <v>785</v>
+      </c>
+      <c r="C76" t="s">
+        <v>672</v>
+      </c>
+      <c r="D76" t="s">
+        <v>828</v>
+      </c>
+      <c r="E76" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>830</v>
+      </c>
+      <c r="B77" t="s">
+        <v>785</v>
+      </c>
+      <c r="C77" t="s">
+        <v>672</v>
+      </c>
+      <c r="D77" t="s">
+        <v>831</v>
+      </c>
+      <c r="E77" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>833</v>
+      </c>
+      <c r="B78" t="s">
+        <v>785</v>
+      </c>
+      <c r="C78" t="s">
+        <v>672</v>
+      </c>
+      <c r="D78" t="s">
+        <v>834</v>
+      </c>
+      <c r="E78" t="s">
         <v>835</v>
       </c>
-      <c r="E50" t="s">
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
         <v>836</v>
+      </c>
+      <c r="B79" t="s">
+        <v>785</v>
+      </c>
+      <c r="C79" t="s">
+        <v>601</v>
+      </c>
+      <c r="D79" t="s">
+        <v>837</v>
+      </c>
+      <c r="E79" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>839</v>
+      </c>
+      <c r="B80" t="s">
+        <v>785</v>
+      </c>
+      <c r="C80" t="s">
+        <v>601</v>
+      </c>
+      <c r="D80" t="s">
+        <v>840</v>
+      </c>
+      <c r="E80" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>842</v>
+      </c>
+      <c r="B81" t="s">
+        <v>785</v>
+      </c>
+      <c r="C81" t="s">
+        <v>601</v>
+      </c>
+      <c r="D81" t="s">
+        <v>843</v>
+      </c>
+      <c r="E81" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>845</v>
+      </c>
+      <c r="B82" t="s">
+        <v>785</v>
+      </c>
+      <c r="C82" t="s">
+        <v>601</v>
+      </c>
+      <c r="D82" t="s">
+        <v>846</v>
+      </c>
+      <c r="E82" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>848</v>
+      </c>
+      <c r="B83" t="s">
+        <v>785</v>
+      </c>
+      <c r="C83" t="s">
+        <v>601</v>
+      </c>
+      <c r="D83" t="s">
+        <v>849</v>
+      </c>
+      <c r="E83" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>851</v>
+      </c>
+      <c r="B84" t="s">
+        <v>785</v>
+      </c>
+      <c r="C84" t="s">
+        <v>601</v>
+      </c>
+      <c r="D84" t="s">
+        <v>852</v>
+      </c>
+      <c r="E84" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>854</v>
+      </c>
+      <c r="B85" t="s">
+        <v>785</v>
+      </c>
+      <c r="C85" t="s">
+        <v>601</v>
+      </c>
+      <c r="D85" t="s">
+        <v>855</v>
+      </c>
+      <c r="E85" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>857</v>
+      </c>
+      <c r="B86" t="s">
+        <v>785</v>
+      </c>
+      <c r="C86" t="s">
+        <v>601</v>
+      </c>
+      <c r="D86" t="s">
+        <v>858</v>
+      </c>
+      <c r="E86" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>860</v>
+      </c>
+      <c r="B87" t="s">
+        <v>785</v>
+      </c>
+      <c r="C87" t="s">
+        <v>601</v>
+      </c>
+      <c r="D87" t="s">
+        <v>861</v>
+      </c>
+      <c r="E87" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>863</v>
+      </c>
+      <c r="B88" t="s">
+        <v>785</v>
+      </c>
+      <c r="C88" t="s">
+        <v>650</v>
+      </c>
+      <c r="D88" t="s">
+        <v>864</v>
+      </c>
+      <c r="E88" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>866</v>
+      </c>
+      <c r="B89" t="s">
+        <v>785</v>
+      </c>
+      <c r="C89" t="s">
+        <v>601</v>
+      </c>
+      <c r="D89" t="s">
+        <v>867</v>
+      </c>
+      <c r="E89" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>869</v>
+      </c>
+      <c r="B90" t="s">
+        <v>785</v>
+      </c>
+      <c r="C90" t="s">
+        <v>650</v>
+      </c>
+      <c r="D90" t="s">
+        <v>870</v>
+      </c>
+      <c r="E90" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>872</v>
+      </c>
+      <c r="B91" t="s">
+        <v>785</v>
+      </c>
+      <c r="C91" t="s">
+        <v>650</v>
+      </c>
+      <c r="D91" t="s">
+        <v>873</v>
+      </c>
+      <c r="E91" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>875</v>
+      </c>
+      <c r="B92" t="s">
+        <v>785</v>
+      </c>
+      <c r="C92" t="s">
+        <v>601</v>
+      </c>
+      <c r="D92" t="s">
+        <v>876</v>
+      </c>
+      <c r="E92" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>878</v>
+      </c>
+      <c r="B93" t="s">
+        <v>785</v>
+      </c>
+      <c r="C93" t="s">
+        <v>601</v>
+      </c>
+      <c r="D93" t="s">
+        <v>879</v>
+      </c>
+      <c r="E93" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>881</v>
+      </c>
+      <c r="B94" t="s">
+        <v>785</v>
+      </c>
+      <c r="C94" t="s">
+        <v>601</v>
+      </c>
+      <c r="D94" t="s">
+        <v>882</v>
+      </c>
+      <c r="E94" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>884</v>
+      </c>
+      <c r="B95" t="s">
+        <v>785</v>
+      </c>
+      <c r="C95" t="s">
+        <v>601</v>
+      </c>
+      <c r="D95" t="s">
+        <v>885</v>
+      </c>
+      <c r="E95" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>887</v>
+      </c>
+      <c r="B96" t="s">
+        <v>888</v>
+      </c>
+      <c r="C96" t="s">
+        <v>650</v>
+      </c>
+      <c r="D96" t="s">
+        <v>889</v>
+      </c>
+      <c r="E96" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>891</v>
+      </c>
+      <c r="B97" t="s">
+        <v>888</v>
+      </c>
+      <c r="C97" t="s">
+        <v>650</v>
+      </c>
+      <c r="D97" t="s">
+        <v>892</v>
+      </c>
+      <c r="E97" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>894</v>
+      </c>
+      <c r="B98" t="s">
+        <v>888</v>
+      </c>
+      <c r="C98" t="s">
+        <v>650</v>
+      </c>
+      <c r="D98" t="s">
+        <v>895</v>
+      </c>
+      <c r="E98" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>897</v>
+      </c>
+      <c r="B99" t="s">
+        <v>888</v>
+      </c>
+      <c r="C99" t="s">
+        <v>650</v>
+      </c>
+      <c r="D99" t="s">
+        <v>898</v>
+      </c>
+      <c r="E99" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>900</v>
+      </c>
+      <c r="B100" t="s">
+        <v>888</v>
+      </c>
+      <c r="C100" t="s">
+        <v>650</v>
+      </c>
+      <c r="D100" t="s">
+        <v>901</v>
+      </c>
+      <c r="E100" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>903</v>
+      </c>
+      <c r="B101" t="s">
+        <v>888</v>
+      </c>
+      <c r="C101" t="s">
+        <v>650</v>
+      </c>
+      <c r="D101" t="s">
+        <v>904</v>
+      </c>
+      <c r="E101" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>906</v>
+      </c>
+      <c r="B102" t="s">
+        <v>888</v>
+      </c>
+      <c r="C102" t="s">
+        <v>650</v>
+      </c>
+      <c r="D102" t="s">
+        <v>907</v>
+      </c>
+      <c r="E102" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>909</v>
+      </c>
+      <c r="B103" t="s">
+        <v>888</v>
+      </c>
+      <c r="C103" t="s">
+        <v>650</v>
+      </c>
+      <c r="D103" t="s">
+        <v>910</v>
+      </c>
+      <c r="E103" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>912</v>
+      </c>
+      <c r="B104" t="s">
+        <v>888</v>
+      </c>
+      <c r="C104" t="s">
+        <v>650</v>
+      </c>
+      <c r="D104" t="s">
+        <v>913</v>
+      </c>
+      <c r="E104" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>915</v>
+      </c>
+      <c r="B105" t="s">
+        <v>888</v>
+      </c>
+      <c r="C105" t="s">
+        <v>650</v>
+      </c>
+      <c r="D105" t="s">
+        <v>916</v>
+      </c>
+      <c r="E105" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>918</v>
+      </c>
+      <c r="B106" t="s">
+        <v>888</v>
+      </c>
+      <c r="C106" t="s">
+        <v>650</v>
+      </c>
+      <c r="D106" t="s">
+        <v>919</v>
+      </c>
+      <c r="E106" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>921</v>
+      </c>
+      <c r="B107" t="s">
+        <v>888</v>
+      </c>
+      <c r="C107" t="s">
+        <v>650</v>
+      </c>
+      <c r="D107" t="s">
+        <v>922</v>
+      </c>
+      <c r="E107" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>924</v>
+      </c>
+      <c r="B108" t="s">
+        <v>888</v>
+      </c>
+      <c r="C108" t="s">
+        <v>650</v>
+      </c>
+      <c r="D108" t="s">
+        <v>925</v>
+      </c>
+      <c r="E108" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>927</v>
+      </c>
+      <c r="B109" t="s">
+        <v>888</v>
+      </c>
+      <c r="C109" t="s">
+        <v>650</v>
+      </c>
+      <c r="D109" t="s">
+        <v>928</v>
+      </c>
+      <c r="E109" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>930</v>
+      </c>
+      <c r="B110" t="s">
+        <v>888</v>
+      </c>
+      <c r="C110" t="s">
+        <v>650</v>
+      </c>
+      <c r="D110" t="s">
+        <v>931</v>
+      </c>
+      <c r="E110" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>933</v>
+      </c>
+      <c r="B111" t="s">
+        <v>888</v>
+      </c>
+      <c r="C111" t="s">
+        <v>650</v>
+      </c>
+      <c r="D111" t="s">
+        <v>934</v>
+      </c>
+      <c r="E111" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>936</v>
+      </c>
+      <c r="B112" t="s">
+        <v>888</v>
+      </c>
+      <c r="C112" t="s">
+        <v>650</v>
+      </c>
+      <c r="D112" t="s">
+        <v>937</v>
+      </c>
+      <c r="E112" t="s">
+        <v>938</v>
       </c>
     </row>
   </sheetData>
@@ -6693,7 +9572,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B16A584-0321-47E4-921F-2D47868734B3}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -6711,363 +9590,1481 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>671</v>
+        <v>542</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>672</v>
+        <v>543</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>673</v>
+        <v>544</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>674</v>
+        <v>545</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>675</v>
+        <v>546</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>676</v>
+        <v>547</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>677</v>
+        <v>548</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>678</v>
+        <v>940</v>
       </c>
       <c r="B2" t="s">
-        <v>679</v>
+        <v>941</v>
       </c>
       <c r="C2" t="s">
-        <v>680</v>
+        <v>942</v>
       </c>
       <c r="D2" t="s">
-        <v>681</v>
+        <v>943</v>
       </c>
       <c r="E2" t="s">
-        <v>682</v>
+        <v>944</v>
       </c>
       <c r="F2" t="s">
-        <v>683</v>
+        <v>945</v>
       </c>
       <c r="G2" t="s">
-        <v>684</v>
+        <v>946</v>
       </c>
       <c r="H2" t="s">
-        <v>685</v>
+        <v>947</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>686</v>
+        <v>948</v>
       </c>
       <c r="B3" t="s">
-        <v>679</v>
+        <v>941</v>
       </c>
       <c r="C3" t="s">
-        <v>687</v>
+        <v>949</v>
       </c>
       <c r="D3" t="s">
-        <v>688</v>
+        <v>950</v>
       </c>
       <c r="E3" t="s">
-        <v>689</v>
+        <v>951</v>
       </c>
       <c r="F3" t="s">
-        <v>690</v>
+        <v>952</v>
       </c>
       <c r="G3" t="s">
-        <v>691</v>
+        <v>953</v>
       </c>
       <c r="H3" t="s">
-        <v>685</v>
+        <v>954</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>692</v>
+        <v>955</v>
       </c>
       <c r="B4" t="s">
-        <v>679</v>
+        <v>941</v>
       </c>
       <c r="C4" t="s">
-        <v>693</v>
+        <v>956</v>
       </c>
       <c r="D4" t="s">
-        <v>688</v>
+        <v>950</v>
       </c>
       <c r="E4" t="s">
-        <v>694</v>
+        <v>957</v>
       </c>
       <c r="F4" t="s">
-        <v>695</v>
+        <v>958</v>
       </c>
       <c r="G4" t="s">
-        <v>696</v>
+        <v>959</v>
       </c>
       <c r="H4" t="s">
-        <v>685</v>
+        <v>954</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>697</v>
+        <v>960</v>
       </c>
       <c r="B5" t="s">
-        <v>679</v>
+        <v>941</v>
       </c>
       <c r="C5" t="s">
-        <v>698</v>
+        <v>961</v>
       </c>
       <c r="D5" t="s">
-        <v>699</v>
+        <v>962</v>
       </c>
       <c r="E5" t="s">
-        <v>700</v>
+        <v>963</v>
       </c>
       <c r="F5" t="s">
-        <v>701</v>
+        <v>964</v>
       </c>
       <c r="G5" t="s">
-        <v>702</v>
+        <v>965</v>
       </c>
       <c r="H5" t="s">
-        <v>703</v>
+        <v>966</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>704</v>
+        <v>967</v>
       </c>
       <c r="B6" t="s">
-        <v>679</v>
+        <v>941</v>
       </c>
       <c r="C6" t="s">
-        <v>705</v>
+        <v>939</v>
       </c>
       <c r="D6" t="s">
-        <v>681</v>
+        <v>968</v>
       </c>
       <c r="E6" t="s">
-        <v>706</v>
+        <v>969</v>
       </c>
       <c r="F6" t="s">
-        <v>707</v>
+        <v>970</v>
       </c>
       <c r="G6" t="s">
-        <v>708</v>
+        <v>971</v>
       </c>
       <c r="H6" t="s">
-        <v>709</v>
+        <v>972</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>710</v>
+        <v>973</v>
       </c>
       <c r="B7" t="s">
-        <v>679</v>
+        <v>941</v>
       </c>
       <c r="C7" t="s">
-        <v>711</v>
+        <v>974</v>
       </c>
       <c r="D7" t="s">
-        <v>712</v>
+        <v>975</v>
       </c>
       <c r="E7" t="s">
-        <v>713</v>
+        <v>976</v>
       </c>
       <c r="F7" t="s">
-        <v>714</v>
+        <v>977</v>
       </c>
       <c r="G7" t="s">
-        <v>715</v>
+        <v>978</v>
       </c>
       <c r="H7" t="s">
-        <v>716</v>
+        <v>979</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>717</v>
+        <v>980</v>
       </c>
       <c r="B8" t="s">
-        <v>718</v>
+        <v>941</v>
       </c>
       <c r="C8" t="s">
-        <v>719</v>
+        <v>981</v>
       </c>
       <c r="D8" t="s">
-        <v>681</v>
+        <v>982</v>
       </c>
       <c r="E8" t="s">
-        <v>720</v>
+        <v>983</v>
       </c>
       <c r="F8" t="s">
-        <v>721</v>
+        <v>984</v>
       </c>
       <c r="G8" t="s">
-        <v>722</v>
+        <v>985</v>
       </c>
       <c r="H8" t="s">
-        <v>723</v>
+        <v>986</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>724</v>
+        <v>987</v>
       </c>
       <c r="B9" t="s">
-        <v>718</v>
+        <v>941</v>
       </c>
       <c r="C9" t="s">
-        <v>725</v>
+        <v>988</v>
       </c>
       <c r="D9" t="s">
-        <v>681</v>
+        <v>989</v>
       </c>
       <c r="E9" t="s">
-        <v>726</v>
+        <v>990</v>
       </c>
       <c r="F9" t="s">
-        <v>727</v>
+        <v>991</v>
       </c>
       <c r="G9" t="s">
-        <v>728</v>
+        <v>992</v>
       </c>
       <c r="H9" t="s">
-        <v>723</v>
+        <v>993</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>729</v>
+        <v>994</v>
       </c>
       <c r="B10" t="s">
-        <v>730</v>
+        <v>941</v>
       </c>
       <c r="C10" t="s">
-        <v>731</v>
+        <v>995</v>
       </c>
       <c r="D10" t="s">
-        <v>732</v>
+        <v>996</v>
       </c>
       <c r="E10" t="s">
-        <v>733</v>
+        <v>997</v>
       </c>
       <c r="F10" t="s">
-        <v>734</v>
+        <v>998</v>
       </c>
       <c r="G10" t="s">
-        <v>735</v>
+        <v>999</v>
       </c>
       <c r="H10" t="s">
-        <v>736</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>737</v>
+        <v>1001</v>
       </c>
       <c r="B11" t="s">
-        <v>738</v>
+        <v>941</v>
       </c>
       <c r="C11" t="s">
-        <v>739</v>
+        <v>1002</v>
       </c>
       <c r="D11" t="s">
-        <v>732</v>
+        <v>1003</v>
       </c>
       <c r="E11" t="s">
-        <v>740</v>
+        <v>1004</v>
       </c>
       <c r="F11" t="s">
-        <v>741</v>
+        <v>1005</v>
       </c>
       <c r="G11" t="s">
-        <v>742</v>
+        <v>1006</v>
       </c>
       <c r="H11" t="s">
-        <v>743</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>744</v>
+        <v>1008</v>
       </c>
       <c r="B12" t="s">
-        <v>745</v>
+        <v>941</v>
       </c>
       <c r="C12" t="s">
-        <v>746</v>
+        <v>1009</v>
       </c>
       <c r="D12" t="s">
-        <v>688</v>
+        <v>1010</v>
       </c>
       <c r="E12" t="s">
-        <v>747</v>
+        <v>1011</v>
       </c>
       <c r="F12" t="s">
-        <v>748</v>
+        <v>1012</v>
       </c>
       <c r="G12" t="s">
-        <v>749</v>
+        <v>1013</v>
       </c>
       <c r="H12" t="s">
-        <v>750</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>751</v>
+        <v>1015</v>
       </c>
       <c r="B13" t="s">
-        <v>752</v>
+        <v>941</v>
       </c>
       <c r="C13" t="s">
-        <v>753</v>
+        <v>1016</v>
       </c>
       <c r="D13" t="s">
-        <v>688</v>
+        <v>1017</v>
       </c>
       <c r="E13" t="s">
-        <v>754</v>
+        <v>1018</v>
       </c>
       <c r="F13" t="s">
-        <v>755</v>
+        <v>1019</v>
       </c>
       <c r="G13" t="s">
-        <v>749</v>
+        <v>1020</v>
       </c>
       <c r="H13" t="s">
-        <v>750</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>756</v>
+        <v>1022</v>
       </c>
       <c r="B14" t="s">
-        <v>757</v>
+        <v>941</v>
       </c>
       <c r="C14" t="s">
-        <v>758</v>
+        <v>1023</v>
       </c>
       <c r="D14" t="s">
-        <v>732</v>
+        <v>1024</v>
       </c>
       <c r="E14" t="s">
-        <v>759</v>
+        <v>1025</v>
       </c>
       <c r="F14" t="s">
-        <v>760</v>
+        <v>1026</v>
       </c>
       <c r="G14" t="s">
-        <v>761</v>
+        <v>1027</v>
       </c>
       <c r="H14" t="s">
-        <v>750</v>
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B15" t="s">
+        <v>941</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B16" t="s">
+        <v>941</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H18" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H19" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H20" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H22" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G23" t="s">
+        <v>1090</v>
+      </c>
+      <c r="H23" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G24" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H24" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G25" t="s">
+        <v>1104</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G27" t="s">
+        <v>1104</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H30" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G32" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G33" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H33" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G34" t="s">
+        <v>1165</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H35" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G36" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1188</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1194</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H38" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H39" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E40" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F40" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G40" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F42" t="s">
+        <v>1222</v>
+      </c>
+      <c r="G42" t="s">
+        <v>1223</v>
+      </c>
+      <c r="H42" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H43" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E44" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F44" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G44" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H44" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E45" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F45" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G45" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H45" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E46" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F46" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G46" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H46" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E47" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F47" t="s">
+        <v>1259</v>
+      </c>
+      <c r="G47" t="s">
+        <v>1260</v>
+      </c>
+      <c r="H47" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E48" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1267</v>
+      </c>
+      <c r="G48" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H48" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E49" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F49" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G49" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H49" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E50" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1282</v>
+      </c>
+      <c r="G50" t="s">
+        <v>1283</v>
+      </c>
+      <c r="H50" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E51" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G51" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H51" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E52" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F52" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G52" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H52" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E53" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H53" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E54" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F54" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H54" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E55" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F55" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G55" t="s">
+        <v>1283</v>
+      </c>
+      <c r="H55" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D56" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E56" t="s">
+        <v>1325</v>
+      </c>
+      <c r="F56" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G56" t="s">
+        <v>1327</v>
+      </c>
+      <c r="H56" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E57" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F57" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G57" t="s">
+        <v>1333</v>
+      </c>
+      <c r="H57" t="s">
+        <v>1334</v>
       </c>
     </row>
   </sheetData>
@@ -7102,132 +11099,132 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>762</v>
+        <v>549</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>763</v>
+        <v>550</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>764</v>
+        <v>551</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>765</v>
+        <v>552</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>766</v>
+        <v>553</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>767</v>
+        <v>554</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>768</v>
+        <v>555</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>769</v>
+        <v>556</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>770</v>
+        <v>557</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>771</v>
+        <v>558</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>772</v>
+        <v>559</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>773</v>
+        <v>560</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>774</v>
+        <v>561</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>775</v>
+        <v>562</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>776</v>
+        <v>563</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>777</v>
+        <v>564</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>778</v>
+        <v>565</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>779</v>
+        <v>566</v>
       </c>
       <c r="B2" t="s">
-        <v>780</v>
+        <v>567</v>
       </c>
       <c r="C2" t="s">
-        <v>781</v>
+        <v>568</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>782</v>
+        <v>569</v>
       </c>
       <c r="B3" t="s">
-        <v>783</v>
+        <v>570</v>
       </c>
       <c r="C3" t="s">
-        <v>784</v>
+        <v>571</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>785</v>
+        <v>572</v>
       </c>
       <c r="B4" t="s">
-        <v>786</v>
+        <v>573</v>
       </c>
       <c r="C4" t="s">
-        <v>787</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>788</v>
+        <v>575</v>
       </c>
       <c r="B5" t="s">
-        <v>789</v>
+        <v>576</v>
       </c>
       <c r="C5" t="s">
-        <v>790</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>791</v>
+        <v>578</v>
       </c>
       <c r="B6" t="s">
-        <v>792</v>
+        <v>579</v>
       </c>
       <c r="C6" t="s">
-        <v>793</v>
+        <v>580</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>794</v>
+        <v>581</v>
       </c>
       <c r="B7" t="s">
-        <v>795</v>
+        <v>582</v>
       </c>
       <c r="C7" t="s">
-        <v>796</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>797</v>
+        <v>584</v>
       </c>
       <c r="B8" t="s">
-        <v>798</v>
+        <v>585</v>
       </c>
       <c r="C8" t="s">
-        <v>799</v>
+        <v>586</v>
       </c>
     </row>
   </sheetData>
@@ -7256,40 +11253,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>800</v>
+        <v>587</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>801</v>
+        <v>588</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>802</v>
+        <v>589</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>803</v>
+        <v>590</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>804</v>
+        <v>591</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>805</v>
+        <v>592</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>806</v>
+        <v>593</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>807</v>
+        <v>594</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>808</v>
+        <v>595</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>809</v>
+        <v>596</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>810</v>
+        <v>597</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>811</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
